--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232EA7E7-83D3-481B-8429-C7BD843CFFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D731D85-78C8-4A48-A27A-BB860D72DD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34980" yWindow="910" windowWidth="24460" windowHeight="20690" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -130,13 +130,91 @@
   </si>
   <si>
     <t>оценка перекрестных помех невозможна</t>
+  </si>
+  <si>
+    <t>частотная характеристика цепи в области высоких частот определяет</t>
+  </si>
+  <si>
+    <t>частотные признаки цепи в области высоких частот определяют</t>
+  </si>
+  <si>
+    <t>Частотная характеристика цепи в области низких частот определяет</t>
+  </si>
+  <si>
+    <t>Частотные признаки цепи в области низких частот определяют</t>
+  </si>
+  <si>
+    <t>исполнении непроводникового отделителя, применённого</t>
+  </si>
+  <si>
+    <t>варианте диэлектрической изоляции, примененнойварианте диэлектрической изоляции, примененной</t>
+  </si>
+  <si>
+    <t>звеньями внутреннего устройства числового прибора</t>
+  </si>
+  <si>
+    <t>элементами конструкции цифрового устройства</t>
+  </si>
+  <si>
+    <t>Послеразводочный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПОСТТОПОЛОГИЧЕСКИЙ </t>
+  </si>
+  <si>
+    <t>Предразводочный</t>
+  </si>
+  <si>
+    <t>ПРЕДТОПОЛОГИЧЕСКИЙ </t>
+  </si>
+  <si>
+    <t>импульсная характеристика снижается</t>
+  </si>
+  <si>
+    <t>всплескообразные признаки снижаются</t>
+  </si>
+  <si>
+    <t>присуща плоская переходная характеристика</t>
+  </si>
+  <si>
+    <t>присущи плоские переходные признаки</t>
+  </si>
+  <si>
+    <t>присуща нарастающая переходная характеристика</t>
+  </si>
+  <si>
+    <t>присущи нарастающие переходные признаки</t>
+  </si>
+  <si>
+    <t>присуща спадающая переходная характеристика</t>
+  </si>
+  <si>
+    <t>присущи спадающие переходные признаки</t>
+  </si>
+  <si>
+    <t>Краткий анализ видов реактивности, приведенный ниже</t>
+  </si>
+  <si>
+    <t>Краткая оценка видов мгновенности, приведенная ниже</t>
+  </si>
+  <si>
+    <t>Энергия, запасаемая</t>
+  </si>
+  <si>
+    <t>Электрический заряд, запасаемый</t>
+  </si>
+  <si>
+    <t>большую энергию электрического поля</t>
+  </si>
+  <si>
+    <t>большой заряд электрического поля</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,6 +243,14 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -186,11 +272,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -507,10 +594,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="55.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="64.36328125" customWidth="1"/>
     <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -634,6 +721,110 @@
         <v>29</v>
       </c>
     </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D731D85-78C8-4A48-A27A-BB860D72DD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D997523-7605-4B3B-BA78-45291FF5C44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34980" yWindow="910" windowWidth="24460" windowHeight="20690" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -208,6 +208,12 @@
   </si>
   <si>
     <t>большой заряд электрического поля</t>
+  </si>
+  <si>
+    <t>схема передачи данных, получающая</t>
+  </si>
+  <si>
+    <t>схема передачи данных, получающий</t>
   </si>
 </sst>
 </file>
@@ -594,7 +600,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="64.36328125" customWidth="1"/>
@@ -825,6 +831,14 @@
         <v>55</v>
       </c>
     </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D997523-7605-4B3B-BA78-45291FF5C44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF66DA6-0CC1-4EA2-B2CD-4FF90B10C91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1530" yWindow="330" windowWidth="28360" windowHeight="20690" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="Составные" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
     <sheet name="Лист4" sheetId="4" r:id="rId4"/>
     <sheet name="неизменные" sheetId="5" r:id="rId5"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -214,6 +214,12 @@
   </si>
   <si>
     <t>схема передачи данных, получающий</t>
+  </si>
+  <si>
+    <t>в материалах</t>
+  </si>
+  <si>
+    <t>в источниках</t>
   </si>
 </sst>
 </file>
@@ -573,9 +579,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="25.453125" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF66DA6-0CC1-4EA2-B2CD-4FF90B10C91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619D9FDC-9067-4A0A-8DFB-9FB8DB85CF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="330" windowWidth="28360" windowHeight="20690" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35090" yWindow="130" windowWidth="22560" windowHeight="20690" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -220,6 +220,54 @@
   </si>
   <si>
     <t>в источниках</t>
+  </si>
+  <si>
+    <t>подробная информация по этим методикам может быть найдена</t>
+  </si>
+  <si>
+    <t>подробные сведения по этим подходам могут быть найдены</t>
+  </si>
+  <si>
+    <t>которая не так проста</t>
+  </si>
+  <si>
+    <t>который не так прост</t>
+  </si>
+  <si>
+    <t>сложную» формулу</t>
+  </si>
+  <si>
+    <t>сложный» формулу</t>
+  </si>
+  <si>
+    <t>Уилера дала бы большую точность</t>
+  </si>
+  <si>
+    <t>Уилера дал бы большую точность</t>
+  </si>
+  <si>
+    <t>недостаток – она</t>
+  </si>
+  <si>
+    <t>недостаток – он</t>
+  </si>
+  <si>
+    <t>центра линии</t>
+  </si>
+  <si>
+    <t>сосредоточения дороги</t>
+  </si>
+  <si>
+    <t>один керамический конденсатор</t>
+  </si>
+  <si>
+    <t>одну керамическую ёмкость</t>
+  </si>
+  <si>
+    <t>capacitor), обеспечивающий</t>
+  </si>
+  <si>
+    <t>capacitor), обеспечивающую</t>
   </si>
 </sst>
 </file>
@@ -579,11 +627,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.453125" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.36328125" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -592,6 +640,62 @@
       </c>
       <c r="B1" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -619,7 +723,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="64.36328125" customWidth="1"/>
@@ -858,6 +962,14 @@
         <v>57</v>
       </c>
     </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619D9FDC-9067-4A0A-8DFB-9FB8DB85CF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8E859A-B0CC-435D-91AD-8CEA6C37BFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35090" yWindow="130" windowWidth="22560" windowHeight="20690" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21600" yWindow="0" windowWidth="21720" windowHeight="20690" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -268,13 +268,73 @@
   </si>
   <si>
     <t>capacitor), обеспечивающую</t>
+  </si>
+  <si>
+    <t>полномасштабный Фурье-анализ</t>
+  </si>
+  <si>
+    <t>полноразмерную Фурье-оценку</t>
+  </si>
+  <si>
+    <t>неравномерной частотной характеристики</t>
+  </si>
+  <si>
+    <t>неравномерных частотных признаков</t>
+  </si>
+  <si>
+    <t>его переходной характеристики во времени — является ли она постоянной, нарастающей или спадающей</t>
+  </si>
+  <si>
+    <t>его переходных признаков во времени — являются ли она постоянными, нарастающими или спадающими</t>
+  </si>
+  <si>
+    <t>большое количество энергии, которая накапливается</t>
+  </si>
+  <si>
+    <t>большое количество зарядов, которые накапливаются</t>
+  </si>
+  <si>
+    <t>приведена измерительная схема, идеально подходящая</t>
+  </si>
+  <si>
+    <t>приведён измерительный чертёж, совершенно подходящий</t>
+  </si>
+  <si>
+    <t>сквозной переходной характеристики</t>
+  </si>
+  <si>
+    <t>сквозных переходных признаков</t>
+  </si>
+  <si>
+    <t>Сквозная переходная характеристика</t>
+  </si>
+  <si>
+    <t>Сквозной переходный признак</t>
+  </si>
+  <si>
+    <t>его переходная характеристика начинает сказываться</t>
+  </si>
+  <si>
+    <t>его переходные признаки начинают сказываться</t>
+  </si>
+  <si>
+    <t>наблюдаемой переходной характеристике</t>
+  </si>
+  <si>
+    <t>наблюдаемом переходном признаке</t>
+  </si>
+  <si>
+    <t>амплитуду сигнала, которая составила</t>
+  </si>
+  <si>
+    <t>амплитуду сигнала, который составил</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,6 +371,13 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -332,12 +399,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -627,7 +695,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.36328125" customWidth="1"/>
@@ -696,6 +764,14 @@
       </c>
       <c r="B8" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -723,11 +799,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="64.36328125" customWidth="1"/>
     <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -970,6 +1047,78 @@
         <v>61</v>
       </c>
     </row>
+    <row r="31" spans="1:2" ht="18" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" t="s">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8E859A-B0CC-435D-91AD-8CEA6C37BFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9DA166-0AA0-4704-8C74-49CDBB37C261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="0" windowWidth="21720" windowHeight="20690" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4150" yWindow="120" windowWidth="16620" windowHeight="20690" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Составные" sheetId="2" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="Вездесущие" sheetId="3" r:id="rId3"/>
     <sheet name="Лист4" sheetId="4" r:id="rId4"/>
     <sheet name="неизменные" sheetId="5" r:id="rId5"/>
   </sheets>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -328,13 +328,43 @@
   </si>
   <si>
     <t>амплитуду сигнала, который составил</t>
+  </si>
+  <si>
+    <t>емко ст</t>
+  </si>
+  <si>
+    <t>емкост</t>
+  </si>
+  <si>
+    <t>индуктивно ст</t>
+  </si>
+  <si>
+    <t>индуктивност</t>
+  </si>
+  <si>
+    <t>те стов</t>
+  </si>
+  <si>
+    <t>тестов</t>
+  </si>
+  <si>
+    <t>используемый для закорачивания инструмент</t>
+  </si>
+  <si>
+    <t>используемое для закорачивания средство</t>
+  </si>
+  <si>
+    <t>цифровая схема, вероятно, окажется неработоспособной</t>
+  </si>
+  <si>
+    <t>числовой чертёж, вероятно, окажется неработоспособным</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -378,6 +408,13 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -399,13 +436,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -781,9 +820,53 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="19.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9DA166-0AA0-4704-8C74-49CDBB37C261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290BC46F-CA05-45BF-8F2D-5B52BEB35F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4150" yWindow="120" windowWidth="16620" windowHeight="20690" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -823,7 +823,7 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.1796875" customWidth="1"/>
+    <col min="1" max="1" width="34.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -5,19 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\запас словарей\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290BC46F-CA05-45BF-8F2D-5B52BEB35F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43CAB21-828C-4A7F-AD76-6B1949D14E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Составные" sheetId="2" r:id="rId2"/>
-    <sheet name="Вездесущие" sheetId="3" r:id="rId3"/>
-    <sheet name="Лист4" sheetId="4" r:id="rId4"/>
-    <sheet name="неизменные" sheetId="5" r:id="rId5"/>
+    <sheet name="Составные" sheetId="2" r:id="rId1"/>
+    <sheet name="Вездесущие" sheetId="3" r:id="rId2"/>
+    <sheet name="Неизменные" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -724,15 +722,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -818,7 +807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -871,16 +860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB91D88-4124-4C4D-8771-3FC1925EDAC2}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
   <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\запас словарей\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43CAB21-828C-4A7F-AD76-6B1949D14E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE5B4EB-91AA-49E1-A8D3-FB4DC24C2BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
     <sheet name="Вездесущие" sheetId="3" r:id="rId2"/>
     <sheet name="Неизменные" sheetId="5" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Неизменные!$A$1:$B$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные!$A$1:$B$9</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -803,6 +807,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B9" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -812,7 +817,7 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.08984375" customWidth="1"/>
+    <col min="1" max="1" width="54.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1183,6 +1188,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B39" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE5B4EB-91AA-49E1-A8D3-FB4DC24C2BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA25D47-1EB5-4B7E-AD95-E2974D4F8F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -360,6 +360,12 @@
   </si>
   <si>
     <t>числовой чертёж, вероятно, окажется неработоспособным</t>
+  </si>
+  <si>
+    <t>геометрией проводников</t>
+  </si>
+  <si>
+    <t>прокладкой проводников</t>
   </si>
 </sst>
 </file>
@@ -727,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.36328125" customWidth="1"/>
@@ -804,6 +810,14 @@
       </c>
       <c r="B9" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA25D47-1EB5-4B7E-AD95-E2974D4F8F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37CFBD4-DBC3-43B6-BF92-F6667ACDC8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
-    <sheet name="Вездесущие" sheetId="3" r:id="rId2"/>
-    <sheet name="Неизменные" sheetId="5" r:id="rId3"/>
+    <sheet name="составные важные" sheetId="6" r:id="rId2"/>
+    <sheet name="Вездесущие" sheetId="3" r:id="rId3"/>
+    <sheet name="Неизменные" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Неизменные!$A$1:$B$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Неизменные!$A$1:$B$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -366,6 +367,66 @@
   </si>
   <si>
     <t>прокладкой проводников</t>
+  </si>
+  <si>
+    <t>выбранная изначально структура печатной платы может быть изменена</t>
+  </si>
+  <si>
+    <t>выбранное изначально устройство печатной платы может быть изменено</t>
+  </si>
+  <si>
+    <t>геометрия печатной платы</t>
+  </si>
+  <si>
+    <t>пространственный образ печатной платый</t>
+  </si>
+  <si>
+    <t>новой элементной базой</t>
+  </si>
+  <si>
+    <t>новым перечнем составных частей</t>
+  </si>
+  <si>
+    <t>Следующая рекомендация достаточно очевидна</t>
+  </si>
+  <si>
+    <t>Следующее предложение достаточно очевидно</t>
+  </si>
+  <si>
+    <t>эффективными паразитными антеннами.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">главными приёмо-передатчиками по улавливанию вредных помех </t>
+  </si>
+  <si>
+    <t>паразитной дипольной антенны</t>
+  </si>
+  <si>
+    <t>вредного двузарядного приёмо-передатчика</t>
+  </si>
+  <si>
+    <t>к полюсу низкого потенциала</t>
+  </si>
+  <si>
+    <t>к краю низкого уровня заряда</t>
+  </si>
+  <si>
+    <t>Геометрия трасс</t>
+  </si>
+  <si>
+    <t>Пространственное расположение дорог</t>
+  </si>
+  <si>
+    <t>реактивного сопротивления, который</t>
+  </si>
+  <si>
+    <t>мгновенного сопротивления, которое</t>
+  </si>
+  <si>
+    <t>Другая аналогия, возможно более подходящая</t>
+  </si>
+  <si>
+    <t>Другое подобие, возможно более подходящее</t>
   </si>
 </sst>
 </file>
@@ -748,14 +809,6 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-    </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>64</v>
@@ -764,14 +817,6 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-    </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>68</v>
@@ -794,22 +839,6 @@
       </c>
       <c r="B7" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -827,6 +856,84 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="43.453125" customWidth="1"/>
+    <col min="2" max="2" width="49.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -879,9 +986,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="64.36328125" customWidth="1"/>
@@ -1201,6 +1308,54 @@
         <v>95</v>
       </c>
     </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>74</v>
+      </c>
+      <c r="B42" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B39" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37CFBD4-DBC3-43B6-BF92-F6667ACDC8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720C6F8E-38AF-47A5-9AAC-94377A54A28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -427,6 +427,30 @@
   </si>
   <si>
     <t>Другое подобие, возможно более подходящее</t>
+  </si>
+  <si>
+    <t>характеристика линии передачи, показывающая</t>
+  </si>
+  <si>
+    <t>признак дороги передачи, показывающий</t>
+  </si>
+  <si>
+    <t>характеристический импеданс</t>
+  </si>
+  <si>
+    <t>описательное полное сопротивление (Z)</t>
+  </si>
+  <si>
+    <t>общий импеданс</t>
+  </si>
+  <si>
+    <t>общее полное сопротивление (Z)</t>
+  </si>
+  <si>
+    <t>регулировать значение импеданса</t>
+  </si>
+  <si>
+    <t>отслеживать значение полного сопротивления (Z)</t>
   </si>
 </sst>
 </file>
@@ -857,7 +881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.453125" customWidth="1"/>
@@ -928,6 +952,30 @@
         <v>125</v>
       </c>
     </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" t="s">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -935,7 +983,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="54.36328125" customWidth="1"/>
@@ -979,6 +1027,14 @@
       </c>
       <c r="B5" s="7" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720C6F8E-38AF-47A5-9AAC-94377A54A28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DE2E9E-AC64-4591-83FF-31FB2DA719C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
     <sheet name="составные важные" sheetId="6" r:id="rId2"/>
     <sheet name="Вездесущие" sheetId="3" r:id="rId3"/>
     <sheet name="Неизменные" sheetId="5" r:id="rId4"/>
+    <sheet name="Неизменные_короткие" sheetId="8" r:id="rId5"/>
+    <sheet name="Неизменные_длинные" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Неизменные!$A$1:$B$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Неизменные!$A$1:$B$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -435,12 +437,6 @@
     <t>признак дороги передачи, показывающий</t>
   </si>
   <si>
-    <t>характеристический импеданс</t>
-  </si>
-  <si>
-    <t>описательное полное сопротивление (Z)</t>
-  </si>
-  <si>
     <t>общий импеданс</t>
   </si>
   <si>
@@ -451,13 +447,55 @@
   </si>
   <si>
     <t>отслеживать значение полного сопротивления (Z)</t>
+  </si>
+  <si>
+    <t>с геометрией трасс</t>
+  </si>
+  <si>
+    <t>с пространственным расположением дорог</t>
+  </si>
+  <si>
+    <t>Активное сопротивление</t>
+  </si>
+  <si>
+    <t>Постоянное сопротивление</t>
+  </si>
+  <si>
+    <t>ожидаемый контур</t>
+  </si>
+  <si>
+    <t>ожидаемый путь</t>
+  </si>
+  <si>
+    <t>Контур тока на высокой</t>
+  </si>
+  <si>
+    <t>Путь тока на высокой</t>
+  </si>
+  <si>
+    <t>контура тока на низкой</t>
+  </si>
+  <si>
+    <t>пути тока на низкой</t>
+  </si>
+  <si>
+    <t>уменьшения контура тока</t>
+  </si>
+  <si>
+    <t>уменьшения пути тока</t>
+  </si>
+  <si>
+    <t>каждого развязывающего конденсатора</t>
+  </si>
+  <si>
+    <t>каждой развязывающей ёмкости</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -508,6 +546,13 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF252A3A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -529,7 +574,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -538,6 +583,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -818,7 +864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.36328125" customWidth="1"/>
@@ -833,6 +879,14 @@
         <v>59</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" t="s">
+        <v>139</v>
+      </c>
+    </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>64</v>
@@ -841,6 +895,14 @@
         <v>65</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" t="s">
+        <v>123</v>
+      </c>
+    </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>68</v>
@@ -865,12 +927,39 @@
         <v>73</v>
       </c>
     </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" t="s">
+        <v>137</v>
+      </c>
+    </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>106</v>
       </c>
       <c r="B10" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -881,21 +970,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A2:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.453125" customWidth="1"/>
     <col min="2" max="2" width="49.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" t="s">
-        <v>111</v>
-      </c>
-    </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>62</v>
@@ -938,10 +1019,10 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -954,26 +1035,34 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>130</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>132</v>
-      </c>
-      <c r="B10" t="s">
-        <v>133</v>
+        <v>144</v>
+      </c>
+      <c r="B9" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>134</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1044,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="64.36328125" customWidth="1"/>
@@ -1197,223 +1286,259 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>34</v>
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>38</v>
+      <c r="A20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
+      <c r="A21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>55</v>
+        <v>80</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="18" x14ac:dyDescent="0.4">
+        <v>84</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>81</v>
+        <v>86</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>83</v>
+      <c r="A32" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
+      </c>
+      <c r="B33" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
+      </c>
+      <c r="B34" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>79</v>
+      <c r="A35" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" t="s">
-        <v>91</v>
+      <c r="A37" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
-        <v>92</v>
+      <c r="A38" t="s">
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
-        <v>94</v>
+      <c r="A39" t="s">
+        <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>109</v>
+      <c r="A40" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>116</v>
-      </c>
-      <c r="B43" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>120</v>
-      </c>
-      <c r="B44" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>126</v>
-      </c>
-      <c r="B45" t="s">
         <v>127</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B39" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}"/>
+  <autoFilter ref="A1:B36" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.453125" customWidth="1"/>
+    <col min="2" max="2" width="81.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="53.54296875" customWidth="1"/>
+    <col min="2" max="2" width="76.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DE2E9E-AC64-4591-83FF-31FB2DA719C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BB43D2-67C2-4FA8-8825-3349B4530158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -489,6 +489,30 @@
   </si>
   <si>
     <t>каждой развязывающей ёмкости</t>
+  </si>
+  <si>
+    <t>электрон должен пересечь барьер</t>
+  </si>
+  <si>
+    <t>отрицательная частица должна пересечь преграду</t>
+  </si>
+  <si>
+    <t>из потенциальной</t>
+  </si>
+  <si>
+    <t>из внутренней</t>
+  </si>
+  <si>
+    <t>большинством электронных компонентов</t>
+  </si>
+  <si>
+    <t>большинством электронными составными частями</t>
+  </si>
+  <si>
+    <t>электрохимический элемент</t>
+  </si>
+  <si>
+    <t>электрохимический источник</t>
   </si>
 </sst>
 </file>
@@ -864,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.36328125" customWidth="1"/>
@@ -952,7 +976,12 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B11" s="3"/>
+      <c r="A11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
@@ -960,6 +989,14 @@
       </c>
       <c r="B12" t="s">
         <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B13" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -1041,6 +1078,14 @@
         <v>145</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" t="s">
+        <v>153</v>
+      </c>
+    </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>132</v>
@@ -1485,10 +1530,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.453125" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="81.54296875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1514,6 +1559,14 @@
       </c>
       <c r="B3" t="s">
         <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BB43D2-67C2-4FA8-8825-3349B4530158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A2A506-3749-4371-8111-AB2AC511831E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -513,6 +513,18 @@
   </si>
   <si>
     <t>электрохимический источник</t>
+  </si>
+  <si>
+    <t>к помехам интерфейса</t>
+  </si>
+  <si>
+    <t>к помехам средства передачи данных</t>
+  </si>
+  <si>
+    <t>омического сопротивления</t>
+  </si>
+  <si>
+    <t>сопротивления (Ом)</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A2:B13"/>
+  <dimension ref="A2:B14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.453125" customWidth="1"/>
@@ -1108,6 +1120,14 @@
       </c>
       <c r="B13" s="8" t="s">
         <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -1178,7 +1198,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="64.36328125" customWidth="1"/>
@@ -1520,6 +1540,14 @@
       </c>
       <c r="B42" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>158</v>
+      </c>
+      <c r="B43" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A2A506-3749-4371-8111-AB2AC511831E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA97235F-494D-4A7D-ABC8-5569D779EEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
-    <sheet name="составные важные" sheetId="6" r:id="rId2"/>
-    <sheet name="Вездесущие" sheetId="3" r:id="rId3"/>
-    <sheet name="Неизменные" sheetId="5" r:id="rId4"/>
-    <sheet name="Неизменные_короткие" sheetId="8" r:id="rId5"/>
-    <sheet name="Неизменные_длинные" sheetId="7" r:id="rId6"/>
+    <sheet name="простые" sheetId="9" r:id="rId2"/>
+    <sheet name="составные важные" sheetId="6" r:id="rId3"/>
+    <sheet name="Вездесущие" sheetId="3" r:id="rId4"/>
+    <sheet name="Неизменные" sheetId="5" r:id="rId5"/>
+    <sheet name="Неизменные_короткие" sheetId="8" r:id="rId6"/>
+    <sheet name="Неизменные_длинные" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Неизменные!$A$1:$B$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Неизменные!$A$1:$B$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -437,12 +438,6 @@
     <t>признак дороги передачи, показывающий</t>
   </si>
   <si>
-    <t>общий импеданс</t>
-  </si>
-  <si>
-    <t>общее полное сопротивление (Z)</t>
-  </si>
-  <si>
     <t>регулировать значение импеданса</t>
   </si>
   <si>
@@ -509,12 +504,6 @@
     <t>большинством электронными составными частями</t>
   </si>
   <si>
-    <t>электрохимический элемент</t>
-  </si>
-  <si>
-    <t>электрохимический источник</t>
-  </si>
-  <si>
     <t>к помехам интерфейса</t>
   </si>
   <si>
@@ -525,6 +514,24 @@
   </si>
   <si>
     <t>сопротивления (Ом)</t>
+  </si>
+  <si>
+    <t>материалы в разъеме подобраны</t>
+  </si>
+  <si>
+    <t>сырьё составных частей в разъёме подобрано</t>
+  </si>
+  <si>
+    <t>характерный фон</t>
+  </si>
+  <si>
+    <t>присущие помехи</t>
+  </si>
+  <si>
+    <t>длинную линию</t>
+  </si>
+  <si>
+    <t>длинную дорогу</t>
   </si>
 </sst>
 </file>
@@ -900,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.36328125" customWidth="1"/>
@@ -917,10 +924,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -963,20 +970,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B8" t="s">
-        <v>131</v>
-      </c>
-    </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -989,10 +988,10 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1005,11 +1004,67 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
-      </c>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B9" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}"/>
@@ -1018,8 +1073,98 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56074B3-3BB9-4C57-99AF-4053FDDF42F2}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A2:B14"/>
+  <dimension ref="A2:B19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.453125" customWidth="1"/>
@@ -1068,10 +1213,10 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1084,60 +1229,84 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>156</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>157</v>
       </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="54.36328125" customWidth="1"/>
@@ -1191,12 +1360,16 @@
         <v>129</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
   <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1544,10 +1717,10 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B43" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -1556,7 +1729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1583,18 +1756,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1602,7 +1775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA97235F-494D-4A7D-ABC8-5569D779EEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4CD56BD-6929-47B1-B83C-A5175FC520DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Составные" sheetId="2" r:id="rId1"/>
-    <sheet name="простые" sheetId="9" r:id="rId2"/>
+    <sheet name="простые" sheetId="9" r:id="rId1"/>
+    <sheet name="Составные" sheetId="2" r:id="rId2"/>
     <sheet name="составные важные" sheetId="6" r:id="rId3"/>
     <sheet name="Вездесущие" sheetId="3" r:id="rId4"/>
     <sheet name="Неизменные" sheetId="5" r:id="rId5"/>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Неизменные!$A$1:$B$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Составные!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="238">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -532,13 +532,241 @@
   </si>
   <si>
     <t>длинную дорогу</t>
+  </si>
+  <si>
+    <t>юный и малоопытный технический персонал</t>
+  </si>
+  <si>
+    <t>с микшерным пультом</t>
+  </si>
+  <si>
+    <t>со смешанной лентяйкой</t>
+  </si>
+  <si>
+    <t>юных и малоопытных технических сотрудников</t>
+  </si>
+  <si>
+    <t>при миграционной поляризации</t>
+  </si>
+  <si>
+    <t>при переездном изменении заряда</t>
+  </si>
+  <si>
+    <t>Релаксационная и миграционная поляризация</t>
+  </si>
+  <si>
+    <t>Блаженственное и переездное изменение заряда</t>
+  </si>
+  <si>
+    <t>взятый диполь</t>
+  </si>
+  <si>
+    <t>взятые два противоположных заряда</t>
+  </si>
+  <si>
+    <t>взятый диполь должен менять</t>
+  </si>
+  <si>
+    <t>взятые два противоположных заряда должны менять</t>
+  </si>
+  <si>
+    <t>взятого диполя</t>
+  </si>
+  <si>
+    <t>взятых двух противоположных зарядов</t>
+  </si>
+  <si>
+    <t>в плоский конденсатор</t>
+  </si>
+  <si>
+    <t>в плоскую ёмкость</t>
+  </si>
+  <si>
+    <t>плоский конденсатор</t>
+  </si>
+  <si>
+    <t>плоская ёмкость</t>
+  </si>
+  <si>
+    <t>плоского конденсатора</t>
+  </si>
+  <si>
+    <t>плоской ёмкости</t>
+  </si>
+  <si>
+    <t>Эталонным называется конденсатор</t>
+  </si>
+  <si>
+    <t>Образцовой называется ёмкость</t>
+  </si>
+  <si>
+    <t>Входной импеданс</t>
+  </si>
+  <si>
+    <t>Входное полное сопротивление (Z)</t>
+  </si>
+  <si>
+    <t>Выходной импеданс</t>
+  </si>
+  <si>
+    <t>выходное полное сопротивление (Z)</t>
+  </si>
+  <si>
+    <t>Дифференциальный импеданс</t>
+  </si>
+  <si>
+    <t>Разностное полное сопротивление (Z)</t>
+  </si>
+  <si>
+    <t>импеданс близок</t>
+  </si>
+  <si>
+    <t>полное сопротивление (Z) близко</t>
+  </si>
+  <si>
+    <t>Импеданс подобен</t>
+  </si>
+  <si>
+    <t>Полное сопротивление (z) подобно</t>
+  </si>
+  <si>
+    <t>импеданс постоянен</t>
+  </si>
+  <si>
+    <t>полное сопротивление (Z) постоянно</t>
+  </si>
+  <si>
+    <t>импеданс, определяемый</t>
+  </si>
+  <si>
+    <t>полное сопротивление (Z), определяемое</t>
+  </si>
+  <si>
+    <t>импеданса линии</t>
+  </si>
+  <si>
+    <t>полного сопротивление (Z) дорожки</t>
+  </si>
+  <si>
+    <t>калькулятора импеданса</t>
+  </si>
+  <si>
+    <t>рассчётчика полного сопротивления (Z)</t>
+  </si>
+  <si>
+    <t>калькуляторы дифференциального импеданса</t>
+  </si>
+  <si>
+    <t>рассчётчики разностного полного сопротивления (Z)</t>
+  </si>
+  <si>
+    <t>Калькуляторы импеданса</t>
+  </si>
+  <si>
+    <t>рассчётчики полного сопротивления (Z)</t>
+  </si>
+  <si>
+    <t>низкий импеданс</t>
+  </si>
+  <si>
+    <t>низкое полное сопротивление (Z)</t>
+  </si>
+  <si>
+    <t>собственный импеданс</t>
+  </si>
+  <si>
+    <t>собственное полное сопротивление (Z)</t>
+  </si>
+  <si>
+    <t>характеристический импеданс</t>
+  </si>
+  <si>
+    <t>определённое полное сопротивление (Z)</t>
+  </si>
+  <si>
+    <t>характеристическим импедансом</t>
+  </si>
+  <si>
+    <t>признаком полного сопротивления (Z)</t>
+  </si>
+  <si>
+    <t>что одиночный импеданс</t>
+  </si>
+  <si>
+    <t>что одиночное полное сопротивление (Z)</t>
+  </si>
+  <si>
+    <t>дифференциальный импеданс пары</t>
+  </si>
+  <si>
+    <t>полное сопротивление (Z) разностной двойки</t>
+  </si>
+  <si>
+    <t>правильный дифференциальный импеданс</t>
+  </si>
+  <si>
+    <t>правильное разностное полное сопротивление (Z)</t>
+  </si>
+  <si>
+    <t>получила шина</t>
+  </si>
+  <si>
+    <t>получило многопутевое средство обмена данными</t>
+  </si>
+  <si>
+    <t>Шина однонаправленная</t>
+  </si>
+  <si>
+    <t>Многопутевое средство обмена данными однонаправленно</t>
+  </si>
+  <si>
+    <t>проектируемой шины</t>
+  </si>
+  <si>
+    <t>разрабатываемой многопутевого средства обмена данными</t>
+  </si>
+  <si>
+    <t>предварительную схему сборки, которая</t>
+  </si>
+  <si>
+    <t>предварительный чертёж сборки, который</t>
+  </si>
+  <si>
+    <t>Информация по сборке платы должна быть очень точной</t>
+  </si>
+  <si>
+    <t>Сведения по сборке платы должны быть очень точными</t>
+  </si>
+  <si>
+    <t>нужен специальный анализ</t>
+  </si>
+  <si>
+    <t>нужна особая оценка</t>
+  </si>
+  <si>
+    <t>Эта информация для контроллера приведена</t>
+  </si>
+  <si>
+    <t>Эти сведения для распорядителя приведены</t>
+  </si>
+  <si>
+    <t>в его спецификации</t>
+  </si>
+  <si>
+    <t>в его сводах требований</t>
+  </si>
+  <si>
+    <t>конструкция шины достаточно проста</t>
+  </si>
+  <si>
+    <t>устройство многопутевого средства обмена данными достаточно просто</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -596,6 +824,18 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF212529"/>
+      <name val="Open Sans"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -617,7 +857,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -627,6 +867,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -906,173 +1148,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="48.36328125" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>158</v>
-      </c>
-      <c r="B13" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B9" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56074B3-3BB9-4C57-99AF-4053FDDF42F2}">
   <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1162,9 +1237,188 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="48.36328125" customWidth="1"/>
+    <col min="2" max="2" width="51.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B9" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A2:B19"/>
+  <dimension ref="A2:B23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.453125" customWidth="1"/>
@@ -1245,10 +1499,10 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="B11" t="s">
-        <v>131</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1284,20 +1538,68 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
+      <c r="A16" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
+      <c r="A19" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>235</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1731,7 +2033,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1770,6 +2072,38 @@
         <v>147</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B8" t="s">
+        <v>237</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1777,7 +2111,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="53.54296875" customWidth="1"/>
@@ -1792,6 +2126,158 @@
         <v>34</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4CD56BD-6929-47B1-B83C-A5175FC520DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1A5538-49E9-4CF3-8443-1B047F22C6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="простые" sheetId="9" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="403">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -760,6 +760,501 @@
   </si>
   <si>
     <t>устройство многопутевого средства обмена данными достаточно просто</t>
+  </si>
+  <si>
+    <t>Две основные проводимые контроллером операции</t>
+  </si>
+  <si>
+    <t>Два основные проводимые распорядителем действия</t>
+  </si>
+  <si>
+    <t>Двунаправленная шина</t>
+  </si>
+  <si>
+    <t>Двунаправленное многопутевое средство обмена данными</t>
+  </si>
+  <si>
+    <t>первый важный элемент</t>
+  </si>
+  <si>
+    <t>первое важное звено</t>
+  </si>
+  <si>
+    <t>честный синхронный дизайн</t>
+  </si>
+  <si>
+    <t>честное согласованое внешнее исполнение</t>
+  </si>
+  <si>
+    <t>первой команды</t>
+  </si>
+  <si>
+    <t>первого приказа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Каждая команда </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Каждый приказ </t>
+  </si>
+  <si>
+    <t>выдачи пакета</t>
+  </si>
+  <si>
+    <t>выдачи посылки</t>
+  </si>
+  <si>
+    <t>выдач пакета</t>
+  </si>
+  <si>
+    <t>выдач посылки</t>
+  </si>
+  <si>
+    <t>выдачей пакета</t>
+  </si>
+  <si>
+    <t>выдачей посылки</t>
+  </si>
+  <si>
+    <t>выдачам пакета</t>
+  </si>
+  <si>
+    <t>выдачам посылки</t>
+  </si>
+  <si>
+    <t>выдачу пакета</t>
+  </si>
+  <si>
+    <t>выдачу посылки</t>
+  </si>
+  <si>
+    <t>длина пакета</t>
+  </si>
+  <si>
+    <t>длина посылки</t>
+  </si>
+  <si>
+    <t>длин пакета</t>
+  </si>
+  <si>
+    <t>длин посылки</t>
+  </si>
+  <si>
+    <t>длинах пакета</t>
+  </si>
+  <si>
+    <t>длина хпосылки</t>
+  </si>
+  <si>
+    <t>длинам пакета</t>
+  </si>
+  <si>
+    <t>длинам посылки</t>
+  </si>
+  <si>
+    <t>длинами пакета</t>
+  </si>
+  <si>
+    <t>длинами посылки</t>
+  </si>
+  <si>
+    <t>длиной пакета</t>
+  </si>
+  <si>
+    <t>длиной посылки</t>
+  </si>
+  <si>
+    <t>длине пакета</t>
+  </si>
+  <si>
+    <t>длине посылки</t>
+  </si>
+  <si>
+    <t>длину пакета</t>
+  </si>
+  <si>
+    <t>длину посылки</t>
+  </si>
+  <si>
+    <t>длины пакета</t>
+  </si>
+  <si>
+    <t>длины посылки</t>
+  </si>
+  <si>
+    <t>порядком пакета</t>
+  </si>
+  <si>
+    <t>порядком посылки</t>
+  </si>
+  <si>
+    <t>порядков пакета</t>
+  </si>
+  <si>
+    <t>порядков посылки</t>
+  </si>
+  <si>
+    <t>порядка пакета</t>
+  </si>
+  <si>
+    <t>порядка посылки</t>
+  </si>
+  <si>
+    <t>порядке пакета</t>
+  </si>
+  <si>
+    <t>порядке посылки</t>
+  </si>
+  <si>
+    <t>порядку пакета</t>
+  </si>
+  <si>
+    <t>порядку посылки</t>
+  </si>
+  <si>
+    <t>порядки пакета</t>
+  </si>
+  <si>
+    <t>порядки посылки</t>
+  </si>
+  <si>
+    <t>порядкам пакета</t>
+  </si>
+  <si>
+    <t>порядкам посылки</t>
+  </si>
+  <si>
+    <t>порядками пакета</t>
+  </si>
+  <si>
+    <t>порядками посылки</t>
+  </si>
+  <si>
+    <t>порядках пакета</t>
+  </si>
+  <si>
+    <t>порядках посылки</t>
+  </si>
+  <si>
+    <t>порядок пакета</t>
+  </si>
+  <si>
+    <t>порядок посылки</t>
+  </si>
+  <si>
+    <t>длине пакетов</t>
+  </si>
+  <si>
+    <t>длине посылок</t>
+  </si>
+  <si>
+    <t>длина пакетов</t>
+  </si>
+  <si>
+    <t>длина посылок</t>
+  </si>
+  <si>
+    <t>длины пакетов</t>
+  </si>
+  <si>
+    <t>длины посылок</t>
+  </si>
+  <si>
+    <t>длину пакетов</t>
+  </si>
+  <si>
+    <t>длину посылок</t>
+  </si>
+  <si>
+    <t>длинам пакетов</t>
+  </si>
+  <si>
+    <t>длинам посылок</t>
+  </si>
+  <si>
+    <t>длинами пакетов</t>
+  </si>
+  <si>
+    <t>длинами посылок</t>
+  </si>
+  <si>
+    <t>длинах пакетов</t>
+  </si>
+  <si>
+    <t>длинах посылок</t>
+  </si>
+  <si>
+    <t>длин пакетов</t>
+  </si>
+  <si>
+    <t>длин посылок</t>
+  </si>
+  <si>
+    <t>длиной пакетов</t>
+  </si>
+  <si>
+    <t>длиной посылок</t>
+  </si>
+  <si>
+    <t>длинных пакетов</t>
+  </si>
+  <si>
+    <t>длинных посылок</t>
+  </si>
+  <si>
+    <t>всему пакету</t>
+  </si>
+  <si>
+    <t>всей посылке</t>
+  </si>
+  <si>
+    <t>всего пакета</t>
+  </si>
+  <si>
+    <t>всей посылки</t>
+  </si>
+  <si>
+    <t>всех пакетов</t>
+  </si>
+  <si>
+    <t>всех посылок</t>
+  </si>
+  <si>
+    <t>обрывающая пакет</t>
+  </si>
+  <si>
+    <t>обрывающая посылку</t>
+  </si>
+  <si>
+    <t>обрывающий пакет</t>
+  </si>
+  <si>
+    <t>обрывающий посылку</t>
+  </si>
+  <si>
+    <t>обрывающие пакет</t>
+  </si>
+  <si>
+    <t>обрывающие посылку</t>
+  </si>
+  <si>
+    <t>обрывающим пакет</t>
+  </si>
+  <si>
+    <t>обрывающим посылку</t>
+  </si>
+  <si>
+    <t>обрывающих пакет</t>
+  </si>
+  <si>
+    <t>обрывающих посылку</t>
+  </si>
+  <si>
+    <t>обрывающую пакет</t>
+  </si>
+  <si>
+    <t>обрывающую посылку</t>
+  </si>
+  <si>
+    <t>обрывающего пакет</t>
+  </si>
+  <si>
+    <t>обрывающего посылку</t>
+  </si>
+  <si>
+    <t>обрывающей пакет</t>
+  </si>
+  <si>
+    <t>обрывающей посылку</t>
+  </si>
+  <si>
+    <t>обрывающее пакет</t>
+  </si>
+  <si>
+    <t>обрывающее посылку</t>
+  </si>
+  <si>
+    <t>прерывающая пакет</t>
+  </si>
+  <si>
+    <t>прерывающая посылку</t>
+  </si>
+  <si>
+    <t>прерывающа пакет</t>
+  </si>
+  <si>
+    <t>прерывающа посылку</t>
+  </si>
+  <si>
+    <t>прерывающую пакет</t>
+  </si>
+  <si>
+    <t>прерывающую посылку</t>
+  </si>
+  <si>
+    <t>прерывающее пакет</t>
+  </si>
+  <si>
+    <t>прерывающее посылку</t>
+  </si>
+  <si>
+    <t>прерывающе пакет</t>
+  </si>
+  <si>
+    <t>прерывающе посылку</t>
+  </si>
+  <si>
+    <t>прерывающем пакет</t>
+  </si>
+  <si>
+    <t>прерывающем посылку</t>
+  </si>
+  <si>
+    <t>прерывающему пакет</t>
+  </si>
+  <si>
+    <t>прерывающему посылку</t>
+  </si>
+  <si>
+    <t>прерывающей пакет</t>
+  </si>
+  <si>
+    <t>прерывающей посылку</t>
+  </si>
+  <si>
+    <t>прерывающего пакет</t>
+  </si>
+  <si>
+    <t>прерывающего посылку</t>
+  </si>
+  <si>
+    <t>размер пакета</t>
+  </si>
+  <si>
+    <t>размер посылки</t>
+  </si>
+  <si>
+    <t>размера пакета</t>
+  </si>
+  <si>
+    <t>размеры пакета</t>
+  </si>
+  <si>
+    <t>размеры посылки</t>
+  </si>
+  <si>
+    <t>размерам пакета</t>
+  </si>
+  <si>
+    <t>размерам посылки</t>
+  </si>
+  <si>
+    <t>размерами пакета</t>
+  </si>
+  <si>
+    <t>размерами посылки</t>
+  </si>
+  <si>
+    <t>размерах пакета</t>
+  </si>
+  <si>
+    <t>размерах посылки</t>
+  </si>
+  <si>
+    <t>размере пакета</t>
+  </si>
+  <si>
+    <t>размере посылки</t>
+  </si>
+  <si>
+    <t>размеру пакета</t>
+  </si>
+  <si>
+    <t>размеру посылки</t>
+  </si>
+  <si>
+    <t>размеров пакета</t>
+  </si>
+  <si>
+    <t>размеров посылки</t>
+  </si>
+  <si>
+    <t>размером пакета</t>
+  </si>
+  <si>
+    <t>размером посылки</t>
+  </si>
+  <si>
+    <t>обрывы пакетов</t>
+  </si>
+  <si>
+    <t>обрывы посылок</t>
+  </si>
+  <si>
+    <t>обрыв пакетов</t>
+  </si>
+  <si>
+    <t>обрыв посылок</t>
+  </si>
+  <si>
+    <t>обрыва пакетов</t>
+  </si>
+  <si>
+    <t>обрыва посылок</t>
+  </si>
+  <si>
+    <t>обрыве пакетов</t>
+  </si>
+  <si>
+    <t>обрыве посылок</t>
+  </si>
+  <si>
+    <t>обрыву пакетов</t>
+  </si>
+  <si>
+    <t>обрыву посылок</t>
+  </si>
+  <si>
+    <t>обрывом пакетов</t>
+  </si>
+  <si>
+    <t>обрывом посылок</t>
+  </si>
+  <si>
+    <t>обрывов пакетов</t>
+  </si>
+  <si>
+    <t>обрывов посылок</t>
+  </si>
+  <si>
+    <t>обрывам пакетов</t>
+  </si>
+  <si>
+    <t>обрывам посылок</t>
+  </si>
+  <si>
+    <t>обрывами пакетов</t>
+  </si>
+  <si>
+    <t>обрывами посылок</t>
+  </si>
+  <si>
+    <t>обрывах пакетов</t>
+  </si>
+  <si>
+    <t>обрывах посылок</t>
+  </si>
+  <si>
+    <t>к массиву</t>
+  </si>
+  <si>
+    <t>к хранилищу</t>
+  </si>
+  <si>
+    <t>хема задержки была сосредоточена в одном месте (в контроллере), и не должна</t>
+  </si>
+  <si>
+    <t>замысел задержки был сосредоточен в одном месте (в распорядителе), и не должен</t>
   </si>
 </sst>
 </file>
@@ -857,7 +1352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -869,6 +1364,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1239,7 +1737,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B99"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.36328125" customWidth="1"/>
@@ -1406,9 +1904,629 @@
         <v>225</v>
       </c>
     </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>400</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B9" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}"/>
@@ -1418,7 +2536,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A2:B23"/>
+  <dimension ref="A2:B26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.453125" customWidth="1"/>
@@ -1599,6 +2717,30 @@
       </c>
       <c r="B23" s="3" t="s">
         <v>235</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -2033,7 +3175,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -2102,6 +3244,22 @@
       </c>
       <c r="B8" t="s">
         <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B9" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="B10" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1A5538-49E9-4CF3-8443-1B047F22C6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189BA668-0244-4CDD-98AD-7D642CD8BE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="простые" sheetId="9" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Неизменные!$A$1:$B$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Составные!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Составные!$A$1:$B$105</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="421">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1255,6 +1255,60 @@
   </si>
   <si>
     <t>замысел задержки был сосредоточен в одном месте (в распорядителе), и не должен</t>
+  </si>
+  <si>
+    <t>Показан пакет</t>
+  </si>
+  <si>
+    <t>Показана послка</t>
+  </si>
+  <si>
+    <t>друг за другом пакетами</t>
+  </si>
+  <si>
+    <t>друг за другом посылками</t>
+  </si>
+  <si>
+    <t>Последовательные пакеты</t>
+  </si>
+  <si>
+    <t>Последовательные посылки</t>
+  </si>
+  <si>
+    <t>последовательного пакета</t>
+  </si>
+  <si>
+    <t>последовательной посылки</t>
+  </si>
+  <si>
+    <t>первый пакет</t>
+  </si>
+  <si>
+    <t>первая посылка</t>
+  </si>
+  <si>
+    <t>интерфейса передачи</t>
+  </si>
+  <si>
+    <t>средства передачи</t>
+  </si>
+  <si>
+    <t>сигналов интерфейса</t>
+  </si>
+  <si>
+    <t>звонков средства передачи</t>
+  </si>
+  <si>
+    <t>верхний нагрузочный резистор</t>
+  </si>
+  <si>
+    <t>верхнее нагрузочное сопротивление</t>
+  </si>
+  <si>
+    <t>повышенный джиттер тактов</t>
+  </si>
+  <si>
+    <t>повышенное частотное дрожжание шагов</t>
   </si>
 </sst>
 </file>
@@ -1737,7 +1791,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B99"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.36328125" customWidth="1"/>
@@ -1752,7 +1807,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -1768,7 +1823,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>122</v>
       </c>
@@ -1776,7 +1831,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -1784,7 +1839,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>70</v>
       </c>
@@ -1792,7 +1847,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>72</v>
       </c>
@@ -1800,7 +1855,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>134</v>
       </c>
@@ -1808,7 +1864,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>106</v>
       </c>
@@ -1816,7 +1872,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>148</v>
       </c>
@@ -1824,7 +1880,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>110</v>
       </c>
@@ -1832,7 +1888,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>158</v>
       </c>
@@ -1840,7 +1896,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>160</v>
       </c>
@@ -1848,7 +1904,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>170</v>
       </c>
@@ -1856,7 +1912,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>174</v>
       </c>
@@ -1864,7 +1920,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>178</v>
       </c>
@@ -1872,7 +1928,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>180</v>
       </c>
@@ -1880,7 +1936,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>220</v>
       </c>
@@ -1888,7 +1944,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>222</v>
       </c>
@@ -1896,7 +1952,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>224</v>
       </c>
@@ -1904,7 +1960,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>246</v>
       </c>
@@ -1912,7 +1968,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>248</v>
       </c>
@@ -1920,7 +1976,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>250</v>
       </c>
@@ -1928,7 +1984,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>252</v>
       </c>
@@ -1936,7 +1992,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>254</v>
       </c>
@@ -1944,7 +2000,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>256</v>
       </c>
@@ -1952,7 +2008,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>258</v>
       </c>
@@ -1960,7 +2016,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>260</v>
       </c>
@@ -1968,7 +2024,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>262</v>
       </c>
@@ -1976,7 +2032,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>264</v>
       </c>
@@ -1984,7 +2040,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>266</v>
       </c>
@@ -1992,7 +2048,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>268</v>
       </c>
@@ -2000,7 +2056,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>270</v>
       </c>
@@ -2008,7 +2064,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>272</v>
       </c>
@@ -2016,7 +2072,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>274</v>
       </c>
@@ -2024,7 +2080,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>276</v>
       </c>
@@ -2032,7 +2088,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>278</v>
       </c>
@@ -2040,7 +2096,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>280</v>
       </c>
@@ -2048,7 +2104,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>282</v>
       </c>
@@ -2056,7 +2112,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>284</v>
       </c>
@@ -2064,7 +2120,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>286</v>
       </c>
@@ -2072,7 +2128,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>288</v>
       </c>
@@ -2080,7 +2136,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>290</v>
       </c>
@@ -2088,7 +2144,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>292</v>
       </c>
@@ -2096,7 +2152,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>294</v>
       </c>
@@ -2104,7 +2160,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>296</v>
       </c>
@@ -2112,7 +2168,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>298</v>
       </c>
@@ -2120,7 +2176,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>300</v>
       </c>
@@ -2128,7 +2184,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>302</v>
       </c>
@@ -2136,7 +2192,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>304</v>
       </c>
@@ -2144,7 +2200,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>306</v>
       </c>
@@ -2152,7 +2208,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>308</v>
       </c>
@@ -2160,7 +2216,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>310</v>
       </c>
@@ -2168,7 +2224,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>312</v>
       </c>
@@ -2176,7 +2232,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>314</v>
       </c>
@@ -2184,7 +2240,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>316</v>
       </c>
@@ -2192,7 +2248,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>318</v>
       </c>
@@ -2200,7 +2256,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>320</v>
       </c>
@@ -2208,7 +2264,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>322</v>
       </c>
@@ -2216,7 +2272,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>324</v>
       </c>
@@ -2224,7 +2280,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>326</v>
       </c>
@@ -2232,7 +2288,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>328</v>
       </c>
@@ -2240,7 +2296,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>330</v>
       </c>
@@ -2248,7 +2304,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>332</v>
       </c>
@@ -2256,7 +2312,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>334</v>
       </c>
@@ -2264,7 +2320,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>336</v>
       </c>
@@ -2272,7 +2328,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>338</v>
       </c>
@@ -2280,7 +2336,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>340</v>
       </c>
@@ -2288,7 +2344,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>342</v>
       </c>
@@ -2296,7 +2352,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>344</v>
       </c>
@@ -2304,7 +2360,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>346</v>
       </c>
@@ -2312,7 +2368,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>348</v>
       </c>
@@ -2320,7 +2376,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>350</v>
       </c>
@@ -2328,7 +2384,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>352</v>
       </c>
@@ -2336,7 +2392,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>354</v>
       </c>
@@ -2344,7 +2400,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>356</v>
       </c>
@@ -2352,7 +2408,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>358</v>
       </c>
@@ -2360,7 +2416,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>360</v>
       </c>
@@ -2368,7 +2424,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>362</v>
       </c>
@@ -2376,7 +2432,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>363</v>
       </c>
@@ -2384,7 +2440,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>365</v>
       </c>
@@ -2392,7 +2448,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>367</v>
       </c>
@@ -2400,7 +2456,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>369</v>
       </c>
@@ -2408,7 +2464,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>371</v>
       </c>
@@ -2416,7 +2472,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>373</v>
       </c>
@@ -2424,7 +2480,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>375</v>
       </c>
@@ -2432,7 +2488,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>377</v>
       </c>
@@ -2440,7 +2496,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>379</v>
       </c>
@@ -2448,7 +2504,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>381</v>
       </c>
@@ -2456,7 +2512,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>383</v>
       </c>
@@ -2464,7 +2520,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>385</v>
       </c>
@@ -2472,7 +2528,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>387</v>
       </c>
@@ -2480,7 +2536,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>389</v>
       </c>
@@ -2488,7 +2544,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>391</v>
       </c>
@@ -2496,7 +2552,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>393</v>
       </c>
@@ -2504,7 +2560,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>395</v>
       </c>
@@ -2512,7 +2568,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>397</v>
       </c>
@@ -2520,7 +2576,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>399</v>
       </c>
@@ -2528,15 +2584,77 @@
         <v>400</v>
       </c>
     </row>
+    <row r="100" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B9" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}"/>
+  <autoFilter ref="A1:B105" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="сложную» формулу"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A2:B26"/>
+  <dimension ref="A2:B28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.453125" customWidth="1"/>
@@ -2741,6 +2859,22 @@
       </c>
       <c r="B26" s="3" t="s">
         <v>245</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -3175,7 +3309,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -3260,6 +3394,14 @@
       </c>
       <c r="B10" t="s">
         <v>402</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>405</v>
+      </c>
+      <c r="B11" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189BA668-0244-4CDD-98AD-7D642CD8BE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274782F7-5FF1-4920-8B4F-32EF93DDE4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="простые" sheetId="9" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -798,210 +798,6 @@
     <t xml:space="preserve">Каждый приказ </t>
   </si>
   <si>
-    <t>выдачи пакета</t>
-  </si>
-  <si>
-    <t>выдачи посылки</t>
-  </si>
-  <si>
-    <t>выдач пакета</t>
-  </si>
-  <si>
-    <t>выдач посылки</t>
-  </si>
-  <si>
-    <t>выдачей пакета</t>
-  </si>
-  <si>
-    <t>выдачей посылки</t>
-  </si>
-  <si>
-    <t>выдачам пакета</t>
-  </si>
-  <si>
-    <t>выдачам посылки</t>
-  </si>
-  <si>
-    <t>выдачу пакета</t>
-  </si>
-  <si>
-    <t>выдачу посылки</t>
-  </si>
-  <si>
-    <t>длина пакета</t>
-  </si>
-  <si>
-    <t>длина посылки</t>
-  </si>
-  <si>
-    <t>длин пакета</t>
-  </si>
-  <si>
-    <t>длин посылки</t>
-  </si>
-  <si>
-    <t>длинах пакета</t>
-  </si>
-  <si>
-    <t>длина хпосылки</t>
-  </si>
-  <si>
-    <t>длинам пакета</t>
-  </si>
-  <si>
-    <t>длинам посылки</t>
-  </si>
-  <si>
-    <t>длинами пакета</t>
-  </si>
-  <si>
-    <t>длинами посылки</t>
-  </si>
-  <si>
-    <t>длиной пакета</t>
-  </si>
-  <si>
-    <t>длиной посылки</t>
-  </si>
-  <si>
-    <t>длине пакета</t>
-  </si>
-  <si>
-    <t>длине посылки</t>
-  </si>
-  <si>
-    <t>длину пакета</t>
-  </si>
-  <si>
-    <t>длину посылки</t>
-  </si>
-  <si>
-    <t>длины пакета</t>
-  </si>
-  <si>
-    <t>длины посылки</t>
-  </si>
-  <si>
-    <t>порядком пакета</t>
-  </si>
-  <si>
-    <t>порядком посылки</t>
-  </si>
-  <si>
-    <t>порядков пакета</t>
-  </si>
-  <si>
-    <t>порядков посылки</t>
-  </si>
-  <si>
-    <t>порядка пакета</t>
-  </si>
-  <si>
-    <t>порядка посылки</t>
-  </si>
-  <si>
-    <t>порядке пакета</t>
-  </si>
-  <si>
-    <t>порядке посылки</t>
-  </si>
-  <si>
-    <t>порядку пакета</t>
-  </si>
-  <si>
-    <t>порядку посылки</t>
-  </si>
-  <si>
-    <t>порядки пакета</t>
-  </si>
-  <si>
-    <t>порядки посылки</t>
-  </si>
-  <si>
-    <t>порядкам пакета</t>
-  </si>
-  <si>
-    <t>порядкам посылки</t>
-  </si>
-  <si>
-    <t>порядками пакета</t>
-  </si>
-  <si>
-    <t>порядками посылки</t>
-  </si>
-  <si>
-    <t>порядках пакета</t>
-  </si>
-  <si>
-    <t>порядках посылки</t>
-  </si>
-  <si>
-    <t>порядок пакета</t>
-  </si>
-  <si>
-    <t>порядок посылки</t>
-  </si>
-  <si>
-    <t>длине пакетов</t>
-  </si>
-  <si>
-    <t>длине посылок</t>
-  </si>
-  <si>
-    <t>длина пакетов</t>
-  </si>
-  <si>
-    <t>длина посылок</t>
-  </si>
-  <si>
-    <t>длины пакетов</t>
-  </si>
-  <si>
-    <t>длины посылок</t>
-  </si>
-  <si>
-    <t>длину пакетов</t>
-  </si>
-  <si>
-    <t>длину посылок</t>
-  </si>
-  <si>
-    <t>длинам пакетов</t>
-  </si>
-  <si>
-    <t>длинам посылок</t>
-  </si>
-  <si>
-    <t>длинами пакетов</t>
-  </si>
-  <si>
-    <t>длинами посылок</t>
-  </si>
-  <si>
-    <t>длинах пакетов</t>
-  </si>
-  <si>
-    <t>длинах посылок</t>
-  </si>
-  <si>
-    <t>длин пакетов</t>
-  </si>
-  <si>
-    <t>длин посылок</t>
-  </si>
-  <si>
-    <t>длиной пакетов</t>
-  </si>
-  <si>
-    <t>длиной посылок</t>
-  </si>
-  <si>
-    <t>длинных пакетов</t>
-  </si>
-  <si>
-    <t>длинных посылок</t>
-  </si>
-  <si>
     <t>всему пакету</t>
   </si>
   <si>
@@ -1014,12 +810,6 @@
     <t>всей посылки</t>
   </si>
   <si>
-    <t>всех пакетов</t>
-  </si>
-  <si>
-    <t>всех посылок</t>
-  </si>
-  <si>
     <t>обрывающая пакет</t>
   </si>
   <si>
@@ -1128,123 +918,6 @@
     <t>прерывающего посылку</t>
   </si>
   <si>
-    <t>размер пакета</t>
-  </si>
-  <si>
-    <t>размер посылки</t>
-  </si>
-  <si>
-    <t>размера пакета</t>
-  </si>
-  <si>
-    <t>размеры пакета</t>
-  </si>
-  <si>
-    <t>размеры посылки</t>
-  </si>
-  <si>
-    <t>размерам пакета</t>
-  </si>
-  <si>
-    <t>размерам посылки</t>
-  </si>
-  <si>
-    <t>размерами пакета</t>
-  </si>
-  <si>
-    <t>размерами посылки</t>
-  </si>
-  <si>
-    <t>размерах пакета</t>
-  </si>
-  <si>
-    <t>размерах посылки</t>
-  </si>
-  <si>
-    <t>размере пакета</t>
-  </si>
-  <si>
-    <t>размере посылки</t>
-  </si>
-  <si>
-    <t>размеру пакета</t>
-  </si>
-  <si>
-    <t>размеру посылки</t>
-  </si>
-  <si>
-    <t>размеров пакета</t>
-  </si>
-  <si>
-    <t>размеров посылки</t>
-  </si>
-  <si>
-    <t>размером пакета</t>
-  </si>
-  <si>
-    <t>размером посылки</t>
-  </si>
-  <si>
-    <t>обрывы пакетов</t>
-  </si>
-  <si>
-    <t>обрывы посылок</t>
-  </si>
-  <si>
-    <t>обрыв пакетов</t>
-  </si>
-  <si>
-    <t>обрыв посылок</t>
-  </si>
-  <si>
-    <t>обрыва пакетов</t>
-  </si>
-  <si>
-    <t>обрыва посылок</t>
-  </si>
-  <si>
-    <t>обрыве пакетов</t>
-  </si>
-  <si>
-    <t>обрыве посылок</t>
-  </si>
-  <si>
-    <t>обрыву пакетов</t>
-  </si>
-  <si>
-    <t>обрыву посылок</t>
-  </si>
-  <si>
-    <t>обрывом пакетов</t>
-  </si>
-  <si>
-    <t>обрывом посылок</t>
-  </si>
-  <si>
-    <t>обрывов пакетов</t>
-  </si>
-  <si>
-    <t>обрывов посылок</t>
-  </si>
-  <si>
-    <t>обрывам пакетов</t>
-  </si>
-  <si>
-    <t>обрывам посылок</t>
-  </si>
-  <si>
-    <t>обрывами пакетов</t>
-  </si>
-  <si>
-    <t>обрывами посылок</t>
-  </si>
-  <si>
-    <t>обрывах пакетов</t>
-  </si>
-  <si>
-    <t>обрывах посылок</t>
-  </si>
-  <si>
     <t>к массиву</t>
   </si>
   <si>
@@ -1269,12 +942,6 @@
     <t>друг за другом посылками</t>
   </si>
   <si>
-    <t>Последовательные пакеты</t>
-  </si>
-  <si>
-    <t>Последовательные посылки</t>
-  </si>
-  <si>
     <t>последовательного пакета</t>
   </si>
   <si>
@@ -1309,6 +976,12 @@
   </si>
   <si>
     <t>повышенное частотное дрожжание шагов</t>
+  </si>
+  <si>
+    <t>вторая пакет</t>
+  </si>
+  <si>
+    <t>вторая посылка</t>
   </si>
 </sst>
 </file>
@@ -1791,7 +1464,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1801,836 +1473,615 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B27" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>64</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B46" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>70</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B48" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>158</v>
-      </c>
-      <c r="B13" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B49" s="10" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>416</v>
-      </c>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
@@ -2641,13 +2092,10 @@
       <c r="B108" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B105" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="сложную» формулу"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:B105" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B108">
+    <sortCondition ref="A1:A108"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2863,18 +2311,18 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>417</v>
+        <v>306</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>418</v>
+        <v>307</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>419</v>
+        <v>308</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>420</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3390,18 +2838,18 @@
     </row>
     <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>401</v>
+        <v>292</v>
       </c>
       <c r="B10" t="s">
-        <v>402</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>405</v>
+        <v>296</v>
       </c>
       <c r="B11" t="s">
-        <v>406</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274782F7-5FF1-4920-8B4F-32EF93DDE4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB84E5A-6738-40E5-8AC6-6C66AE3B8062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="простые" sheetId="9" r:id="rId1"/>
@@ -24,6 +24,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Неизменные!$A$1:$B$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Составные!$A$1:$B$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'составные важные'!$A$2:$B$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,6 +41,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1375,85 +1379,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56074B3-3BB9-4C57-99AF-4053FDDF42F2}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
@@ -1465,13 +1469,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
   <dimension ref="A1:B108"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="48.36328125" customWidth="1"/>
-    <col min="2" max="2" width="51.453125" customWidth="1"/>
+    <col min="1" max="1" width="48.3671875" customWidth="1"/>
+    <col min="2" max="2" width="51.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>134</v>
       </c>
@@ -1479,7 +1483,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1487,7 +1491,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>174</v>
       </c>
@@ -1495,7 +1499,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
         <v>170</v>
       </c>
@@ -1503,7 +1507,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
         <v>252</v>
       </c>
@@ -1511,7 +1515,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
         <v>250</v>
       </c>
@@ -1519,7 +1523,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3" t="s">
         <v>310</v>
       </c>
@@ -1527,7 +1531,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -1535,7 +1539,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3" t="s">
         <v>110</v>
       </c>
@@ -1543,7 +1547,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>122</v>
       </c>
@@ -1551,7 +1555,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
         <v>160</v>
       </c>
@@ -1559,7 +1563,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>148</v>
       </c>
@@ -1567,7 +1571,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3" t="s">
         <v>302</v>
       </c>
@@ -1575,7 +1579,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3" t="s">
         <v>290</v>
       </c>
@@ -1583,7 +1587,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3" t="s">
         <v>248</v>
       </c>
@@ -1591,7 +1595,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -1599,7 +1603,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3" t="s">
         <v>254</v>
       </c>
@@ -1607,7 +1611,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3" t="s">
         <v>266</v>
       </c>
@@ -1615,7 +1619,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3" t="s">
         <v>270</v>
       </c>
@@ -1623,7 +1627,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3" t="s">
         <v>268</v>
       </c>
@@ -1631,7 +1635,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3" t="s">
         <v>258</v>
       </c>
@@ -1639,7 +1643,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3" t="s">
         <v>256</v>
       </c>
@@ -1647,7 +1651,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3" t="s">
         <v>260</v>
       </c>
@@ -1655,7 +1659,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3" t="s">
         <v>262</v>
       </c>
@@ -1663,7 +1667,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3" t="s">
         <v>264</v>
       </c>
@@ -1671,7 +1675,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>72</v>
       </c>
@@ -1679,7 +1683,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>136</v>
       </c>
@@ -1687,7 +1691,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3" t="s">
         <v>246</v>
       </c>
@@ -1695,7 +1699,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3" t="s">
         <v>300</v>
       </c>
@@ -1703,7 +1707,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3" t="s">
         <v>178</v>
       </c>
@@ -1711,7 +1715,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3" t="s">
         <v>180</v>
       </c>
@@ -1719,7 +1723,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3" t="s">
         <v>294</v>
       </c>
@@ -1727,7 +1731,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3" t="s">
         <v>220</v>
       </c>
@@ -1735,7 +1739,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3" t="s">
         <v>298</v>
       </c>
@@ -1743,7 +1747,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3" t="s">
         <v>274</v>
       </c>
@@ -1751,7 +1755,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3" t="s">
         <v>272</v>
       </c>
@@ -1759,7 +1763,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3" t="s">
         <v>280</v>
       </c>
@@ -1767,7 +1771,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3" t="s">
         <v>288</v>
       </c>
@@ -1775,7 +1779,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3" t="s">
         <v>278</v>
       </c>
@@ -1783,7 +1787,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="3" t="s">
         <v>286</v>
       </c>
@@ -1791,7 +1795,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="3" t="s">
         <v>282</v>
       </c>
@@ -1799,7 +1803,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="3" t="s">
         <v>284</v>
       </c>
@@ -1807,7 +1811,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="3" t="s">
         <v>276</v>
       </c>
@@ -1815,7 +1819,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="3" t="s">
         <v>224</v>
       </c>
@@ -1823,7 +1827,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="3" t="s">
         <v>304</v>
       </c>
@@ -1831,7 +1835,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>64</v>
       </c>
@@ -1839,7 +1843,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>158</v>
       </c>
@@ -1847,7 +1851,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>70</v>
       </c>
@@ -1855,7 +1859,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="3" t="s">
         <v>222</v>
       </c>
@@ -1863,231 +1867,231 @@
         <v>223</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
     </row>
@@ -2103,205 +2107,205 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
   <dimension ref="A2:B28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="43.453125" customWidth="1"/>
-    <col min="2" max="2" width="49.81640625" customWidth="1"/>
+    <col min="1" max="1" width="43.47265625" customWidth="1"/>
+    <col min="2" max="2" width="49.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
         <v>62</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
         <v>76</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B18" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
         <v>114</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B24" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
         <v>142</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B25" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>150</v>
-      </c>
-      <c r="B10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>230</v>
-      </c>
-      <c r="B11" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>144</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>152</v>
-      </c>
-      <c r="B14" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>156</v>
-      </c>
-      <c r="B15" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3" t="s">
         <v>244</v>
       </c>
@@ -2309,23 +2313,27 @@
         <v>245</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3" t="s">
-        <v>306</v>
+        <v>182</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3" t="s">
-        <v>308</v>
+        <v>162</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>309</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:B29" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B28">
+    <sortCondition ref="A2:A28"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2333,12 +2341,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="54.36328125" customWidth="1"/>
+    <col min="1" max="1" width="54.3671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
         <v>96</v>
       </c>
@@ -2346,7 +2354,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="6" t="s">
         <v>98</v>
       </c>
@@ -2354,7 +2362,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -2362,7 +2370,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -2370,7 +2378,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="7" t="s">
         <v>104</v>
       </c>
@@ -2378,7 +2386,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>128</v>
       </c>
@@ -2386,7 +2394,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
@@ -2398,14 +2406,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="64.36328125" customWidth="1"/>
-    <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.81640625" customWidth="1"/>
+    <col min="1" max="1" width="64.3671875" customWidth="1"/>
+    <col min="2" max="2" width="54.7890625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2413,7 +2421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2421,7 +2429,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2429,7 +2437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2437,7 +2445,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -2445,7 +2453,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2453,7 +2461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2461,7 +2469,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2469,7 +2477,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -2477,7 +2485,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2485,7 +2493,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2493,7 +2501,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2501,7 +2509,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2509,7 +2517,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2517,7 +2525,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -2525,7 +2533,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2533,7 +2541,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -2541,7 +2549,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -2549,7 +2557,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -2557,7 +2565,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -2565,7 +2573,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,7 +2581,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -2581,7 +2589,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -2589,7 +2597,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -2597,7 +2605,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -2605,7 +2613,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -2613,7 +2621,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
         <v>60</v>
       </c>
@@ -2621,7 +2629,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" ht="17.7" x14ac:dyDescent="0.6">
       <c r="A28" s="1" t="s">
         <v>80</v>
       </c>
@@ -2629,7 +2637,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -2637,7 +2645,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
         <v>84</v>
       </c>
@@ -2645,7 +2653,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
         <v>86</v>
       </c>
@@ -2653,7 +2661,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3" t="s">
         <v>78</v>
       </c>
@@ -2661,7 +2669,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
         <v>88</v>
       </c>
@@ -2669,7 +2677,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
@@ -2677,7 +2685,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
         <v>92</v>
       </c>
@@ -2685,7 +2693,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
         <v>94</v>
       </c>
@@ -2693,7 +2701,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3" t="s">
         <v>108</v>
       </c>
@@ -2701,7 +2709,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -2709,7 +2717,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -2717,7 +2725,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>116</v>
       </c>
@@ -2725,7 +2733,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>120</v>
       </c>
@@ -2733,7 +2741,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>126</v>
       </c>
@@ -2741,7 +2749,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>154</v>
       </c>
@@ -2758,13 +2766,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="81.54296875" customWidth="1"/>
+    <col min="2" max="2" width="81.5234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>39</v>
       </c>
@@ -2772,7 +2780,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -2780,7 +2788,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -2788,7 +2796,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>146</v>
       </c>
@@ -2796,7 +2804,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>226</v>
       </c>
@@ -2804,7 +2812,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>228</v>
       </c>
@@ -2812,7 +2820,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>232</v>
       </c>
@@ -2820,7 +2828,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>236</v>
       </c>
@@ -2828,7 +2836,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>238</v>
       </c>
@@ -2836,7 +2844,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="11" t="s">
         <v>292</v>
       </c>
@@ -2844,7 +2852,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>296</v>
       </c>
@@ -2860,13 +2868,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="53.54296875" customWidth="1"/>
-    <col min="2" max="2" width="76.90625" customWidth="1"/>
+    <col min="1" max="1" width="53.5234375" customWidth="1"/>
+    <col min="2" max="2" width="76.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -2874,7 +2882,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>184</v>
       </c>
@@ -2882,7 +2890,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
         <v>186</v>
       </c>
@@ -2890,7 +2898,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -2898,7 +2906,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
         <v>190</v>
       </c>
@@ -2906,7 +2914,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
         <v>192</v>
       </c>
@@ -2914,7 +2922,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3" t="s">
         <v>194</v>
       </c>
@@ -2922,7 +2930,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3" t="s">
         <v>196</v>
       </c>
@@ -2930,7 +2938,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3" t="s">
         <v>198</v>
       </c>
@@ -2938,7 +2946,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3" t="s">
         <v>200</v>
       </c>
@@ -2946,7 +2954,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
         <v>202</v>
       </c>
@@ -2954,7 +2962,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3" t="s">
         <v>204</v>
       </c>
@@ -2962,7 +2970,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3" t="s">
         <v>206</v>
       </c>
@@ -2970,7 +2978,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3" t="s">
         <v>208</v>
       </c>
@@ -2978,7 +2986,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3" t="s">
         <v>210</v>
       </c>
@@ -2986,7 +2994,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3" t="s">
         <v>212</v>
       </c>
@@ -2994,7 +3002,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3" t="s">
         <v>214</v>
       </c>
@@ -3002,7 +3010,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>216</v>
       </c>
@@ -3010,7 +3018,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3" t="s">
         <v>218</v>
       </c>
@@ -3018,7 +3026,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>130</v>
       </c>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB84E5A-6738-40E5-8AC6-6C66AE3B8062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C6A93D-F504-4626-9633-765F26A14392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="простые" sheetId="9" r:id="rId1"/>
@@ -42,15 +42,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="339">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -715,15 +712,9 @@
     <t>получила шина</t>
   </si>
   <si>
-    <t>получило многопутевое средство обмена данными</t>
-  </si>
-  <si>
     <t>Шина однонаправленная</t>
   </si>
   <si>
-    <t>Многопутевое средство обмена данными однонаправленно</t>
-  </si>
-  <si>
     <t>проектируемой шины</t>
   </si>
   <si>
@@ -772,12 +763,6 @@
     <t>Два основные проводимые распорядителем действия</t>
   </si>
   <si>
-    <t>Двунаправленная шина</t>
-  </si>
-  <si>
-    <t>Двунаправленное многопутевое средство обмена данными</t>
-  </si>
-  <si>
     <t>первый важный элемент</t>
   </si>
   <si>
@@ -986,13 +971,106 @@
   </si>
   <si>
     <t>вторая посылка</t>
+  </si>
+  <si>
+    <t>Два основных проводимых распорядителем действия</t>
+  </si>
+  <si>
+    <t>шине адреса</t>
+  </si>
+  <si>
+    <t>шина адреса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Двунаправленная шина данных </t>
+  </si>
+  <si>
+    <t>количеством линий для передачи</t>
+  </si>
+  <si>
+    <t>количеством дорог для передачи</t>
+  </si>
+  <si>
+    <t>Обычно линия состоит</t>
+  </si>
+  <si>
+    <t>Обычно дорога состоит</t>
+  </si>
+  <si>
+    <t>Двунаправленное средство обмена данными</t>
+  </si>
+  <si>
+    <t>данной линии</t>
+  </si>
+  <si>
+    <t>данной дороги</t>
+  </si>
+  <si>
+    <t>рассматриваемой линии</t>
+  </si>
+  <si>
+    <t>рассматриваемой дороги</t>
+  </si>
+  <si>
+    <t>командная шина</t>
+  </si>
+  <si>
+    <t>приказное многопутевое средство передачи</t>
+  </si>
+  <si>
+    <t>внешней шины данных</t>
+  </si>
+  <si>
+    <t>даташиты компании</t>
+  </si>
+  <si>
+    <t>руководства по изделиям предприятия</t>
+  </si>
+  <si>
+    <t>одинаковую адресацию</t>
+  </si>
+  <si>
+    <t>одинаковые начальные и конечные пути сообщения</t>
+  </si>
+  <si>
+    <t>У внутренней шины данных</t>
+  </si>
+  <si>
+    <t>Шина команд</t>
+  </si>
+  <si>
+    <t>средство обмена приказов</t>
+  </si>
+  <si>
+    <t>средство обмена местоположениями</t>
+  </si>
+  <si>
+    <t>средству обмена местоположениями</t>
+  </si>
+  <si>
+    <t>однонаправленное средство обмена данными</t>
+  </si>
+  <si>
+    <t>получило средство обмена данными</t>
+  </si>
+  <si>
+    <t>У внутреннего средства обмена данными</t>
+  </si>
+  <si>
+    <t>внешнего средства обмена данными</t>
+  </si>
+  <si>
+    <t>на шине</t>
+  </si>
+  <si>
+    <t>на средстве обмена данными</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1062,6 +1140,19 @@
       <color rgb="FF212529"/>
       <name val="Open Sans"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF212529"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1083,7 +1174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1098,6 +1189,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1379,85 +1472,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56074B3-3BB9-4C57-99AF-4053FDDF42F2}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
@@ -1469,13 +1562,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
   <dimension ref="A1:B108"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.3671875" customWidth="1"/>
-    <col min="2" max="2" width="51.47265625" customWidth="1"/>
+    <col min="1" max="1" width="48.36328125" customWidth="1"/>
+    <col min="2" max="2" width="51.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>134</v>
       </c>
@@ -1483,7 +1576,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1491,7 +1584,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>174</v>
       </c>
@@ -1499,7 +1592,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>170</v>
       </c>
@@ -1507,31 +1600,31 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -1539,7 +1632,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>110</v>
       </c>
@@ -1547,7 +1640,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>122</v>
       </c>
@@ -1555,7 +1648,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>160</v>
       </c>
@@ -1563,7 +1656,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>148</v>
       </c>
@@ -1571,31 +1664,31 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -1603,79 +1696,79 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="3" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="3" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>72</v>
       </c>
@@ -1683,7 +1776,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>136</v>
       </c>
@@ -1691,23 +1784,23 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>178</v>
       </c>
@@ -1715,7 +1808,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>180</v>
       </c>
@@ -1723,119 +1816,119 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>220</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="3" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B43" s="3" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>64</v>
       </c>
@@ -1843,7 +1936,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>158</v>
       </c>
@@ -1851,7 +1944,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>70</v>
       </c>
@@ -1859,239 +1952,279 @@
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>221</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>309</v>
+      </c>
+      <c r="B50" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>310</v>
+      </c>
+      <c r="B51" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
     </row>
@@ -2106,14 +2239,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A2:B28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A2:B33"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.47265625" customWidth="1"/>
-    <col min="2" max="2" width="49.7890625" customWidth="1"/>
+    <col min="1" max="1" width="43.453125" customWidth="1"/>
+    <col min="2" max="2" width="49.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>150</v>
       </c>
@@ -2121,15 +2254,15 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>176</v>
       </c>
@@ -2137,15 +2270,15 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>172</v>
       </c>
@@ -2153,15 +2286,11 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>152</v>
       </c>
@@ -2169,7 +2298,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>144</v>
       </c>
@@ -2177,7 +2306,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>140</v>
       </c>
@@ -2185,7 +2314,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -2193,7 +2322,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>156</v>
       </c>
@@ -2201,7 +2330,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -2209,15 +2338,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B14" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>118</v>
       </c>
@@ -2225,23 +2354,23 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -2249,7 +2378,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>166</v>
       </c>
@@ -2257,7 +2386,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>124</v>
       </c>
@@ -2265,7 +2394,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>168</v>
       </c>
@@ -2273,7 +2402,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>132</v>
       </c>
@@ -2281,7 +2410,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>163</v>
       </c>
@@ -2289,7 +2418,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>114</v>
       </c>
@@ -2297,7 +2426,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>142</v>
       </c>
@@ -2305,15 +2434,15 @@
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>182</v>
       </c>
@@ -2321,12 +2450,52 @@
         <v>183</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>162</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -2341,12 +2510,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="54.3671875" customWidth="1"/>
+    <col min="1" max="1" width="54.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>96</v>
       </c>
@@ -2354,7 +2523,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>98</v>
       </c>
@@ -2362,7 +2531,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -2370,7 +2539,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -2378,7 +2547,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>104</v>
       </c>
@@ -2386,7 +2555,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>128</v>
       </c>
@@ -2394,7 +2563,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
@@ -2405,15 +2574,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
-  <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B44"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="64.3671875" customWidth="1"/>
-    <col min="2" max="2" width="54.7890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7890625" customWidth="1"/>
+    <col min="1" max="1" width="64.36328125" customWidth="1"/>
+    <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2421,7 +2590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2429,7 +2598,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2437,7 +2606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2445,7 +2614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -2453,7 +2622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2461,7 +2630,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2469,7 +2638,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2477,7 +2646,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -2485,7 +2654,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2493,7 +2662,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2501,7 +2670,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2509,7 +2678,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2517,7 +2686,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2525,7 +2694,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -2533,7 +2702,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2541,7 +2710,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -2549,7 +2718,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -2557,7 +2726,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -2565,7 +2734,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -2573,7 +2742,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -2581,7 +2750,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -2589,7 +2758,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -2597,7 +2766,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -2605,7 +2774,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -2613,7 +2782,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,7 +2790,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>60</v>
       </c>
@@ -2629,7 +2798,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="17.7" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>80</v>
       </c>
@@ -2637,7 +2806,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -2645,7 +2814,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>84</v>
       </c>
@@ -2653,7 +2822,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>86</v>
       </c>
@@ -2661,7 +2830,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>78</v>
       </c>
@@ -2669,7 +2838,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>88</v>
       </c>
@@ -2677,7 +2846,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
@@ -2685,7 +2854,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>92</v>
       </c>
@@ -2693,7 +2862,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>94</v>
       </c>
@@ -2701,7 +2870,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>108</v>
       </c>
@@ -2709,7 +2878,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -2717,7 +2886,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -2725,7 +2894,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>116</v>
       </c>
@@ -2733,7 +2902,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>120</v>
       </c>
@@ -2741,7 +2910,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>126</v>
       </c>
@@ -2749,12 +2918,20 @@
         <v>127</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>154</v>
       </c>
       <c r="B43" t="s">
         <v>155</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>236</v>
+      </c>
+      <c r="B44" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -2766,13 +2943,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="81.5234375" customWidth="1"/>
+    <col min="2" max="2" width="81.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>39</v>
       </c>
@@ -2780,7 +2957,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -2788,7 +2965,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -2796,7 +2973,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>146</v>
       </c>
@@ -2804,60 +2981,60 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>226</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B7" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>236</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>238</v>
-      </c>
-      <c r="B9" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>292</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>293</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>296</v>
-      </c>
-      <c r="B11" t="s">
-        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -2868,13 +3045,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="53.5234375" customWidth="1"/>
-    <col min="2" max="2" width="76.89453125" customWidth="1"/>
+    <col min="1" max="1" width="53.54296875" customWidth="1"/>
+    <col min="2" max="2" width="76.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -2882,7 +3059,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>184</v>
       </c>
@@ -2890,7 +3067,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>186</v>
       </c>
@@ -2898,7 +3075,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -2906,7 +3083,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>190</v>
       </c>
@@ -2914,7 +3091,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>192</v>
       </c>
@@ -2922,7 +3099,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>194</v>
       </c>
@@ -2930,7 +3107,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>196</v>
       </c>
@@ -2938,7 +3115,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>198</v>
       </c>
@@ -2946,7 +3123,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>200</v>
       </c>
@@ -2954,7 +3131,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>202</v>
       </c>
@@ -2962,7 +3139,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>204</v>
       </c>
@@ -2970,7 +3147,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>206</v>
       </c>
@@ -2978,7 +3155,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>208</v>
       </c>
@@ -2986,7 +3163,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>210</v>
       </c>
@@ -2994,7 +3171,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>212</v>
       </c>
@@ -3002,7 +3179,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>214</v>
       </c>
@@ -3010,7 +3187,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>216</v>
       </c>
@@ -3018,7 +3195,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>218</v>
       </c>
@@ -3026,7 +3203,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>130</v>
       </c>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C6A93D-F504-4626-9633-765F26A14392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451387AE-0D68-46DA-95CB-C6D39C752E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="простые" sheetId="9" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Неизменные!$A$1:$B$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Составные!$A$1:$B$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Составные!$A$1:$B$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'составные важные'!$A$2:$B$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,6 +41,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1472,85 +1475,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56074B3-3BB9-4C57-99AF-4053FDDF42F2}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
@@ -1562,13 +1565,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
   <dimension ref="A1:B108"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="48.36328125" customWidth="1"/>
-    <col min="2" max="2" width="51.453125" customWidth="1"/>
+    <col min="1" max="1" width="48.3671875" customWidth="1"/>
+    <col min="2" max="2" width="51.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>134</v>
       </c>
@@ -1576,7 +1579,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1584,7 +1587,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>174</v>
       </c>
@@ -1592,7 +1595,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
         <v>170</v>
       </c>
@@ -1600,7 +1603,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
         <v>248</v>
       </c>
@@ -1608,7 +1611,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
         <v>246</v>
       </c>
@@ -1616,7 +1619,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3" t="s">
         <v>306</v>
       </c>
@@ -1624,7 +1627,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -1632,7 +1635,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3" t="s">
         <v>110</v>
       </c>
@@ -1640,7 +1643,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>122</v>
       </c>
@@ -1648,588 +1651,588 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
         <v>148</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
         <v>68</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B20" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B22" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B26" s="3" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B27" s="3" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B28" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
         <v>72</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B30" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
         <v>136</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B32" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B36" s="3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B37" s="3" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B38" s="3" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B41" s="3" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B42" s="3" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B43" s="3" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B44" s="3" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B45" s="3" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B46" s="3" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="3" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B47" s="3" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B48" s="3" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B49" s="10" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="3" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B51" s="3" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
         <v>64</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B52" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
         <v>158</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B53" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
         <v>70</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B54" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="3" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>310</v>
+      </c>
+      <c r="B55" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B57" s="12" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
         <v>309</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B58" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>310</v>
-      </c>
-      <c r="B51" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B105" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}"/>
+  <autoFilter ref="A1:B109" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B108">
     <sortCondition ref="A1:A108"/>
   </sortState>
@@ -2240,13 +2243,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
   <dimension ref="A2:B33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="43.453125" customWidth="1"/>
-    <col min="2" max="2" width="49.81640625" customWidth="1"/>
+    <col min="1" max="1" width="43.47265625" customWidth="1"/>
+    <col min="2" max="2" width="49.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>150</v>
       </c>
@@ -2254,7 +2257,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>232</v>
       </c>
@@ -2262,7 +2265,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
         <v>176</v>
       </c>
@@ -2270,7 +2273,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
         <v>302</v>
       </c>
@@ -2278,7 +2281,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
         <v>172</v>
       </c>
@@ -2286,11 +2289,11 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>152</v>
       </c>
@@ -2298,7 +2301,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>144</v>
       </c>
@@ -2306,7 +2309,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>140</v>
       </c>
@@ -2314,7 +2317,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -2322,7 +2325,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>156</v>
       </c>
@@ -2330,7 +2333,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -2338,7 +2341,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>228</v>
       </c>
@@ -2346,7 +2349,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>118</v>
       </c>
@@ -2354,7 +2357,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3" t="s">
         <v>238</v>
       </c>
@@ -2362,7 +2365,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3" t="s">
         <v>304</v>
       </c>
@@ -2370,7 +2373,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -2378,7 +2381,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3" t="s">
         <v>166</v>
       </c>
@@ -2386,7 +2389,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>124</v>
       </c>
@@ -2394,7 +2397,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3" t="s">
         <v>168</v>
       </c>
@@ -2402,7 +2405,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>132</v>
       </c>
@@ -2410,7 +2413,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3" t="s">
         <v>163</v>
       </c>
@@ -2418,7 +2421,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>114</v>
       </c>
@@ -2426,7 +2429,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>142</v>
       </c>
@@ -2434,7 +2437,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3" t="s">
         <v>240</v>
       </c>
@@ -2442,7 +2445,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3" t="s">
         <v>182</v>
       </c>
@@ -2450,7 +2453,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3" t="s">
         <v>162</v>
       </c>
@@ -2458,7 +2461,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3" t="s">
         <v>311</v>
       </c>
@@ -2466,7 +2469,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3" t="s">
         <v>312</v>
       </c>
@@ -2474,7 +2477,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3" t="s">
         <v>314</v>
       </c>
@@ -2482,7 +2485,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="13" t="s">
         <v>323</v>
       </c>
@@ -2490,7 +2493,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3" t="s">
         <v>328</v>
       </c>
@@ -2510,12 +2513,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="54.36328125" customWidth="1"/>
+    <col min="1" max="1" width="54.3671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
         <v>96</v>
       </c>
@@ -2523,7 +2526,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="6" t="s">
         <v>98</v>
       </c>
@@ -2531,7 +2534,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -2539,7 +2542,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -2547,7 +2550,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="7" t="s">
         <v>104</v>
       </c>
@@ -2555,7 +2558,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>128</v>
       </c>
@@ -2563,7 +2566,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
@@ -2575,14 +2578,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
   <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="64.36328125" customWidth="1"/>
-    <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.81640625" customWidth="1"/>
+    <col min="1" max="1" width="64.3671875" customWidth="1"/>
+    <col min="2" max="2" width="54.7890625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2590,7 +2593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2598,7 +2601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2606,7 +2609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2614,7 +2617,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -2622,7 +2625,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2630,7 +2633,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2638,7 +2641,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2646,7 +2649,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -2654,7 +2657,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2662,7 +2665,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2670,7 +2673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2678,7 +2681,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2686,7 +2689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2694,7 +2697,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -2702,7 +2705,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2710,7 +2713,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -2718,7 +2721,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -2726,7 +2729,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -2734,7 +2737,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -2742,7 +2745,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -2750,7 +2753,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -2758,7 +2761,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -2766,7 +2769,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -2774,7 +2777,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -2782,7 +2785,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -2790,7 +2793,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
         <v>60</v>
       </c>
@@ -2798,7 +2801,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" ht="17.7" x14ac:dyDescent="0.6">
       <c r="A28" s="1" t="s">
         <v>80</v>
       </c>
@@ -2806,7 +2809,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -2814,7 +2817,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
         <v>84</v>
       </c>
@@ -2822,7 +2825,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
         <v>86</v>
       </c>
@@ -2830,7 +2833,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3" t="s">
         <v>78</v>
       </c>
@@ -2838,7 +2841,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
         <v>88</v>
       </c>
@@ -2846,7 +2849,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
@@ -2854,7 +2857,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
         <v>92</v>
       </c>
@@ -2862,7 +2865,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
         <v>94</v>
       </c>
@@ -2870,7 +2873,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3" t="s">
         <v>108</v>
       </c>
@@ -2878,7 +2881,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -2886,7 +2889,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -2894,7 +2897,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>116</v>
       </c>
@@ -2902,7 +2905,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>120</v>
       </c>
@@ -2910,7 +2913,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>126</v>
       </c>
@@ -2918,7 +2921,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>154</v>
       </c>
@@ -2926,7 +2929,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>236</v>
       </c>
@@ -2943,13 +2946,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="81.54296875" customWidth="1"/>
+    <col min="2" max="2" width="81.5234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>39</v>
       </c>
@@ -2957,7 +2960,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -2965,7 +2968,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -2973,7 +2976,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>146</v>
       </c>
@@ -2981,7 +2984,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>224</v>
       </c>
@@ -2989,7 +2992,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>226</v>
       </c>
@@ -2997,7 +3000,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>230</v>
       </c>
@@ -3005,7 +3008,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>234</v>
       </c>
@@ -3013,7 +3016,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>236</v>
       </c>
@@ -3021,7 +3024,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="11" t="s">
         <v>288</v>
       </c>
@@ -3029,7 +3032,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>292</v>
       </c>
@@ -3045,13 +3048,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="53.54296875" customWidth="1"/>
-    <col min="2" max="2" width="76.90625" customWidth="1"/>
+    <col min="1" max="1" width="53.5234375" customWidth="1"/>
+    <col min="2" max="2" width="76.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -3059,7 +3062,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>184</v>
       </c>
@@ -3067,7 +3070,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
         <v>186</v>
       </c>
@@ -3075,7 +3078,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -3083,7 +3086,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
         <v>190</v>
       </c>
@@ -3091,7 +3094,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
         <v>192</v>
       </c>
@@ -3099,7 +3102,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3" t="s">
         <v>194</v>
       </c>
@@ -3107,7 +3110,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3" t="s">
         <v>196</v>
       </c>
@@ -3115,7 +3118,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3" t="s">
         <v>198</v>
       </c>
@@ -3123,7 +3126,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3" t="s">
         <v>200</v>
       </c>
@@ -3131,7 +3134,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
         <v>202</v>
       </c>
@@ -3139,7 +3142,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3" t="s">
         <v>204</v>
       </c>
@@ -3147,7 +3150,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3" t="s">
         <v>206</v>
       </c>
@@ -3155,7 +3158,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3" t="s">
         <v>208</v>
       </c>
@@ -3163,7 +3166,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3" t="s">
         <v>210</v>
       </c>
@@ -3171,7 +3174,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3" t="s">
         <v>212</v>
       </c>
@@ -3179,7 +3182,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3" t="s">
         <v>214</v>
       </c>
@@ -3187,7 +3190,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>216</v>
       </c>
@@ -3195,7 +3198,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3" t="s">
         <v>218</v>
       </c>
@@ -3203,7 +3206,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>130</v>
       </c>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451387AE-0D68-46DA-95CB-C6D39C752E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFC6B4E-9561-4D55-907E-D2AEF2F14706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="простые" sheetId="9" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'составные важные'!$A$2:$B$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,15 +43,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="349">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1067,6 +1065,36 @@
   </si>
   <si>
     <t>на средстве обмена данными</t>
+  </si>
+  <si>
+    <t>наш проект платы, который</t>
+  </si>
+  <si>
+    <t>нашу разработку платы, которую</t>
+  </si>
+  <si>
+    <t>интегральных схем</t>
+  </si>
+  <si>
+    <t>встроенных изделий</t>
+  </si>
+  <si>
+    <t>шине данных</t>
+  </si>
+  <si>
+    <t>средству обмена данных</t>
+  </si>
+  <si>
+    <t>адреса/команд</t>
+  </si>
+  <si>
+    <t>местоположения/приказов</t>
+  </si>
+  <si>
+    <t>адреса/команды</t>
+  </si>
+  <si>
+    <t>местоположения/приказа</t>
   </si>
 </sst>
 </file>
@@ -1475,85 +1503,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56074B3-3BB9-4C57-99AF-4053FDDF42F2}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
@@ -1565,13 +1593,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
   <dimension ref="A1:B108"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.3671875" customWidth="1"/>
-    <col min="2" max="2" width="51.47265625" customWidth="1"/>
+    <col min="1" max="1" width="48.33203125" customWidth="1"/>
+    <col min="2" max="2" width="51.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>134</v>
       </c>
@@ -1579,7 +1607,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1587,7 +1615,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>174</v>
       </c>
@@ -1595,7 +1623,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>170</v>
       </c>
@@ -1603,7 +1631,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>248</v>
       </c>
@@ -1611,7 +1639,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>246</v>
       </c>
@@ -1619,7 +1647,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>306</v>
       </c>
@@ -1627,7 +1655,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -1635,7 +1663,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>110</v>
       </c>
@@ -1643,7 +1671,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>122</v>
       </c>
@@ -1651,7 +1679,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>317</v>
       </c>
@@ -1659,7 +1687,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>324</v>
       </c>
@@ -1667,7 +1695,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>160</v>
       </c>
@@ -1675,7 +1703,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>148</v>
       </c>
@@ -1683,7 +1711,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>298</v>
       </c>
@@ -1691,7 +1719,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>286</v>
       </c>
@@ -1699,7 +1727,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>244</v>
       </c>
@@ -1707,7 +1735,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>321</v>
       </c>
@@ -1715,7 +1743,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>337</v>
       </c>
@@ -1723,7 +1751,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>68</v>
       </c>
@@ -1731,7 +1759,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>250</v>
       </c>
@@ -1739,7 +1767,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>262</v>
       </c>
@@ -1747,7 +1775,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>266</v>
       </c>
@@ -1755,7 +1783,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>264</v>
       </c>
@@ -1763,7 +1791,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>254</v>
       </c>
@@ -1771,7 +1799,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>252</v>
       </c>
@@ -1779,7 +1807,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>256</v>
       </c>
@@ -1787,7 +1815,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>258</v>
       </c>
@@ -1795,7 +1823,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>260</v>
       </c>
@@ -1803,7 +1831,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -1811,7 +1839,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>326</v>
       </c>
@@ -1819,7 +1847,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>136</v>
       </c>
@@ -1827,7 +1855,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>242</v>
       </c>
@@ -1835,7 +1863,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>296</v>
       </c>
@@ -1843,7 +1871,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>178</v>
       </c>
@@ -1851,7 +1879,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>180</v>
       </c>
@@ -1859,7 +1887,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>290</v>
       </c>
@@ -1867,7 +1895,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>220</v>
       </c>
@@ -1875,7 +1903,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>294</v>
       </c>
@@ -1883,7 +1911,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>270</v>
       </c>
@@ -1891,7 +1919,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>268</v>
       </c>
@@ -1899,7 +1927,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>276</v>
       </c>
@@ -1907,7 +1935,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>284</v>
       </c>
@@ -1915,7 +1943,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>274</v>
       </c>
@@ -1923,7 +1951,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>282</v>
       </c>
@@ -1931,7 +1959,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>278</v>
       </c>
@@ -1939,7 +1967,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>280</v>
       </c>
@@ -1947,7 +1975,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>272</v>
       </c>
@@ -1955,7 +1983,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>222</v>
       </c>
@@ -1963,7 +1991,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>319</v>
       </c>
@@ -1971,7 +1999,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>300</v>
       </c>
@@ -1979,7 +2007,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>64</v>
       </c>
@@ -1987,7 +2015,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>158</v>
       </c>
@@ -1995,7 +2023,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>70</v>
       </c>
@@ -2003,7 +2031,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>310</v>
       </c>
@@ -2011,7 +2039,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>329</v>
       </c>
@@ -2019,7 +2047,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>221</v>
       </c>
@@ -2027,7 +2055,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>309</v>
       </c>
@@ -2035,199 +2063,207 @@
         <v>332</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B60" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
     </row>
@@ -2243,13 +2279,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
   <dimension ref="A2:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.47265625" customWidth="1"/>
-    <col min="2" max="2" width="49.7890625" customWidth="1"/>
+    <col min="1" max="1" width="43.44140625" customWidth="1"/>
+    <col min="2" max="2" width="49.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>150</v>
       </c>
@@ -2257,7 +2293,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>232</v>
       </c>
@@ -2265,7 +2301,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>176</v>
       </c>
@@ -2273,7 +2309,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>302</v>
       </c>
@@ -2281,7 +2317,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>172</v>
       </c>
@@ -2289,11 +2325,11 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>152</v>
       </c>
@@ -2301,7 +2337,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>144</v>
       </c>
@@ -2309,7 +2345,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>140</v>
       </c>
@@ -2317,7 +2353,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -2325,7 +2361,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>156</v>
       </c>
@@ -2333,7 +2369,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -2341,7 +2377,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>228</v>
       </c>
@@ -2349,7 +2385,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>118</v>
       </c>
@@ -2357,7 +2393,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>238</v>
       </c>
@@ -2365,7 +2401,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>304</v>
       </c>
@@ -2373,7 +2409,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -2381,7 +2417,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>166</v>
       </c>
@@ -2389,7 +2425,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>124</v>
       </c>
@@ -2397,7 +2433,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>168</v>
       </c>
@@ -2405,7 +2441,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>132</v>
       </c>
@@ -2413,7 +2449,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>163</v>
       </c>
@@ -2421,7 +2457,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>114</v>
       </c>
@@ -2429,7 +2465,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>142</v>
       </c>
@@ -2437,7 +2473,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>240</v>
       </c>
@@ -2445,7 +2481,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>182</v>
       </c>
@@ -2453,7 +2489,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>162</v>
       </c>
@@ -2461,7 +2497,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>311</v>
       </c>
@@ -2469,7 +2505,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>312</v>
       </c>
@@ -2477,7 +2513,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>314</v>
       </c>
@@ -2485,7 +2521,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>323</v>
       </c>
@@ -2493,7 +2529,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>328</v>
       </c>
@@ -2513,12 +2549,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="54.3671875" customWidth="1"/>
+    <col min="1" max="1" width="54.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>96</v>
       </c>
@@ -2526,7 +2562,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>98</v>
       </c>
@@ -2534,7 +2570,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -2542,7 +2578,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -2550,7 +2586,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>104</v>
       </c>
@@ -2558,7 +2594,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>128</v>
       </c>
@@ -2566,7 +2602,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
@@ -2577,15 +2613,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
-  <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B47"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="64.3671875" customWidth="1"/>
-    <col min="2" max="2" width="54.7890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7890625" customWidth="1"/>
+    <col min="1" max="1" width="64.33203125" customWidth="1"/>
+    <col min="2" max="2" width="54.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2593,7 +2629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2601,7 +2637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2609,7 +2645,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2617,7 +2653,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -2625,7 +2661,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2633,7 +2669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2641,7 +2677,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2649,7 +2685,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -2657,7 +2693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2665,7 +2701,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2673,7 +2709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2681,7 +2717,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2689,7 +2725,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2697,7 +2733,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -2705,7 +2741,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2713,7 +2749,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -2721,7 +2757,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -2729,7 +2765,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -2737,7 +2773,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -2745,7 +2781,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -2753,7 +2789,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -2761,7 +2797,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -2769,7 +2805,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -2777,7 +2813,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -2785,7 +2821,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -2793,7 +2829,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>60</v>
       </c>
@@ -2801,7 +2837,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="17.7" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>80</v>
       </c>
@@ -2809,7 +2845,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -2817,7 +2853,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>84</v>
       </c>
@@ -2825,7 +2861,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>86</v>
       </c>
@@ -2833,7 +2869,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>78</v>
       </c>
@@ -2841,7 +2877,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>88</v>
       </c>
@@ -2849,7 +2885,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
@@ -2857,7 +2893,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>92</v>
       </c>
@@ -2865,7 +2901,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>94</v>
       </c>
@@ -2873,7 +2909,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>108</v>
       </c>
@@ -2881,7 +2917,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -2889,7 +2925,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -2897,7 +2933,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>116</v>
       </c>
@@ -2905,7 +2941,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>120</v>
       </c>
@@ -2913,7 +2949,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>126</v>
       </c>
@@ -2921,7 +2957,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>154</v>
       </c>
@@ -2929,12 +2965,36 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>236</v>
       </c>
       <c r="B44" t="s">
         <v>308</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>339</v>
+      </c>
+      <c r="B45" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>345</v>
+      </c>
+      <c r="B46" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>347</v>
+      </c>
+      <c r="B47" t="s">
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -2946,13 +3006,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="81.5234375" customWidth="1"/>
+    <col min="2" max="2" width="81.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>39</v>
       </c>
@@ -2960,7 +3020,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -2968,7 +3028,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -2976,7 +3036,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>146</v>
       </c>
@@ -2984,7 +3044,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>224</v>
       </c>
@@ -2992,7 +3052,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>226</v>
       </c>
@@ -3000,7 +3060,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>230</v>
       </c>
@@ -3008,7 +3068,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>234</v>
       </c>
@@ -3016,7 +3076,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>236</v>
       </c>
@@ -3024,7 +3084,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>288</v>
       </c>
@@ -3032,7 +3092,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>292</v>
       </c>
@@ -3048,13 +3108,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="53.5234375" customWidth="1"/>
-    <col min="2" max="2" width="76.89453125" customWidth="1"/>
+    <col min="1" max="1" width="53.5546875" customWidth="1"/>
+    <col min="2" max="2" width="76.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -3062,7 +3122,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>184</v>
       </c>
@@ -3070,7 +3130,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>186</v>
       </c>
@@ -3078,7 +3138,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -3086,7 +3146,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>190</v>
       </c>
@@ -3094,7 +3154,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>192</v>
       </c>
@@ -3102,7 +3162,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>194</v>
       </c>
@@ -3110,7 +3170,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>196</v>
       </c>
@@ -3118,7 +3178,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>198</v>
       </c>
@@ -3126,7 +3186,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>200</v>
       </c>
@@ -3134,7 +3194,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>202</v>
       </c>
@@ -3142,7 +3202,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>204</v>
       </c>
@@ -3150,7 +3210,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>206</v>
       </c>
@@ -3158,7 +3218,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>208</v>
       </c>
@@ -3166,7 +3226,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>210</v>
       </c>
@@ -3174,7 +3234,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>212</v>
       </c>
@@ -3182,7 +3242,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>214</v>
       </c>
@@ -3190,7 +3250,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>216</v>
       </c>
@@ -3198,7 +3258,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>218</v>
       </c>
@@ -3206,7 +3266,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>130</v>
       </c>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFC6B4E-9561-4D55-907E-D2AEF2F14706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42A8814-12B5-4816-8107-1205D00C4E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="простые" sheetId="9" r:id="rId1"/>
@@ -27,7 +27,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'составные важные'!$A$2:$B$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,12 +42,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="353">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1095,6 +1097,18 @@
   </si>
   <si>
     <t>местоположения/приказа</t>
+  </si>
+  <si>
+    <t>Спецификация информации</t>
+  </si>
+  <si>
+    <t>свод требований сведений</t>
+  </si>
+  <si>
+    <t>шине адреса/команд</t>
+  </si>
+  <si>
+    <t>средству обмена местоположений/приказов</t>
   </si>
 </sst>
 </file>
@@ -1503,85 +1517,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56074B3-3BB9-4C57-99AF-4053FDDF42F2}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
@@ -1593,13 +1607,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
   <dimension ref="A1:B108"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.33203125" customWidth="1"/>
-    <col min="2" max="2" width="51.44140625" customWidth="1"/>
+    <col min="1" max="1" width="48.36328125" customWidth="1"/>
+    <col min="2" max="2" width="51.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>134</v>
       </c>
@@ -1607,7 +1621,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1615,7 +1629,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>174</v>
       </c>
@@ -1623,7 +1637,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>170</v>
       </c>
@@ -1631,7 +1645,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>248</v>
       </c>
@@ -1639,7 +1653,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>246</v>
       </c>
@@ -1647,7 +1661,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>306</v>
       </c>
@@ -1655,7 +1669,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -1663,7 +1677,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>110</v>
       </c>
@@ -1671,7 +1685,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>122</v>
       </c>
@@ -1679,7 +1693,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>317</v>
       </c>
@@ -1687,7 +1701,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>324</v>
       </c>
@@ -1695,7 +1709,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>160</v>
       </c>
@@ -1703,7 +1717,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>148</v>
       </c>
@@ -1711,7 +1725,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>298</v>
       </c>
@@ -1719,7 +1733,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>286</v>
       </c>
@@ -1727,7 +1741,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>244</v>
       </c>
@@ -1735,7 +1749,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>321</v>
       </c>
@@ -1743,7 +1757,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>337</v>
       </c>
@@ -1751,7 +1765,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>68</v>
       </c>
@@ -1759,7 +1773,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>250</v>
       </c>
@@ -1767,7 +1781,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>262</v>
       </c>
@@ -1775,7 +1789,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>266</v>
       </c>
@@ -1783,7 +1797,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>264</v>
       </c>
@@ -1791,7 +1805,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>254</v>
       </c>
@@ -1799,7 +1813,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>252</v>
       </c>
@@ -1807,7 +1821,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>256</v>
       </c>
@@ -1815,7 +1829,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>258</v>
       </c>
@@ -1823,7 +1837,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>260</v>
       </c>
@@ -1831,7 +1845,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -1839,7 +1853,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>326</v>
       </c>
@@ -1847,7 +1861,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>136</v>
       </c>
@@ -1855,7 +1869,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>242</v>
       </c>
@@ -1863,7 +1877,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>296</v>
       </c>
@@ -1871,7 +1885,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>178</v>
       </c>
@@ -1879,7 +1893,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>180</v>
       </c>
@@ -1887,7 +1901,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>290</v>
       </c>
@@ -1895,7 +1909,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>220</v>
       </c>
@@ -1903,7 +1917,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>294</v>
       </c>
@@ -1911,7 +1925,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>270</v>
       </c>
@@ -1919,7 +1933,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>268</v>
       </c>
@@ -1927,7 +1941,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>276</v>
       </c>
@@ -1935,7 +1949,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>284</v>
       </c>
@@ -1943,7 +1957,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>274</v>
       </c>
@@ -1951,7 +1965,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>282</v>
       </c>
@@ -1959,7 +1973,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>278</v>
       </c>
@@ -1967,7 +1981,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>280</v>
       </c>
@@ -1975,7 +1989,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>272</v>
       </c>
@@ -1983,7 +1997,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>222</v>
       </c>
@@ -1991,7 +2005,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>319</v>
       </c>
@@ -1999,7 +2013,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>300</v>
       </c>
@@ -2007,7 +2021,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>64</v>
       </c>
@@ -2015,7 +2029,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>158</v>
       </c>
@@ -2023,7 +2037,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>70</v>
       </c>
@@ -2031,7 +2045,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>310</v>
       </c>
@@ -2039,7 +2053,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>329</v>
       </c>
@@ -2047,7 +2061,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>221</v>
       </c>
@@ -2055,7 +2069,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>309</v>
       </c>
@@ -2063,7 +2077,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>341</v>
       </c>
@@ -2071,7 +2085,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>343</v>
       </c>
@@ -2079,191 +2093,191 @@
         <v>344</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
     </row>
@@ -2278,14 +2292,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A2:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:B34"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.44140625" customWidth="1"/>
-    <col min="2" max="2" width="49.77734375" customWidth="1"/>
+    <col min="1" max="1" width="43.453125" customWidth="1"/>
+    <col min="2" max="2" width="49.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>150</v>
       </c>
@@ -2293,7 +2307,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>232</v>
       </c>
@@ -2301,7 +2315,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>176</v>
       </c>
@@ -2309,7 +2323,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>302</v>
       </c>
@@ -2317,7 +2331,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>172</v>
       </c>
@@ -2325,11 +2339,11 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>152</v>
       </c>
@@ -2337,7 +2351,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>144</v>
       </c>
@@ -2345,7 +2359,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>140</v>
       </c>
@@ -2353,7 +2367,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -2361,7 +2375,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>156</v>
       </c>
@@ -2369,7 +2383,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -2377,7 +2391,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>228</v>
       </c>
@@ -2385,7 +2399,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>118</v>
       </c>
@@ -2393,7 +2407,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>238</v>
       </c>
@@ -2401,7 +2415,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>304</v>
       </c>
@@ -2409,7 +2423,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -2417,7 +2431,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>166</v>
       </c>
@@ -2425,7 +2439,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>124</v>
       </c>
@@ -2433,7 +2447,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>168</v>
       </c>
@@ -2441,7 +2455,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>132</v>
       </c>
@@ -2449,7 +2463,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>163</v>
       </c>
@@ -2457,7 +2471,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>114</v>
       </c>
@@ -2465,7 +2479,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>142</v>
       </c>
@@ -2473,7 +2487,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>240</v>
       </c>
@@ -2481,7 +2495,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>182</v>
       </c>
@@ -2489,7 +2503,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>162</v>
       </c>
@@ -2497,7 +2511,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>311</v>
       </c>
@@ -2505,7 +2519,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>312</v>
       </c>
@@ -2513,7 +2527,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>314</v>
       </c>
@@ -2521,7 +2535,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="13" t="s">
         <v>323</v>
       </c>
@@ -2529,12 +2543,20 @@
         <v>336</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>328</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>335</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -2549,12 +2571,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="54.33203125" customWidth="1"/>
+    <col min="1" max="1" width="54.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>96</v>
       </c>
@@ -2562,7 +2584,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>98</v>
       </c>
@@ -2570,7 +2592,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -2578,7 +2600,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -2586,7 +2608,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>104</v>
       </c>
@@ -2594,7 +2616,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>128</v>
       </c>
@@ -2602,7 +2624,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
@@ -2614,14 +2636,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="64.33203125" customWidth="1"/>
-    <col min="2" max="2" width="54.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="1" max="1" width="64.36328125" customWidth="1"/>
+    <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2629,7 +2651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2637,7 +2659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2645,7 +2667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2653,7 +2675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -2661,7 +2683,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2669,7 +2691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2677,7 +2699,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2685,7 +2707,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -2693,7 +2715,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2701,7 +2723,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2709,7 +2731,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2717,7 +2739,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2725,7 +2747,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2733,7 +2755,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -2741,7 +2763,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2749,7 +2771,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -2757,7 +2779,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -2765,7 +2787,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -2773,7 +2795,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -2781,7 +2803,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -2789,7 +2811,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -2797,7 +2819,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -2805,7 +2827,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -2813,7 +2835,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -2821,7 +2843,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -2829,7 +2851,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>60</v>
       </c>
@@ -2837,7 +2859,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>80</v>
       </c>
@@ -2845,7 +2867,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -2853,7 +2875,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>84</v>
       </c>
@@ -2861,7 +2883,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>86</v>
       </c>
@@ -2869,7 +2891,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>78</v>
       </c>
@@ -2877,7 +2899,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>88</v>
       </c>
@@ -2885,7 +2907,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
@@ -2893,7 +2915,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>92</v>
       </c>
@@ -2901,7 +2923,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>94</v>
       </c>
@@ -2909,7 +2931,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>108</v>
       </c>
@@ -2917,7 +2939,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -2925,7 +2947,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -2933,7 +2955,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>116</v>
       </c>
@@ -2941,7 +2963,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>120</v>
       </c>
@@ -2949,7 +2971,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>126</v>
       </c>
@@ -2957,7 +2979,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>154</v>
       </c>
@@ -2965,7 +2987,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>236</v>
       </c>
@@ -2973,7 +2995,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>339</v>
       </c>
@@ -2981,7 +3003,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>345</v>
       </c>
@@ -2989,7 +3011,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>347</v>
       </c>
@@ -3006,13 +3028,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="81.5546875" customWidth="1"/>
+    <col min="2" max="2" width="81.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>39</v>
       </c>
@@ -3020,7 +3042,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -3028,7 +3050,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -3036,7 +3058,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>146</v>
       </c>
@@ -3044,7 +3066,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>224</v>
       </c>
@@ -3052,7 +3074,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>226</v>
       </c>
@@ -3060,7 +3082,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>230</v>
       </c>
@@ -3068,7 +3090,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>234</v>
       </c>
@@ -3076,7 +3098,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>236</v>
       </c>
@@ -3084,7 +3106,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>288</v>
       </c>
@@ -3092,7 +3114,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>292</v>
       </c>
@@ -3108,13 +3130,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="53.5546875" customWidth="1"/>
-    <col min="2" max="2" width="76.88671875" customWidth="1"/>
+    <col min="1" max="1" width="53.54296875" customWidth="1"/>
+    <col min="2" max="2" width="76.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -3122,7 +3144,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>184</v>
       </c>
@@ -3130,7 +3152,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>186</v>
       </c>
@@ -3138,7 +3160,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -3146,7 +3168,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>190</v>
       </c>
@@ -3154,7 +3176,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>192</v>
       </c>
@@ -3162,7 +3184,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>194</v>
       </c>
@@ -3170,7 +3192,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>196</v>
       </c>
@@ -3178,7 +3200,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>198</v>
       </c>
@@ -3186,7 +3208,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>200</v>
       </c>
@@ -3194,7 +3216,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>202</v>
       </c>
@@ -3202,7 +3224,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>204</v>
       </c>
@@ -3210,7 +3232,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>206</v>
       </c>
@@ -3218,7 +3240,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>208</v>
       </c>
@@ -3226,7 +3248,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>210</v>
       </c>
@@ -3234,7 +3256,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>212</v>
       </c>
@@ -3242,7 +3264,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>214</v>
       </c>
@@ -3250,7 +3272,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>216</v>
       </c>
@@ -3258,7 +3280,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>218</v>
       </c>
@@ -3266,7 +3288,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>130</v>
       </c>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -5,26 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42A8814-12B5-4816-8107-1205D00C4E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41421009-8AAD-47F6-A0B6-A6C6D40E8BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="простые" sheetId="9" r:id="rId1"/>
-    <sheet name="Составные" sheetId="2" r:id="rId2"/>
-    <sheet name="составные важные" sheetId="6" r:id="rId3"/>
-    <sheet name="Вездесущие" sheetId="3" r:id="rId4"/>
-    <sheet name="Неизменные" sheetId="5" r:id="rId5"/>
-    <sheet name="Неизменные_короткие" sheetId="8" r:id="rId6"/>
-    <sheet name="Неизменные_длинные" sheetId="7" r:id="rId7"/>
+    <sheet name="Составные" sheetId="2" r:id="rId1"/>
+    <sheet name="составные важные" sheetId="6" r:id="rId2"/>
+    <sheet name="Вездесущие" sheetId="3" r:id="rId3"/>
+    <sheet name="Неизменные" sheetId="5" r:id="rId4"/>
+    <sheet name="Неизменные_короткие" sheetId="8" r:id="rId5"/>
+    <sheet name="Неизменные_длинные" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Неизменные!$A$1:$B$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Составные!$A$1:$B$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'составные важные'!$A$2:$B$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Неизменные!$A$1:$B$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные!$A$1:$B$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'составные важные'!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -223,9 +222,6 @@
     <t>схема передачи данных, получающая</t>
   </si>
   <si>
-    <t>схема передачи данных, получающий</t>
-  </si>
-  <si>
     <t>в материалах</t>
   </si>
   <si>
@@ -247,9 +243,6 @@
     <t>сложную» формулу</t>
   </si>
   <si>
-    <t>сложный» формулу</t>
-  </si>
-  <si>
     <t>Уилера дала бы большую точность</t>
   </si>
   <si>
@@ -337,9 +330,6 @@
     <t>амплитуду сигнала, которая составила</t>
   </si>
   <si>
-    <t>амплитуду сигнала, который составил</t>
-  </si>
-  <si>
     <t>емко ст</t>
   </si>
   <si>
@@ -355,9 +345,6 @@
     <t>те стов</t>
   </si>
   <si>
-    <t>тестов</t>
-  </si>
-  <si>
     <t>используемый для закорачивания инструмент</t>
   </si>
   <si>
@@ -1109,6 +1096,18 @@
   </si>
   <si>
     <t>средству обмена местоположений/приказов</t>
+  </si>
+  <si>
+    <t>проверок</t>
+  </si>
+  <si>
+    <t>сложный» рассчёт</t>
+  </si>
+  <si>
+    <t>размах звонка, который составил</t>
+  </si>
+  <si>
+    <t>порядок передачи данных, получающий</t>
   </si>
 </sst>
 </file>
@@ -1515,769 +1514,679 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56074B3-3BB9-4C57-99AF-4053FDDF42F2}">
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
   <dimension ref="A1:B108"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="48.36328125" customWidth="1"/>
-    <col min="2" max="2" width="51.453125" customWidth="1"/>
+    <col min="1" max="1" width="48.3671875" customWidth="1"/>
+    <col min="2" max="2" width="51.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
         <v>58</v>
       </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>154</v>
+      </c>
+      <c r="B53" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>68</v>
+      </c>
+      <c r="B54" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
         <v>306</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>106</v>
-      </c>
-      <c r="B8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>122</v>
-      </c>
-      <c r="B10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="B55" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="3" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>148</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
+      <c r="B56" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>305</v>
+      </c>
+      <c r="B58" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B59" s="3" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>136</v>
-      </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>64</v>
-      </c>
-      <c r="B52" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>158</v>
-      </c>
-      <c r="B53" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>70</v>
-      </c>
-      <c r="B54" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>310</v>
-      </c>
-      <c r="B55" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>309</v>
-      </c>
-      <c r="B58" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B60" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
     </row>
@@ -2290,341 +2199,342 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A2:B34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="43.453125" customWidth="1"/>
-    <col min="2" max="2" width="49.81640625" customWidth="1"/>
+    <col min="1" max="1" width="43.47265625" customWidth="1"/>
+    <col min="2" max="2" width="49.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
-        <v>232</v>
+        <v>172</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
-        <v>176</v>
+        <v>298</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
-        <v>302</v>
+        <v>168</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="13" t="s">
+        <v>319</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
         <v>152</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B13" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B12" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="B14" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>224</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3" t="s">
-        <v>238</v>
+        <v>310</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3" t="s">
-        <v>166</v>
+        <v>300</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B25" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3" t="s">
-        <v>182</v>
+        <v>324</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3" t="s">
-        <v>311</v>
+        <v>236</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3" t="s">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3" t="s">
-        <v>314</v>
+        <v>178</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="13" t="s">
-        <v>323</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>352</v>
-      </c>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:B29" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B28">
-    <sortCondition ref="A2:A28"/>
+  <autoFilter ref="A1:B28" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B34">
+    <sortCondition ref="A2:A34"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="54.36328125" customWidth="1"/>
+    <col min="1" max="1" width="54.3671875" customWidth="1"/>
+    <col min="2" max="2" width="46.734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="6" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="B3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="5" spans="1:2" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
@@ -2633,17 +2543,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="64.36328125" customWidth="1"/>
-    <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.81640625" customWidth="1"/>
+    <col min="1" max="1" width="64.3671875" customWidth="1"/>
+    <col min="2" max="2" width="54.7890625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2651,7 +2561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2659,7 +2569,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2667,7 +2577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2675,7 +2585,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -2683,7 +2593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2691,7 +2601,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2699,7 +2609,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2707,7 +2617,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -2715,7 +2625,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2723,7 +2633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2731,7 +2641,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2739,7 +2649,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2747,7 +2657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2755,7 +2665,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -2763,7 +2673,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2771,7 +2681,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -2779,7 +2689,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -2787,7 +2697,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -2795,7 +2705,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -2803,7 +2713,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -2811,7 +2721,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -2819,7 +2729,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -2827,7 +2737,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -2835,7 +2745,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -2843,180 +2753,180 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:2" ht="17.7" x14ac:dyDescent="0.6">
       <c r="A28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B29" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B33" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B35" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="B36" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
         <v>116</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>120</v>
-      </c>
-      <c r="B41" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B43" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B44" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B45" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -3025,16 +2935,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="81.54296875" customWidth="1"/>
+    <col min="2" max="2" width="81.5234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>39</v>
       </c>
@@ -3042,7 +2952,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -3050,76 +2960,76 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
         <v>226</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
         <v>230</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>234</v>
-      </c>
-      <c r="B8" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="B10" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
         <v>288</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>289</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>292</v>
-      </c>
-      <c r="B11" t="s">
-        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -3127,16 +3037,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="53.54296875" customWidth="1"/>
-    <col min="2" max="2" width="76.90625" customWidth="1"/>
+    <col min="1" max="1" width="53.5234375" customWidth="1"/>
+    <col min="2" max="2" width="76.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -3144,156 +3054,156 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B18" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41421009-8AAD-47F6-A0B6-A6C6D40E8BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BED4282-DEA5-4196-97A2-75BEC48CBE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="365">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1108,6 +1108,42 @@
   </si>
   <si>
     <t>порядок передачи данных, получающий</t>
+  </si>
+  <si>
+    <t>шумы на линии</t>
+  </si>
+  <si>
+    <t>шумы на пути</t>
+  </si>
+  <si>
+    <t>высокоскоростной цифровой аппаратуры</t>
+  </si>
+  <si>
+    <t>высоко-скоростных числовых приборов</t>
+  </si>
+  <si>
+    <t>Цифровое аудио невосприимчиво</t>
+  </si>
+  <si>
+    <t>числовой звук невосприимчив</t>
+  </si>
+  <si>
+    <t>аналоговой форме</t>
+  </si>
+  <si>
+    <t>аналоговом виде</t>
+  </si>
+  <si>
+    <t>аналоговой формы</t>
+  </si>
+  <si>
+    <t>аналогового вида</t>
+  </si>
+  <si>
+    <t>Цифровое аудио</t>
+  </si>
+  <si>
+    <t>числовой звук</t>
   </si>
 </sst>
 </file>
@@ -1516,13 +1552,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
   <dimension ref="A1:B108"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.3671875" customWidth="1"/>
-    <col min="2" max="2" width="51.47265625" customWidth="1"/>
+    <col min="1" max="1" width="48.36328125" customWidth="1"/>
+    <col min="2" max="2" width="51.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>130</v>
       </c>
@@ -1530,7 +1566,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -1538,7 +1574,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>170</v>
       </c>
@@ -1546,7 +1582,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>166</v>
       </c>
@@ -1554,7 +1590,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>244</v>
       </c>
@@ -1562,7 +1598,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>242</v>
       </c>
@@ -1570,7 +1606,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>302</v>
       </c>
@@ -1578,7 +1614,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -1586,7 +1622,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>106</v>
       </c>
@@ -1594,7 +1630,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -1602,7 +1638,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>313</v>
       </c>
@@ -1610,7 +1646,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>320</v>
       </c>
@@ -1618,7 +1654,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>156</v>
       </c>
@@ -1626,7 +1662,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>144</v>
       </c>
@@ -1634,7 +1670,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>294</v>
       </c>
@@ -1642,7 +1678,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>282</v>
       </c>
@@ -1650,7 +1686,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>240</v>
       </c>
@@ -1658,7 +1694,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>317</v>
       </c>
@@ -1666,7 +1702,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>333</v>
       </c>
@@ -1674,7 +1710,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -1682,7 +1718,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>246</v>
       </c>
@@ -1690,7 +1726,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>258</v>
       </c>
@@ -1698,7 +1734,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>262</v>
       </c>
@@ -1706,7 +1742,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>260</v>
       </c>
@@ -1714,7 +1750,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>250</v>
       </c>
@@ -1722,7 +1758,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>248</v>
       </c>
@@ -1730,7 +1766,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>252</v>
       </c>
@@ -1738,7 +1774,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>254</v>
       </c>
@@ -1746,7 +1782,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>256</v>
       </c>
@@ -1754,7 +1790,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1762,7 +1798,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>322</v>
       </c>
@@ -1770,7 +1806,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>132</v>
       </c>
@@ -1778,7 +1814,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>238</v>
       </c>
@@ -1786,7 +1822,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>292</v>
       </c>
@@ -1794,7 +1830,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>174</v>
       </c>
@@ -1802,7 +1838,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>176</v>
       </c>
@@ -1810,7 +1846,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>286</v>
       </c>
@@ -1818,7 +1854,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>216</v>
       </c>
@@ -1826,7 +1862,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>290</v>
       </c>
@@ -1834,7 +1870,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>266</v>
       </c>
@@ -1842,7 +1878,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>264</v>
       </c>
@@ -1850,7 +1886,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>272</v>
       </c>
@@ -1858,7 +1894,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>280</v>
       </c>
@@ -1866,7 +1902,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>270</v>
       </c>
@@ -1874,7 +1910,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>278</v>
       </c>
@@ -1882,7 +1918,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>274</v>
       </c>
@@ -1890,7 +1926,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>276</v>
       </c>
@@ -1898,7 +1934,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>268</v>
       </c>
@@ -1906,7 +1942,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>218</v>
       </c>
@@ -1914,7 +1950,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>315</v>
       </c>
@@ -1922,7 +1958,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>296</v>
       </c>
@@ -1930,7 +1966,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -1938,7 +1974,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>154</v>
       </c>
@@ -1946,7 +1982,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -1954,7 +1990,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>306</v>
       </c>
@@ -1962,7 +1998,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>325</v>
       </c>
@@ -1970,7 +2006,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>217</v>
       </c>
@@ -1978,7 +2014,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>305</v>
       </c>
@@ -1986,7 +2022,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>337</v>
       </c>
@@ -1994,7 +2030,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>339</v>
       </c>
@@ -2002,7 +2038,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>345</v>
       </c>
@@ -2010,183 +2046,199 @@
         <v>346</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
     </row>
@@ -2201,14 +2253,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.47265625" customWidth="1"/>
-    <col min="2" max="2" width="49.7890625" customWidth="1"/>
+    <col min="1" max="1" width="43.453125" customWidth="1"/>
+    <col min="2" max="2" width="49.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>146</v>
       </c>
@@ -2216,7 +2268,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>228</v>
       </c>
@@ -2224,7 +2276,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>172</v>
       </c>
@@ -2232,7 +2284,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>298</v>
       </c>
@@ -2240,7 +2292,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>168</v>
       </c>
@@ -2248,7 +2300,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>319</v>
       </c>
@@ -2256,7 +2308,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>307</v>
       </c>
@@ -2264,7 +2316,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -2272,7 +2324,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>140</v>
       </c>
@@ -2280,7 +2332,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>308</v>
       </c>
@@ -2288,7 +2340,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>136</v>
       </c>
@@ -2296,7 +2348,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -2304,7 +2356,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>152</v>
       </c>
@@ -2312,7 +2364,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>108</v>
       </c>
@@ -2320,7 +2372,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>224</v>
       </c>
@@ -2328,7 +2380,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>310</v>
       </c>
@@ -2336,7 +2388,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>114</v>
       </c>
@@ -2344,7 +2396,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>234</v>
       </c>
@@ -2352,7 +2404,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>300</v>
       </c>
@@ -2360,7 +2412,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -2368,7 +2420,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>162</v>
       </c>
@@ -2376,7 +2428,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -2384,7 +2436,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>164</v>
       </c>
@@ -2392,7 +2444,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>128</v>
       </c>
@@ -2400,7 +2452,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>159</v>
       </c>
@@ -2408,7 +2460,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>110</v>
       </c>
@@ -2416,7 +2468,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>324</v>
       </c>
@@ -2424,7 +2476,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>138</v>
       </c>
@@ -2432,7 +2484,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>236</v>
       </c>
@@ -2440,7 +2492,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>347</v>
       </c>
@@ -2448,7 +2500,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>178</v>
       </c>
@@ -2456,7 +2508,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>158</v>
       </c>
@@ -2464,9 +2516,29 @@
         <v>161</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>358</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B28" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}"/>
@@ -2480,13 +2552,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="54.3671875" customWidth="1"/>
-    <col min="2" max="2" width="46.734375" customWidth="1"/>
+    <col min="1" max="1" width="54.36328125" customWidth="1"/>
+    <col min="2" max="2" width="46.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>93</v>
       </c>
@@ -2494,7 +2566,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>95</v>
       </c>
@@ -2502,7 +2574,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -2510,7 +2582,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -2518,7 +2590,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>100</v>
       </c>
@@ -2526,7 +2598,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -2534,7 +2606,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
@@ -2546,14 +2618,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="64.3671875" customWidth="1"/>
-    <col min="2" max="2" width="54.7890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7890625" customWidth="1"/>
+    <col min="1" max="1" width="64.36328125" customWidth="1"/>
+    <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2561,7 +2633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2569,7 +2641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2577,7 +2649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2585,7 +2657,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -2593,7 +2665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2601,7 +2673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2609,7 +2681,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2617,7 +2689,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -2625,7 +2697,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2633,7 +2705,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2641,7 +2713,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2649,7 +2721,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2657,7 +2729,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2665,7 +2737,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -2673,7 +2745,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2681,7 +2753,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -2689,7 +2761,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -2697,7 +2769,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -2705,7 +2777,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -2713,7 +2785,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -2721,7 +2793,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -2729,7 +2801,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -2737,7 +2809,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -2745,7 +2817,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -2753,7 +2825,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -2761,7 +2833,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -2769,7 +2841,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="17.7" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>78</v>
       </c>
@@ -2777,7 +2849,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -2785,7 +2857,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -2793,7 +2865,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>84</v>
       </c>
@@ -2801,7 +2873,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>76</v>
       </c>
@@ -2809,7 +2881,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>86</v>
       </c>
@@ -2817,7 +2889,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>88</v>
       </c>
@@ -2825,7 +2897,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>90</v>
       </c>
@@ -2833,7 +2905,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>92</v>
       </c>
@@ -2841,7 +2913,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>104</v>
       </c>
@@ -2849,7 +2921,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -2857,7 +2929,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -2865,7 +2937,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>112</v>
       </c>
@@ -2873,7 +2945,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>116</v>
       </c>
@@ -2881,7 +2953,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>122</v>
       </c>
@@ -2889,7 +2961,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -2897,7 +2969,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>232</v>
       </c>
@@ -2905,7 +2977,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>335</v>
       </c>
@@ -2913,7 +2985,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>341</v>
       </c>
@@ -2921,7 +2993,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>343</v>
       </c>
@@ -2938,13 +3010,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="81.5234375" customWidth="1"/>
+    <col min="2" max="2" width="81.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>39</v>
       </c>
@@ -2952,7 +3024,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -2960,7 +3032,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>134</v>
       </c>
@@ -2968,7 +3040,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>142</v>
       </c>
@@ -2976,7 +3048,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>220</v>
       </c>
@@ -2984,7 +3056,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>222</v>
       </c>
@@ -2992,7 +3064,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>226</v>
       </c>
@@ -3000,7 +3072,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>230</v>
       </c>
@@ -3008,7 +3080,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>232</v>
       </c>
@@ -3016,7 +3088,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>284</v>
       </c>
@@ -3024,7 +3096,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>288</v>
       </c>
@@ -3040,13 +3112,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="53.5234375" customWidth="1"/>
-    <col min="2" max="2" width="76.89453125" customWidth="1"/>
+    <col min="1" max="1" width="53.54296875" customWidth="1"/>
+    <col min="2" max="2" width="76.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -3054,7 +3126,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>180</v>
       </c>
@@ -3062,7 +3134,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>182</v>
       </c>
@@ -3070,7 +3142,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>184</v>
       </c>
@@ -3078,7 +3150,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>186</v>
       </c>
@@ -3086,7 +3158,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>188</v>
       </c>
@@ -3094,7 +3166,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>190</v>
       </c>
@@ -3102,7 +3174,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -3110,7 +3182,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>194</v>
       </c>
@@ -3118,7 +3190,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>196</v>
       </c>
@@ -3126,7 +3198,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>198</v>
       </c>
@@ -3134,7 +3206,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>200</v>
       </c>
@@ -3142,7 +3214,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>202</v>
       </c>
@@ -3150,7 +3222,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>204</v>
       </c>
@@ -3158,7 +3230,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>206</v>
       </c>
@@ -3166,7 +3238,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>208</v>
       </c>
@@ -3174,7 +3246,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>210</v>
       </c>
@@ -3182,7 +3254,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>212</v>
       </c>
@@ -3190,7 +3262,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>214</v>
       </c>
@@ -3198,7 +3270,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>126</v>
       </c>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BED4282-DEA5-4196-97A2-75BEC48CBE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188AE5A3-16F6-48BA-A749-9CCB1F923E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="369">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1144,6 +1144,18 @@
   </si>
   <si>
     <t>числовой звук</t>
+  </si>
+  <si>
+    <t>цифровой форме</t>
+  </si>
+  <si>
+    <t>числовом виде</t>
+  </si>
+  <si>
+    <t>фазовая модуляция формы</t>
+  </si>
+  <si>
+    <t>временно-промежуточное разделение образа</t>
   </si>
 </sst>
 </file>
@@ -2071,8 +2083,12 @@
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
+      <c r="A65" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
@@ -2253,7 +2269,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.453125" customWidth="1"/>
@@ -2538,6 +2554,14 @@
       </c>
       <c r="B35" s="3" t="s">
         <v>358</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188AE5A3-16F6-48BA-A749-9CCB1F923E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95BCEF6-561D-43F4-844D-83F0BE8EE6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95BCEF6-561D-43F4-844D-83F0BE8EE6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E13988C-4D71-46F5-B592-6F49FEC3C794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="387">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1156,6 +1156,60 @@
   </si>
   <si>
     <t>временно-промежуточное разделение образа</t>
+  </si>
+  <si>
+    <t>минимальный номинальный временной интервал</t>
+  </si>
+  <si>
+    <t>минимальный номинальный</t>
+  </si>
+  <si>
+    <t>наименьшее исходное</t>
+  </si>
+  <si>
+    <t>наименьшее исходное значение временного промежутка</t>
+  </si>
+  <si>
+    <t>выбранной схеме</t>
+  </si>
+  <si>
+    <t>выбранном чертеже</t>
+  </si>
+  <si>
+    <t>двухфазной модуляции</t>
+  </si>
+  <si>
+    <t>двух-шагового разделения</t>
+  </si>
+  <si>
+    <t>двухфазная модуляция</t>
+  </si>
+  <si>
+    <t>двух-шаговое разделение</t>
+  </si>
+  <si>
+    <t>двухфазные модуляции</t>
+  </si>
+  <si>
+    <t>двух-шаговые разделения</t>
+  </si>
+  <si>
+    <t>цифрового аудио</t>
+  </si>
+  <si>
+    <t>числового звука</t>
+  </si>
+  <si>
+    <t>по спецификации</t>
+  </si>
+  <si>
+    <t>по своду требований</t>
+  </si>
+  <si>
+    <t>отмасштабировать отображение</t>
+  </si>
+  <si>
+    <t>установить размер изображения</t>
   </si>
 </sst>
 </file>
@@ -2091,36 +2145,68 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
+      <c r="A66" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
+      <c r="A67" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
+      <c r="A68" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
+      <c r="A69" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
+      <c r="A70" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
+      <c r="A71" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
+      <c r="A72" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
+      <c r="A73" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
@@ -2641,7 +2727,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="64.36328125" customWidth="1"/>
@@ -3023,6 +3109,14 @@
       </c>
       <c r="B47" t="s">
         <v>344</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>369</v>
+      </c>
+      <c r="B48" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E13988C-4D71-46F5-B592-6F49FEC3C794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFEA010-FAC9-42EF-ABC7-3F0A519321DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="399">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1210,6 +1210,42 @@
   </si>
   <si>
     <t>установить размер изображения</t>
+  </si>
+  <si>
+    <t>низкочастотном джиттере</t>
+  </si>
+  <si>
+    <t>частотном дрожжании на низких частотах</t>
+  </si>
+  <si>
+    <t>низкочастотный джиттер</t>
+  </si>
+  <si>
+    <t>частотное дрожжание на низких частотах</t>
+  </si>
+  <si>
+    <t>допуск спецификации</t>
+  </si>
+  <si>
+    <t>допуск свода требований</t>
+  </si>
+  <si>
+    <t>источником синхронизации</t>
+  </si>
+  <si>
+    <t>источником согласования</t>
+  </si>
+  <si>
+    <t>джиттер может быть добавлен</t>
+  </si>
+  <si>
+    <t>частотное дрожжание может быть добавлено</t>
+  </si>
+  <si>
+    <t>сигнала синхронизации</t>
+  </si>
+  <si>
+    <t>согласующего звонка</t>
   </si>
 </sst>
 </file>
@@ -2209,24 +2245,44 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
+      <c r="A74" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
+      <c r="A75" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
+      <c r="A76" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
+      <c r="A77" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
+      <c r="A78" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
@@ -3127,7 +3183,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -3220,6 +3276,14 @@
       </c>
       <c r="B11" t="s">
         <v>289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>395</v>
+      </c>
+      <c r="B12" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFEA010-FAC9-42EF-ABC7-3F0A519321DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513D64C7-D26F-45A3-BAEE-84ECDA57A389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
-    <sheet name="составные важные" sheetId="6" r:id="rId2"/>
-    <sheet name="Вездесущие" sheetId="3" r:id="rId3"/>
-    <sheet name="Неизменные" sheetId="5" r:id="rId4"/>
-    <sheet name="Неизменные_короткие" sheetId="8" r:id="rId5"/>
-    <sheet name="Неизменные_длинные" sheetId="7" r:id="rId6"/>
+    <sheet name="запятые" sheetId="9" r:id="rId2"/>
+    <sheet name="составные важные" sheetId="6" r:id="rId3"/>
+    <sheet name="Вездесущие" sheetId="3" r:id="rId4"/>
+    <sheet name="Неизменные" sheetId="5" r:id="rId5"/>
+    <sheet name="Неизменные_короткие" sheetId="8" r:id="rId6"/>
+    <sheet name="Неизменные_длинные" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Неизменные!$A$1:$B$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Неизменные!$A$1:$B$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные!$A$1:$B$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'составные важные'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'составные важные'!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="434">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1246,6 +1247,111 @@
   </si>
   <si>
     <t>согласующего звонка</t>
+  </si>
+  <si>
+    <t>во фрейме</t>
+  </si>
+  <si>
+    <t>в посылке</t>
+  </si>
+  <si>
+    <t>на фрейм</t>
+  </si>
+  <si>
+    <t>на посылку</t>
+  </si>
+  <si>
+    <t>тактовой синхронизацией</t>
+  </si>
+  <si>
+    <t>задающей соглавание</t>
+  </si>
+  <si>
+    <t>производную фазы</t>
+  </si>
+  <si>
+    <t>производную временного промежутка</t>
+  </si>
+  <si>
+    <t>порчу формы</t>
+  </si>
+  <si>
+    <t>порчу образа</t>
+  </si>
+  <si>
+    <t>Бытовая версия</t>
+  </si>
+  <si>
+    <t>Бытовое исполнение</t>
+  </si>
+  <si>
+    <t>Собственный джиттер</t>
+  </si>
+  <si>
+    <t>Собственное частотное дрожжание</t>
+  </si>
+  <si>
+    <t>джиттер, измеренный</t>
+  </si>
+  <si>
+    <t>частотное дрожжание, измеренное</t>
+  </si>
+  <si>
+    <t>Такой джиттер</t>
+  </si>
+  <si>
+    <t>такое частотное дрожжание</t>
+  </si>
+  <si>
+    <t>внешняя синхронизация</t>
+  </si>
+  <si>
+    <t>внешнее согласование</t>
+  </si>
+  <si>
+    <t>низкую флуктуацию</t>
+  </si>
+  <si>
+    <t>низкое отклонение</t>
+  </si>
+  <si>
+    <t>джиттер мал</t>
+  </si>
+  <si>
+    <t>частотное дрожжание мало</t>
+  </si>
+  <si>
+    <t>внешнюю синхронизацию</t>
+  </si>
+  <si>
+    <t xml:space="preserve">для синхронизации </t>
+  </si>
+  <si>
+    <t>для согласования</t>
+  </si>
+  <si>
+    <t>Джиттер, возникающий</t>
+  </si>
+  <si>
+    <t>частотное дрожжание, возникающее</t>
+  </si>
+  <si>
+    <t>линии передачи</t>
+  </si>
+  <si>
+    <t>пути передачи</t>
+  </si>
+  <si>
+    <t>формы сигнала</t>
+  </si>
+  <si>
+    <t>образа звонка</t>
+  </si>
+  <si>
+    <t>Джиттер, вызванный</t>
+  </si>
+  <si>
+    <t>частотное дрожжание, вызванное</t>
   </si>
 </sst>
 </file>
@@ -2285,64 +2391,124 @@
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
+      <c r="A79" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
+      <c r="A80" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
+      <c r="A81" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
+      <c r="A82" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
+      <c r="A83" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
+      <c r="A84" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
+      <c r="A85" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
+      <c r="A86" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
+      <c r="A87" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
+      <c r="A88" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
+      <c r="A89" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
+      <c r="A90" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
+      <c r="A91" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
+      <c r="A92" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
+      <c r="A93" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
@@ -2410,6 +2576,44 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A9ACB0-12B1-45DA-8517-08CD2F731837}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.7265625" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
   <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2715,7 +2919,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2781,7 +2985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
   <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3181,7 +3385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3291,7 +3495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513D64C7-D26F-45A3-BAEE-84ECDA57A389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E656F903-5C30-4898-9C09-F275A4408065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="438">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1352,6 +1352,18 @@
   </si>
   <si>
     <t>частотное дрожжание, вызванное</t>
+  </si>
+  <si>
+    <t>межсимвольной интерференции</t>
+  </si>
+  <si>
+    <t>меж-знакового взаимного влияния</t>
+  </si>
+  <si>
+    <t>линии связи</t>
+  </si>
+  <si>
+    <t>пути связи</t>
   </si>
 </sst>
 </file>
@@ -2511,12 +2523,20 @@
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
+      <c r="A94" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
+      <c r="A95" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E656F903-5C30-4898-9C09-F275A4408065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B280AC62-7027-4E32-9D2F-AEB13DACE3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B280AC62-7027-4E32-9D2F-AEB13DACE3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D028120-6257-45DE-A961-E19E73FCA771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D028120-6257-45DE-A961-E19E73FCA771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD8C91A-14CC-4DA7-9C62-4A3D696DE1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="27493" windowHeight="13866" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
-    <sheet name="запятые" sheetId="9" r:id="rId2"/>
-    <sheet name="составные важные" sheetId="6" r:id="rId3"/>
+    <sheet name="составные важные" sheetId="6" r:id="rId2"/>
+    <sheet name="запятые" sheetId="9" r:id="rId3"/>
     <sheet name="Вездесущие" sheetId="3" r:id="rId4"/>
     <sheet name="Неизменные" sheetId="5" r:id="rId5"/>
     <sheet name="Неизменные_короткие" sheetId="8" r:id="rId6"/>
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Неизменные!$A$1:$B$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные!$A$1:$B$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'составные важные'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'составные важные'!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="458">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1336,12 +1336,6 @@
     <t>частотное дрожжание, возникающее</t>
   </si>
   <si>
-    <t>линии передачи</t>
-  </si>
-  <si>
-    <t>пути передачи</t>
-  </si>
-  <si>
     <t>формы сигнала</t>
   </si>
   <si>
@@ -1357,13 +1351,79 @@
     <t>межсимвольной интерференции</t>
   </si>
   <si>
-    <t>меж-знакового взаимного влияния</t>
-  </si>
-  <si>
     <t>линии связи</t>
   </si>
   <si>
     <t>пути связи</t>
+  </si>
+  <si>
+    <t>Межсимвольная интерференция</t>
+  </si>
+  <si>
+    <t>Меж-знаковое взаимное влияние</t>
+  </si>
+  <si>
+    <t>измерительной станции</t>
+  </si>
+  <si>
+    <t>измерительной установке</t>
+  </si>
+  <si>
+    <t>начинающий субфрейм</t>
+  </si>
+  <si>
+    <t>начинающий вложенную посылку</t>
+  </si>
+  <si>
+    <t>каждом фрейме</t>
+  </si>
+  <si>
+    <t>каждой посылке</t>
+  </si>
+  <si>
+    <t>смены модуляции</t>
+  </si>
+  <si>
+    <t>смены раз-деления</t>
+  </si>
+  <si>
+    <t>меж-знаковым взаимным влиянияем</t>
+  </si>
+  <si>
+    <t>индикатором межсимвольной интерференции</t>
+  </si>
+  <si>
+    <t>показателем меж-знакового взаимного влияния</t>
+  </si>
+  <si>
+    <t>нечувствительна к межсимвольной интерференции</t>
+  </si>
+  <si>
+    <t>нечувствительна к меж-знаковому взаимному влиянию</t>
+  </si>
+  <si>
+    <t>или межсимвольной интерференции</t>
+  </si>
+  <si>
+    <t>или меж-знаковым взаимным влиянием</t>
+  </si>
+  <si>
+    <t>Джиттер, вызываемый</t>
+  </si>
+  <si>
+    <t>Частотное дрожжание, вызываемое</t>
+  </si>
+  <si>
+    <t>второго субфрейма</t>
+  </si>
+  <si>
+    <t>второй вложенной посылки</t>
+  </si>
+  <si>
+    <t>вызванный шумом джиттер</t>
+  </si>
+  <si>
+    <t>вызваноей шумом частотное дрожжание</t>
   </si>
 </sst>
 </file>
@@ -1772,13 +1832,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
   <dimension ref="A1:B108"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="48.36328125" customWidth="1"/>
-    <col min="2" max="2" width="51.453125" customWidth="1"/>
+    <col min="1" max="1" width="48.3515625" customWidth="1"/>
+    <col min="2" max="2" width="51.46875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>130</v>
       </c>
@@ -1786,7 +1846,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -1794,7 +1854,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" s="3" t="s">
         <v>170</v>
       </c>
@@ -1802,7 +1862,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="3" t="s">
         <v>166</v>
       </c>
@@ -1810,7 +1870,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" s="3" t="s">
         <v>244</v>
       </c>
@@ -1818,7 +1878,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" s="3" t="s">
         <v>242</v>
       </c>
@@ -1826,7 +1886,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>302</v>
       </c>
@@ -1834,7 +1894,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -1842,7 +1902,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" s="3" t="s">
         <v>106</v>
       </c>
@@ -1850,7 +1910,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -1858,7 +1918,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" s="3" t="s">
         <v>313</v>
       </c>
@@ -1866,7 +1926,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
         <v>320</v>
       </c>
@@ -1874,7 +1934,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" s="3" t="s">
         <v>156</v>
       </c>
@@ -1882,7 +1942,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
         <v>144</v>
       </c>
@@ -1890,7 +1950,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" s="3" t="s">
         <v>294</v>
       </c>
@@ -1898,7 +1958,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" s="3" t="s">
         <v>282</v>
       </c>
@@ -1906,7 +1966,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" s="3" t="s">
         <v>240</v>
       </c>
@@ -1914,7 +1974,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" s="3" t="s">
         <v>317</v>
       </c>
@@ -1922,7 +1982,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
         <v>333</v>
       </c>
@@ -1930,7 +1990,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -1938,7 +1998,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A21" s="3" t="s">
         <v>246</v>
       </c>
@@ -1946,7 +2006,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A22" s="3" t="s">
         <v>258</v>
       </c>
@@ -1954,7 +2014,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A23" s="3" t="s">
         <v>262</v>
       </c>
@@ -1962,7 +2022,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A24" s="3" t="s">
         <v>260</v>
       </c>
@@ -1970,7 +2030,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A25" s="3" t="s">
         <v>250</v>
       </c>
@@ -1978,7 +2038,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A26" s="3" t="s">
         <v>248</v>
       </c>
@@ -1986,7 +2046,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A27" s="3" t="s">
         <v>252</v>
       </c>
@@ -1994,7 +2054,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A28" s="3" t="s">
         <v>254</v>
       </c>
@@ -2002,7 +2062,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A29" s="3" t="s">
         <v>256</v>
       </c>
@@ -2010,7 +2070,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2018,7 +2078,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A31" s="3" t="s">
         <v>322</v>
       </c>
@@ -2026,7 +2086,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
         <v>132</v>
       </c>
@@ -2034,7 +2094,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A33" s="3" t="s">
         <v>238</v>
       </c>
@@ -2042,7 +2102,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A34" s="3" t="s">
         <v>292</v>
       </c>
@@ -2050,7 +2110,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A35" s="3" t="s">
         <v>174</v>
       </c>
@@ -2058,7 +2118,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A36" s="3" t="s">
         <v>176</v>
       </c>
@@ -2066,7 +2126,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A37" s="3" t="s">
         <v>286</v>
       </c>
@@ -2074,7 +2134,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A38" s="3" t="s">
         <v>216</v>
       </c>
@@ -2082,7 +2142,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A39" s="3" t="s">
         <v>290</v>
       </c>
@@ -2090,7 +2150,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A40" s="3" t="s">
         <v>266</v>
       </c>
@@ -2098,7 +2158,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A41" s="3" t="s">
         <v>264</v>
       </c>
@@ -2106,7 +2166,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A42" s="3" t="s">
         <v>272</v>
       </c>
@@ -2114,7 +2174,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A43" s="3" t="s">
         <v>280</v>
       </c>
@@ -2122,7 +2182,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A44" s="3" t="s">
         <v>270</v>
       </c>
@@ -2130,7 +2190,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A45" s="3" t="s">
         <v>278</v>
       </c>
@@ -2138,7 +2198,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A46" s="3" t="s">
         <v>274</v>
       </c>
@@ -2146,7 +2206,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A47" s="3" t="s">
         <v>276</v>
       </c>
@@ -2154,7 +2214,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A48" s="3" t="s">
         <v>268</v>
       </c>
@@ -2162,7 +2222,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A49" s="3" t="s">
         <v>218</v>
       </c>
@@ -2170,7 +2230,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A50" s="3" t="s">
         <v>315</v>
       </c>
@@ -2178,7 +2238,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A51" s="3" t="s">
         <v>296</v>
       </c>
@@ -2186,7 +2246,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -2194,7 +2254,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
         <v>154</v>
       </c>
@@ -2202,7 +2262,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -2210,7 +2270,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
         <v>306</v>
       </c>
@@ -2218,7 +2278,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A56" s="3" t="s">
         <v>325</v>
       </c>
@@ -2226,7 +2286,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A57" s="3" t="s">
         <v>217</v>
       </c>
@@ -2234,7 +2294,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
         <v>305</v>
       </c>
@@ -2242,7 +2302,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A59" s="3" t="s">
         <v>337</v>
       </c>
@@ -2250,7 +2310,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A60" s="3" t="s">
         <v>339</v>
       </c>
@@ -2258,7 +2318,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A61" s="3" t="s">
         <v>345</v>
       </c>
@@ -2266,7 +2326,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A62" s="3" t="s">
         <v>359</v>
       </c>
@@ -2274,7 +2334,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A63" s="3" t="s">
         <v>361</v>
       </c>
@@ -2282,7 +2342,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A64" s="3" t="s">
         <v>363</v>
       </c>
@@ -2290,7 +2350,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A65" s="3" t="s">
         <v>365</v>
       </c>
@@ -2298,7 +2358,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A66" s="3" t="s">
         <v>370</v>
       </c>
@@ -2306,7 +2366,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A67" s="3" t="s">
         <v>373</v>
       </c>
@@ -2314,7 +2374,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A68" s="3" t="s">
         <v>375</v>
       </c>
@@ -2322,7 +2382,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A69" s="3" t="s">
         <v>377</v>
       </c>
@@ -2330,7 +2390,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A70" s="3" t="s">
         <v>379</v>
       </c>
@@ -2338,7 +2398,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A71" s="3" t="s">
         <v>381</v>
       </c>
@@ -2346,7 +2406,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A72" s="3" t="s">
         <v>383</v>
       </c>
@@ -2354,7 +2414,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A73" s="3" t="s">
         <v>385</v>
       </c>
@@ -2362,7 +2422,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A74" s="3" t="s">
         <v>387</v>
       </c>
@@ -2370,7 +2430,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A75" s="3" t="s">
         <v>389</v>
       </c>
@@ -2378,7 +2438,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A76" s="3" t="s">
         <v>391</v>
       </c>
@@ -2386,7 +2446,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A77" s="3" t="s">
         <v>393</v>
       </c>
@@ -2394,7 +2454,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A78" s="3" t="s">
         <v>397</v>
       </c>
@@ -2402,7 +2462,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A79" s="3" t="s">
         <v>399</v>
       </c>
@@ -2410,7 +2470,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A80" s="3" t="s">
         <v>401</v>
       </c>
@@ -2418,7 +2478,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A81" s="3" t="s">
         <v>403</v>
       </c>
@@ -2426,7 +2486,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A82" s="3" t="s">
         <v>405</v>
       </c>
@@ -2434,7 +2494,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A83" s="3" t="s">
         <v>407</v>
       </c>
@@ -2442,7 +2502,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A84" s="3" t="s">
         <v>409</v>
       </c>
@@ -2450,7 +2510,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A85" s="3" t="s">
         <v>411</v>
       </c>
@@ -2458,7 +2518,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A86" s="3" t="s">
         <v>415</v>
       </c>
@@ -2466,7 +2526,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A87" s="3" t="s">
         <v>417</v>
       </c>
@@ -2474,7 +2534,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A88" s="3" t="s">
         <v>419</v>
       </c>
@@ -2482,7 +2542,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A89" s="3" t="s">
         <v>421</v>
       </c>
@@ -2490,7 +2550,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A90" s="3" t="s">
         <v>423</v>
       </c>
@@ -2498,7 +2558,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A91" s="3" t="s">
         <v>424</v>
       </c>
@@ -2506,83 +2566,103 @@
         <v>425</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A92" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A93" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B93" s="3" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A93" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A94" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A95" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A95" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="B95" s="3" t="s">
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A96" s="3" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A96" s="3"/>
-      <c r="B96" s="3"/>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B96" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A97" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A98" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A99" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A100" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
     </row>
@@ -2596,53 +2676,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A9ACB0-12B1-45DA-8517-08CD2F731837}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
+  <dimension ref="A1:B37"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" customWidth="1"/>
-    <col min="2" max="2" width="32.6328125" customWidth="1"/>
+    <col min="1" max="1" width="43.46875" customWidth="1"/>
+    <col min="2" max="2" width="49.8203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>413</v>
-      </c>
-      <c r="B1" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>432</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="43.453125" customWidth="1"/>
-    <col min="2" max="2" width="49.81640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>146</v>
       </c>
@@ -2650,7 +2692,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" s="3" t="s">
         <v>228</v>
       </c>
@@ -2658,7 +2700,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" s="3" t="s">
         <v>172</v>
       </c>
@@ -2666,7 +2708,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="3" t="s">
         <v>298</v>
       </c>
@@ -2674,7 +2716,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" s="3" t="s">
         <v>168</v>
       </c>
@@ -2682,7 +2724,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" s="13" t="s">
         <v>319</v>
       </c>
@@ -2690,7 +2732,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>307</v>
       </c>
@@ -2698,7 +2740,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -2706,7 +2748,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
         <v>140</v>
       </c>
@@ -2714,7 +2756,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
         <v>308</v>
       </c>
@@ -2722,7 +2764,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
         <v>136</v>
       </c>
@@ -2730,7 +2772,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -2738,7 +2780,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
         <v>152</v>
       </c>
@@ -2746,7 +2788,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
         <v>108</v>
       </c>
@@ -2754,7 +2796,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
         <v>224</v>
       </c>
@@ -2762,7 +2804,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" s="3" t="s">
         <v>310</v>
       </c>
@@ -2770,7 +2812,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
         <v>114</v>
       </c>
@@ -2778,7 +2820,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" s="3" t="s">
         <v>234</v>
       </c>
@@ -2786,7 +2828,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
         <v>300</v>
       </c>
@@ -2794,7 +2836,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -2802,7 +2844,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A21" s="3" t="s">
         <v>162</v>
       </c>
@@ -2810,7 +2852,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -2818,7 +2860,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A23" s="3" t="s">
         <v>164</v>
       </c>
@@ -2826,7 +2868,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
         <v>128</v>
       </c>
@@ -2834,7 +2876,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A25" s="3" t="s">
         <v>159</v>
       </c>
@@ -2842,7 +2884,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
         <v>110</v>
       </c>
@@ -2850,7 +2892,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A27" s="3" t="s">
         <v>324</v>
       </c>
@@ -2858,7 +2900,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
         <v>138</v>
       </c>
@@ -2866,7 +2908,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A29" s="3" t="s">
         <v>236</v>
       </c>
@@ -2874,7 +2916,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A30" s="3" t="s">
         <v>347</v>
       </c>
@@ -2882,7 +2924,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A31" s="3" t="s">
         <v>178</v>
       </c>
@@ -2890,7 +2932,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A32" s="3" t="s">
         <v>158</v>
       </c>
@@ -2898,7 +2940,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A33" s="3" t="s">
         <v>353</v>
       </c>
@@ -2906,7 +2948,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
       <c r="A34" s="7" t="s">
         <v>355</v>
       </c>
@@ -2914,7 +2956,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A35" s="3" t="s">
         <v>357</v>
       </c>
@@ -2922,12 +2964,20 @@
         <v>358</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A36" s="3" t="s">
         <v>367</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>368</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A37" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -2939,16 +2989,62 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A9ACB0-12B1-45DA-8517-08CD2F731837}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="25.703125" customWidth="1"/>
+    <col min="2" max="2" width="32.64453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A2" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A4" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="54.36328125" customWidth="1"/>
-    <col min="2" max="2" width="46.7265625" customWidth="1"/>
+    <col min="1" max="1" width="54.3515625" customWidth="1"/>
+    <col min="2" max="2" width="46.703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" s="6" t="s">
         <v>93</v>
       </c>
@@ -2956,7 +3052,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" s="6" t="s">
         <v>95</v>
       </c>
@@ -2964,7 +3060,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -2972,7 +3068,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -2980,7 +3076,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
       <c r="A5" s="7" t="s">
         <v>100</v>
       </c>
@@ -2988,7 +3084,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -2996,7 +3092,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
@@ -3007,15 +3103,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
-  <dimension ref="A1:B48"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B49"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="64.36328125" customWidth="1"/>
-    <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.81640625" customWidth="1"/>
+    <col min="1" max="1" width="64.3515625" customWidth="1"/>
+    <col min="2" max="2" width="54.8203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.8203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3023,7 +3119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3031,7 +3127,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3039,7 +3135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3047,7 +3143,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -3055,7 +3151,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3063,7 +3159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3071,7 +3167,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3079,7 +3175,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -3087,7 +3183,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3095,7 +3191,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3103,7 +3199,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3111,7 +3207,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3119,7 +3215,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3127,7 +3223,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3135,7 +3231,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3143,7 +3239,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3151,7 +3247,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -3159,7 +3255,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -3167,7 +3263,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -3175,7 +3271,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -3183,7 +3279,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -3191,7 +3287,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -3199,7 +3295,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -3207,7 +3303,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -3215,7 +3311,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -3223,7 +3319,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -3231,7 +3327,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" ht="17.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
         <v>78</v>
       </c>
@@ -3239,7 +3335,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -3247,7 +3343,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -3255,7 +3351,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A31" s="1" t="s">
         <v>84</v>
       </c>
@@ -3263,7 +3359,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A32" s="3" t="s">
         <v>76</v>
       </c>
@@ -3271,7 +3367,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A33" s="1" t="s">
         <v>86</v>
       </c>
@@ -3279,7 +3375,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A34" s="1" t="s">
         <v>88</v>
       </c>
@@ -3287,7 +3383,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A35" s="1" t="s">
         <v>90</v>
       </c>
@@ -3295,7 +3391,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A36" s="1" t="s">
         <v>92</v>
       </c>
@@ -3303,7 +3399,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A37" s="3" t="s">
         <v>104</v>
       </c>
@@ -3311,7 +3407,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -3319,7 +3415,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -3327,7 +3423,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
         <v>112</v>
       </c>
@@ -3335,7 +3431,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
         <v>116</v>
       </c>
@@ -3343,7 +3439,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
         <v>122</v>
       </c>
@@ -3351,7 +3447,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -3359,7 +3455,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
         <v>232</v>
       </c>
@@ -3367,7 +3463,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
         <v>335</v>
       </c>
@@ -3375,7 +3471,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
         <v>341</v>
       </c>
@@ -3383,7 +3479,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
         <v>343</v>
       </c>
@@ -3391,12 +3487,20 @@
         <v>344</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
         <v>369</v>
       </c>
       <c r="B48" t="s">
         <v>372</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A49" t="s">
+        <v>456</v>
+      </c>
+      <c r="B49" t="s">
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -3407,14 +3511,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="81.54296875" customWidth="1"/>
+    <col min="2" max="2" width="81.52734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
         <v>39</v>
       </c>
@@ -3422,7 +3526,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -3430,7 +3534,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>134</v>
       </c>
@@ -3438,7 +3542,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>142</v>
       </c>
@@ -3446,7 +3550,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>220</v>
       </c>
@@ -3454,7 +3558,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>222</v>
       </c>
@@ -3462,7 +3566,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
         <v>226</v>
       </c>
@@ -3470,7 +3574,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>230</v>
       </c>
@@ -3478,7 +3582,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
         <v>232</v>
       </c>
@@ -3486,7 +3590,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A10" s="11" t="s">
         <v>284</v>
       </c>
@@ -3494,7 +3598,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
         <v>288</v>
       </c>
@@ -3502,12 +3606,28 @@
         <v>289</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
         <v>395</v>
       </c>
       <c r="B12" t="s">
         <v>396</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A13" t="s">
+        <v>448</v>
+      </c>
+      <c r="B13" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A14" t="s">
+        <v>450</v>
+      </c>
+      <c r="B14" t="s">
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -3518,13 +3638,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="53.54296875" customWidth="1"/>
-    <col min="2" max="2" width="76.90625" customWidth="1"/>
+    <col min="1" max="1" width="53.52734375" customWidth="1"/>
+    <col min="2" max="2" width="76.87890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -3532,7 +3652,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" s="3" t="s">
         <v>180</v>
       </c>
@@ -3540,7 +3660,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" s="9" t="s">
         <v>182</v>
       </c>
@@ -3548,7 +3668,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="3" t="s">
         <v>184</v>
       </c>
@@ -3556,7 +3676,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" s="3" t="s">
         <v>186</v>
       </c>
@@ -3564,7 +3684,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" s="3" t="s">
         <v>188</v>
       </c>
@@ -3572,7 +3692,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>190</v>
       </c>
@@ -3580,7 +3700,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -3588,7 +3708,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" s="3" t="s">
         <v>194</v>
       </c>
@@ -3596,7 +3716,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
         <v>196</v>
       </c>
@@ -3604,7 +3724,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" s="3" t="s">
         <v>198</v>
       </c>
@@ -3612,7 +3732,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
         <v>200</v>
       </c>
@@ -3620,7 +3740,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" s="3" t="s">
         <v>202</v>
       </c>
@@ -3628,7 +3748,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" s="3" t="s">
         <v>204</v>
       </c>
@@ -3636,7 +3756,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" s="3" t="s">
         <v>206</v>
       </c>
@@ -3644,7 +3764,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" s="3" t="s">
         <v>208</v>
       </c>
@@ -3652,7 +3772,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" s="3" t="s">
         <v>210</v>
       </c>
@@ -3660,7 +3780,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" s="1" t="s">
         <v>212</v>
       </c>
@@ -3668,7 +3788,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
         <v>214</v>
       </c>
@@ -3676,7 +3796,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>126</v>
       </c>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD8C91A-14CC-4DA7-9C62-4A3D696DE1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C91786-4B82-4460-ACD1-C890244CB4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="27493" windowHeight="13866" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="27493" windowHeight="13866" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -23,6 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Неизменные!$A$1:$B$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Неизменные_длинные!$A$1:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные!$A$1:$B$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'составные важные'!$A$1:$B$28</definedName>
   </definedNames>
@@ -3805,6 +3806,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B20" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C91786-4B82-4460-ACD1-C890244CB4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64291995-0154-4739-9130-FC0F5275D4C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="27493" windowHeight="13866" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="472">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1425,6 +1425,48 @@
   </si>
   <si>
     <t>вызваноей шумом частотное дрожжание</t>
+  </si>
+  <si>
+    <t>пиковый джиттер</t>
+  </si>
+  <si>
+    <t>высшее частотное дрожжание</t>
+  </si>
+  <si>
+    <t>фазовой характеристики</t>
+  </si>
+  <si>
+    <t>временно-про-межуточныз при-знаков</t>
+  </si>
+  <si>
+    <t>срыв синхронизации</t>
+  </si>
+  <si>
+    <t>срыв со-гласования</t>
+  </si>
+  <si>
+    <t>анализ Фурье</t>
+  </si>
+  <si>
+    <t>оценку Фурье</t>
+  </si>
+  <si>
+    <t>временная модуляция</t>
+  </si>
+  <si>
+    <t>временное разделение</t>
+  </si>
+  <si>
+    <t>джиттер распределен</t>
+  </si>
+  <si>
+    <t>частотное дрожжание распределено</t>
+  </si>
+  <si>
+    <t>джиттер редко распределен</t>
+  </si>
+  <si>
+    <t>частотное дрожжание редко распределено</t>
   </si>
 </sst>
 </file>
@@ -2640,24 +2682,44 @@
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
+      <c r="A101" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
+      <c r="A102" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A103" s="3"/>
-      <c r="B103" s="3"/>
+      <c r="A103" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A104" s="3"/>
-      <c r="B104" s="3"/>
+      <c r="A104" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
+      <c r="A105" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B105" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A107" s="3"/>
@@ -2678,7 +2740,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="43.46875" customWidth="1"/>
@@ -2979,6 +3041,14 @@
       </c>
       <c r="B37" s="3" t="s">
         <v>447</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A38" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -3512,7 +3582,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -3629,6 +3699,14 @@
       </c>
       <c r="B14" t="s">
         <v>451</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A15" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>465</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C91786-4B82-4460-ACD1-C890244CB4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CE5E9C-B771-42D3-B198-1A84D0CF11BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="27493" windowHeight="13866" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="466">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1425,6 +1425,30 @@
   </si>
   <si>
     <t>вызваноей шумом частотное дрожжание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">пиковый джиттер </t>
+  </si>
+  <si>
+    <t>высшее частотное дрожжание</t>
+  </si>
+  <si>
+    <t>фазовой характеристики</t>
+  </si>
+  <si>
+    <t>из-за особенностей фазовой характеристики</t>
+  </si>
+  <si>
+    <t>из-за особенностей временно-про-межуточных признаков</t>
+  </si>
+  <si>
+    <t>временно-про-межуточных при-знаков</t>
+  </si>
+  <si>
+    <t xml:space="preserve">суммарный джиттер </t>
+  </si>
+  <si>
+    <t>сложенное частотное дрожжание</t>
   </si>
 </sst>
 </file>
@@ -1833,13 +1857,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
   <dimension ref="A1:B108"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.3515625" customWidth="1"/>
-    <col min="2" max="2" width="51.46875" customWidth="1"/>
+    <col min="1" max="1" width="48.36328125" customWidth="1"/>
+    <col min="2" max="2" width="51.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>130</v>
       </c>
@@ -1847,7 +1871,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -1855,7 +1879,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>170</v>
       </c>
@@ -1863,7 +1887,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>166</v>
       </c>
@@ -1871,7 +1895,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>244</v>
       </c>
@@ -1879,7 +1903,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>242</v>
       </c>
@@ -1887,7 +1911,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>302</v>
       </c>
@@ -1895,7 +1919,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -1903,7 +1927,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>106</v>
       </c>
@@ -1911,7 +1935,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -1919,7 +1943,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>313</v>
       </c>
@@ -1927,7 +1951,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>320</v>
       </c>
@@ -1935,7 +1959,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>156</v>
       </c>
@@ -1943,7 +1967,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>144</v>
       </c>
@@ -1951,7 +1975,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>294</v>
       </c>
@@ -1959,7 +1983,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>282</v>
       </c>
@@ -1967,7 +1991,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>240</v>
       </c>
@@ -1975,7 +1999,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>317</v>
       </c>
@@ -1983,7 +2007,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>333</v>
       </c>
@@ -1991,7 +2015,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -1999,7 +2023,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>246</v>
       </c>
@@ -2007,7 +2031,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>258</v>
       </c>
@@ -2015,7 +2039,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>262</v>
       </c>
@@ -2023,7 +2047,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>260</v>
       </c>
@@ -2031,7 +2055,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>250</v>
       </c>
@@ -2039,7 +2063,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>248</v>
       </c>
@@ -2047,7 +2071,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>252</v>
       </c>
@@ -2055,7 +2079,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>254</v>
       </c>
@@ -2063,7 +2087,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>256</v>
       </c>
@@ -2071,7 +2095,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2079,7 +2103,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>322</v>
       </c>
@@ -2087,7 +2111,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>132</v>
       </c>
@@ -2095,7 +2119,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>238</v>
       </c>
@@ -2103,7 +2127,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>292</v>
       </c>
@@ -2111,7 +2135,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>174</v>
       </c>
@@ -2119,7 +2143,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>176</v>
       </c>
@@ -2127,7 +2151,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>286</v>
       </c>
@@ -2135,7 +2159,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>216</v>
       </c>
@@ -2143,7 +2167,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>290</v>
       </c>
@@ -2151,7 +2175,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>266</v>
       </c>
@@ -2159,7 +2183,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>264</v>
       </c>
@@ -2167,7 +2191,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>272</v>
       </c>
@@ -2175,7 +2199,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>280</v>
       </c>
@@ -2183,7 +2207,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>270</v>
       </c>
@@ -2191,7 +2215,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>278</v>
       </c>
@@ -2199,7 +2223,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>274</v>
       </c>
@@ -2207,7 +2231,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>276</v>
       </c>
@@ -2215,7 +2239,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>268</v>
       </c>
@@ -2223,7 +2247,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>218</v>
       </c>
@@ -2231,7 +2255,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>315</v>
       </c>
@@ -2239,7 +2263,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>296</v>
       </c>
@@ -2247,7 +2271,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -2255,7 +2279,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>154</v>
       </c>
@@ -2263,7 +2287,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -2271,7 +2295,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>306</v>
       </c>
@@ -2279,7 +2303,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>325</v>
       </c>
@@ -2287,7 +2311,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>217</v>
       </c>
@@ -2295,7 +2319,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>305</v>
       </c>
@@ -2303,7 +2327,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>337</v>
       </c>
@@ -2311,7 +2335,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>339</v>
       </c>
@@ -2319,7 +2343,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>345</v>
       </c>
@@ -2327,7 +2351,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>359</v>
       </c>
@@ -2335,7 +2359,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>361</v>
       </c>
@@ -2343,7 +2367,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>363</v>
       </c>
@@ -2351,7 +2375,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>365</v>
       </c>
@@ -2359,7 +2383,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>370</v>
       </c>
@@ -2367,7 +2391,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>373</v>
       </c>
@@ -2375,7 +2399,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>375</v>
       </c>
@@ -2383,7 +2407,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>377</v>
       </c>
@@ -2391,7 +2415,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>379</v>
       </c>
@@ -2399,7 +2423,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>381</v>
       </c>
@@ -2407,7 +2431,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>383</v>
       </c>
@@ -2415,7 +2439,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>385</v>
       </c>
@@ -2423,7 +2447,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>387</v>
       </c>
@@ -2431,7 +2455,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>389</v>
       </c>
@@ -2439,7 +2463,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>391</v>
       </c>
@@ -2447,7 +2471,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>393</v>
       </c>
@@ -2455,7 +2479,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>397</v>
       </c>
@@ -2463,7 +2487,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>399</v>
       </c>
@@ -2471,7 +2495,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>401</v>
       </c>
@@ -2479,7 +2503,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>403</v>
       </c>
@@ -2487,7 +2511,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>405</v>
       </c>
@@ -2495,7 +2519,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>407</v>
       </c>
@@ -2503,7 +2527,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>409</v>
       </c>
@@ -2511,7 +2535,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>411</v>
       </c>
@@ -2519,7 +2543,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>415</v>
       </c>
@@ -2527,7 +2551,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>417</v>
       </c>
@@ -2535,7 +2559,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>419</v>
       </c>
@@ -2543,7 +2567,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>421</v>
       </c>
@@ -2551,7 +2575,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>423</v>
       </c>
@@ -2559,7 +2583,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>424</v>
       </c>
@@ -2567,7 +2591,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>435</v>
       </c>
@@ -2575,7 +2599,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>428</v>
       </c>
@@ -2583,7 +2607,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>432</v>
       </c>
@@ -2591,7 +2615,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>433</v>
       </c>
@@ -2599,7 +2623,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>437</v>
       </c>
@@ -2607,7 +2631,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>439</v>
       </c>
@@ -2615,7 +2639,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>441</v>
       </c>
@@ -2623,7 +2647,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>443</v>
       </c>
@@ -2631,7 +2655,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
         <v>454</v>
       </c>
@@ -2639,31 +2663,43 @@
         <v>455</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A103" s="3"/>
-      <c r="B103" s="3"/>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
     </row>
@@ -2679,13 +2715,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
   <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.46875" customWidth="1"/>
-    <col min="2" max="2" width="49.8203125" customWidth="1"/>
+    <col min="1" max="1" width="43.453125" customWidth="1"/>
+    <col min="2" max="2" width="49.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>146</v>
       </c>
@@ -2693,7 +2729,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>228</v>
       </c>
@@ -2701,7 +2737,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>172</v>
       </c>
@@ -2709,7 +2745,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>298</v>
       </c>
@@ -2717,7 +2753,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>168</v>
       </c>
@@ -2725,7 +2761,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>319</v>
       </c>
@@ -2733,7 +2769,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>307</v>
       </c>
@@ -2741,7 +2777,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -2749,7 +2785,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>140</v>
       </c>
@@ -2757,7 +2793,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>308</v>
       </c>
@@ -2765,7 +2801,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>136</v>
       </c>
@@ -2773,7 +2809,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -2781,7 +2817,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>152</v>
       </c>
@@ -2789,7 +2825,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>108</v>
       </c>
@@ -2797,7 +2833,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>224</v>
       </c>
@@ -2805,7 +2841,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>310</v>
       </c>
@@ -2813,7 +2849,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>114</v>
       </c>
@@ -2821,7 +2857,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>234</v>
       </c>
@@ -2829,7 +2865,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>300</v>
       </c>
@@ -2837,7 +2873,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -2845,7 +2881,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>162</v>
       </c>
@@ -2853,7 +2889,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -2861,7 +2897,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>164</v>
       </c>
@@ -2869,7 +2905,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>128</v>
       </c>
@@ -2877,7 +2913,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>159</v>
       </c>
@@ -2885,7 +2921,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>110</v>
       </c>
@@ -2893,7 +2929,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>324</v>
       </c>
@@ -2901,7 +2937,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>138</v>
       </c>
@@ -2909,7 +2945,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>236</v>
       </c>
@@ -2917,7 +2953,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>347</v>
       </c>
@@ -2925,7 +2961,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>178</v>
       </c>
@@ -2933,7 +2969,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>158</v>
       </c>
@@ -2941,7 +2977,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>353</v>
       </c>
@@ -2949,7 +2985,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>355</v>
       </c>
@@ -2957,7 +2993,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>357</v>
       </c>
@@ -2965,7 +3001,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>367</v>
       </c>
@@ -2973,7 +3009,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>446</v>
       </c>
@@ -2993,13 +3029,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A9ACB0-12B1-45DA-8517-08CD2F731837}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.703125" customWidth="1"/>
-    <col min="2" max="2" width="32.64453125" customWidth="1"/>
+    <col min="1" max="1" width="25.7265625" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>413</v>
       </c>
@@ -3007,7 +3043,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>426</v>
       </c>
@@ -3015,7 +3051,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>430</v>
       </c>
@@ -3023,7 +3059,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>452</v>
       </c>
@@ -3039,13 +3075,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="54.3515625" customWidth="1"/>
-    <col min="2" max="2" width="46.703125" customWidth="1"/>
+    <col min="1" max="1" width="54.36328125" customWidth="1"/>
+    <col min="2" max="2" width="46.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>93</v>
       </c>
@@ -3053,7 +3089,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>95</v>
       </c>
@@ -3061,7 +3097,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -3069,7 +3105,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -3077,7 +3113,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>100</v>
       </c>
@@ -3085,7 +3121,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -3093,7 +3129,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
@@ -3105,14 +3141,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
   <dimension ref="A1:B49"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="64.3515625" customWidth="1"/>
-    <col min="2" max="2" width="54.8203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.8203125" customWidth="1"/>
+    <col min="1" max="1" width="64.36328125" customWidth="1"/>
+    <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3120,7 +3156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3128,7 +3164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3136,7 +3172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3144,7 +3180,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -3152,7 +3188,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3160,7 +3196,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3168,7 +3204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3176,7 +3212,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -3184,7 +3220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3192,7 +3228,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3200,7 +3236,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3208,7 +3244,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3216,7 +3252,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3224,7 +3260,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3232,7 +3268,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3240,7 +3276,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3248,7 +3284,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -3256,7 +3292,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -3264,7 +3300,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -3272,7 +3308,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -3280,7 +3316,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -3288,7 +3324,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -3296,7 +3332,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -3304,7 +3340,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -3312,7 +3348,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -3320,7 +3356,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -3328,7 +3364,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="17.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>78</v>
       </c>
@@ -3336,7 +3372,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -3344,7 +3380,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -3352,7 +3388,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>84</v>
       </c>
@@ -3360,7 +3396,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>76</v>
       </c>
@@ -3368,7 +3404,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>86</v>
       </c>
@@ -3376,7 +3412,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>88</v>
       </c>
@@ -3384,7 +3420,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>90</v>
       </c>
@@ -3392,7 +3428,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>92</v>
       </c>
@@ -3400,7 +3436,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>104</v>
       </c>
@@ -3408,7 +3444,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -3416,7 +3452,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -3424,7 +3460,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>112</v>
       </c>
@@ -3432,7 +3468,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>116</v>
       </c>
@@ -3440,7 +3476,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>122</v>
       </c>
@@ -3448,7 +3484,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -3456,7 +3492,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>232</v>
       </c>
@@ -3464,7 +3500,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>335</v>
       </c>
@@ -3472,7 +3508,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>341</v>
       </c>
@@ -3480,7 +3516,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>343</v>
       </c>
@@ -3488,7 +3524,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>369</v>
       </c>
@@ -3496,7 +3532,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>456</v>
       </c>
@@ -3512,14 +3548,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="81.52734375" customWidth="1"/>
+    <col min="2" max="2" width="81.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>39</v>
       </c>
@@ -3527,7 +3563,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -3535,7 +3571,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>134</v>
       </c>
@@ -3543,7 +3579,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>142</v>
       </c>
@@ -3551,7 +3587,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>220</v>
       </c>
@@ -3559,7 +3595,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>222</v>
       </c>
@@ -3567,7 +3603,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>226</v>
       </c>
@@ -3575,7 +3611,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>230</v>
       </c>
@@ -3583,7 +3619,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>232</v>
       </c>
@@ -3591,7 +3627,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>284</v>
       </c>
@@ -3599,7 +3635,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>288</v>
       </c>
@@ -3607,7 +3643,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>395</v>
       </c>
@@ -3615,7 +3651,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>448</v>
       </c>
@@ -3623,12 +3659,20 @@
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>450</v>
       </c>
       <c r="B14" t="s">
         <v>451</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="18" x14ac:dyDescent="0.4">
+      <c r="A15" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -3639,13 +3683,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="53.52734375" customWidth="1"/>
-    <col min="2" max="2" width="76.87890625" customWidth="1"/>
+    <col min="1" max="1" width="53.54296875" customWidth="1"/>
+    <col min="2" max="2" width="76.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -3653,7 +3697,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>180</v>
       </c>
@@ -3661,7 +3705,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>182</v>
       </c>
@@ -3669,7 +3713,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>184</v>
       </c>
@@ -3677,7 +3721,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>186</v>
       </c>
@@ -3685,7 +3729,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>188</v>
       </c>
@@ -3693,7 +3737,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>190</v>
       </c>
@@ -3701,7 +3745,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -3709,7 +3753,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>194</v>
       </c>
@@ -3717,7 +3761,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>196</v>
       </c>
@@ -3725,7 +3769,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>198</v>
       </c>
@@ -3733,7 +3777,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>200</v>
       </c>
@@ -3741,7 +3785,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>202</v>
       </c>
@@ -3749,7 +3793,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>204</v>
       </c>
@@ -3757,7 +3801,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>206</v>
       </c>
@@ -3765,7 +3809,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>208</v>
       </c>
@@ -3773,7 +3817,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>210</v>
       </c>
@@ -3781,7 +3825,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>212</v>
       </c>
@@ -3789,7 +3833,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>214</v>
       </c>
@@ -3797,7 +3841,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>126</v>
       </c>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64291995-0154-4739-9130-FC0F5275D4C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CB5ECD-1795-41FE-A23A-F70E5C9F0F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="476">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1467,6 +1467,18 @@
   </si>
   <si>
     <t>частотное дрожжание редко распределено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">суммарный джиттер </t>
+  </si>
+  <si>
+    <t>сложенное частотное дрожжание</t>
+  </si>
+  <si>
+    <t>из-за особенностей фазовой характеристики</t>
+  </si>
+  <si>
+    <t>из-за особенностей временно-про-межуточных признаков</t>
   </si>
 </sst>
 </file>
@@ -1875,13 +1887,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
   <dimension ref="A1:B108"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.3515625" customWidth="1"/>
-    <col min="2" max="2" width="51.46875" customWidth="1"/>
+    <col min="1" max="1" width="48.36328125" customWidth="1"/>
+    <col min="2" max="2" width="51.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>130</v>
       </c>
@@ -1889,7 +1901,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -1897,7 +1909,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>170</v>
       </c>
@@ -1905,7 +1917,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>166</v>
       </c>
@@ -1913,7 +1925,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>244</v>
       </c>
@@ -1921,7 +1933,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>242</v>
       </c>
@@ -1929,7 +1941,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>302</v>
       </c>
@@ -1937,7 +1949,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -1945,7 +1957,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>106</v>
       </c>
@@ -1953,7 +1965,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -1961,7 +1973,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>313</v>
       </c>
@@ -1969,7 +1981,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>320</v>
       </c>
@@ -1977,7 +1989,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>156</v>
       </c>
@@ -1985,7 +1997,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>144</v>
       </c>
@@ -1993,7 +2005,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>294</v>
       </c>
@@ -2001,7 +2013,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>282</v>
       </c>
@@ -2009,7 +2021,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>240</v>
       </c>
@@ -2017,7 +2029,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>317</v>
       </c>
@@ -2025,7 +2037,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>333</v>
       </c>
@@ -2033,7 +2045,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -2041,7 +2053,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>246</v>
       </c>
@@ -2049,7 +2061,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>258</v>
       </c>
@@ -2057,7 +2069,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>262</v>
       </c>
@@ -2065,7 +2077,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>260</v>
       </c>
@@ -2073,7 +2085,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>250</v>
       </c>
@@ -2081,7 +2093,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>248</v>
       </c>
@@ -2089,7 +2101,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>252</v>
       </c>
@@ -2097,7 +2109,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>254</v>
       </c>
@@ -2105,7 +2117,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>256</v>
       </c>
@@ -2113,7 +2125,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2121,7 +2133,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>322</v>
       </c>
@@ -2129,7 +2141,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>132</v>
       </c>
@@ -2137,7 +2149,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>238</v>
       </c>
@@ -2145,7 +2157,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>292</v>
       </c>
@@ -2153,7 +2165,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>174</v>
       </c>
@@ -2161,7 +2173,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>176</v>
       </c>
@@ -2169,7 +2181,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>286</v>
       </c>
@@ -2177,7 +2189,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>216</v>
       </c>
@@ -2185,7 +2197,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>290</v>
       </c>
@@ -2193,7 +2205,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>266</v>
       </c>
@@ -2201,7 +2213,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>264</v>
       </c>
@@ -2209,7 +2221,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>272</v>
       </c>
@@ -2217,7 +2229,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>280</v>
       </c>
@@ -2225,7 +2237,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>270</v>
       </c>
@@ -2233,7 +2245,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>278</v>
       </c>
@@ -2241,7 +2253,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>274</v>
       </c>
@@ -2249,7 +2261,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>276</v>
       </c>
@@ -2257,7 +2269,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>268</v>
       </c>
@@ -2265,7 +2277,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>218</v>
       </c>
@@ -2273,7 +2285,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>315</v>
       </c>
@@ -2281,7 +2293,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>296</v>
       </c>
@@ -2289,7 +2301,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -2297,7 +2309,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>154</v>
       </c>
@@ -2305,7 +2317,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -2313,7 +2325,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>306</v>
       </c>
@@ -2321,7 +2333,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>325</v>
       </c>
@@ -2329,7 +2341,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>217</v>
       </c>
@@ -2337,7 +2349,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>305</v>
       </c>
@@ -2345,7 +2357,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>337</v>
       </c>
@@ -2353,7 +2365,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>339</v>
       </c>
@@ -2361,7 +2373,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>345</v>
       </c>
@@ -2369,7 +2381,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>359</v>
       </c>
@@ -2377,7 +2389,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>361</v>
       </c>
@@ -2385,7 +2397,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>363</v>
       </c>
@@ -2393,7 +2405,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>365</v>
       </c>
@@ -2401,7 +2413,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>370</v>
       </c>
@@ -2409,7 +2421,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>373</v>
       </c>
@@ -2417,7 +2429,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>375</v>
       </c>
@@ -2425,7 +2437,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>377</v>
       </c>
@@ -2433,7 +2445,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>379</v>
       </c>
@@ -2441,7 +2453,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>381</v>
       </c>
@@ -2449,7 +2461,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>383</v>
       </c>
@@ -2457,7 +2469,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>385</v>
       </c>
@@ -2465,7 +2477,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>387</v>
       </c>
@@ -2473,7 +2485,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>389</v>
       </c>
@@ -2481,7 +2493,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>391</v>
       </c>
@@ -2489,7 +2501,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>393</v>
       </c>
@@ -2497,7 +2509,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>397</v>
       </c>
@@ -2505,7 +2517,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>399</v>
       </c>
@@ -2513,7 +2525,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>401</v>
       </c>
@@ -2521,7 +2533,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>403</v>
       </c>
@@ -2529,7 +2541,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>405</v>
       </c>
@@ -2537,7 +2549,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>407</v>
       </c>
@@ -2545,7 +2557,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>409</v>
       </c>
@@ -2553,7 +2565,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>411</v>
       </c>
@@ -2561,7 +2573,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>415</v>
       </c>
@@ -2569,7 +2581,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>417</v>
       </c>
@@ -2577,7 +2589,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>419</v>
       </c>
@@ -2585,7 +2597,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>421</v>
       </c>
@@ -2593,7 +2605,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>423</v>
       </c>
@@ -2601,7 +2613,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>424</v>
       </c>
@@ -2609,7 +2621,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>435</v>
       </c>
@@ -2617,7 +2629,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>428</v>
       </c>
@@ -2625,7 +2637,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>432</v>
       </c>
@@ -2633,7 +2645,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>433</v>
       </c>
@@ -2641,7 +2653,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>437</v>
       </c>
@@ -2649,7 +2661,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>439</v>
       </c>
@@ -2657,7 +2669,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>441</v>
       </c>
@@ -2665,7 +2677,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>443</v>
       </c>
@@ -2673,7 +2685,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
         <v>454</v>
       </c>
@@ -2681,7 +2693,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
         <v>458</v>
       </c>
@@ -2689,7 +2701,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
         <v>460</v>
       </c>
@@ -2697,7 +2709,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>462</v>
       </c>
@@ -2705,7 +2717,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
         <v>466</v>
       </c>
@@ -2713,7 +2725,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>468</v>
       </c>
@@ -2721,11 +2733,19 @@
         <v>469</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
     </row>
@@ -2741,13 +2761,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
   <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.46875" customWidth="1"/>
-    <col min="2" max="2" width="49.8203125" customWidth="1"/>
+    <col min="1" max="1" width="43.453125" customWidth="1"/>
+    <col min="2" max="2" width="49.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>146</v>
       </c>
@@ -2755,7 +2775,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>228</v>
       </c>
@@ -2763,7 +2783,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>172</v>
       </c>
@@ -2771,7 +2791,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>298</v>
       </c>
@@ -2779,7 +2799,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>168</v>
       </c>
@@ -2787,7 +2807,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>319</v>
       </c>
@@ -2795,7 +2815,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>307</v>
       </c>
@@ -2803,7 +2823,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -2811,7 +2831,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>140</v>
       </c>
@@ -2819,7 +2839,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>308</v>
       </c>
@@ -2827,7 +2847,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>136</v>
       </c>
@@ -2835,7 +2855,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -2843,7 +2863,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>152</v>
       </c>
@@ -2851,7 +2871,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>108</v>
       </c>
@@ -2859,7 +2879,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>224</v>
       </c>
@@ -2867,7 +2887,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>310</v>
       </c>
@@ -2875,7 +2895,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>114</v>
       </c>
@@ -2883,7 +2903,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>234</v>
       </c>
@@ -2891,7 +2911,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>300</v>
       </c>
@@ -2899,7 +2919,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -2907,7 +2927,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>162</v>
       </c>
@@ -2915,7 +2935,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -2923,7 +2943,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>164</v>
       </c>
@@ -2931,7 +2951,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>128</v>
       </c>
@@ -2939,7 +2959,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>159</v>
       </c>
@@ -2947,7 +2967,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>110</v>
       </c>
@@ -2955,7 +2975,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>324</v>
       </c>
@@ -2963,7 +2983,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>138</v>
       </c>
@@ -2971,7 +2991,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>236</v>
       </c>
@@ -2979,7 +2999,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>347</v>
       </c>
@@ -2987,7 +3007,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>178</v>
       </c>
@@ -2995,7 +3015,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>158</v>
       </c>
@@ -3003,7 +3023,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>353</v>
       </c>
@@ -3011,7 +3031,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>355</v>
       </c>
@@ -3019,7 +3039,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>357</v>
       </c>
@@ -3027,7 +3047,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>367</v>
       </c>
@@ -3035,7 +3055,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>446</v>
       </c>
@@ -3043,7 +3063,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>470</v>
       </c>
@@ -3063,13 +3083,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A9ACB0-12B1-45DA-8517-08CD2F731837}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.703125" customWidth="1"/>
-    <col min="2" max="2" width="32.64453125" customWidth="1"/>
+    <col min="1" max="1" width="25.7265625" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>413</v>
       </c>
@@ -3077,7 +3097,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>426</v>
       </c>
@@ -3085,7 +3105,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>430</v>
       </c>
@@ -3093,7 +3113,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>452</v>
       </c>
@@ -3109,13 +3129,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="54.3515625" customWidth="1"/>
-    <col min="2" max="2" width="46.703125" customWidth="1"/>
+    <col min="1" max="1" width="54.36328125" customWidth="1"/>
+    <col min="2" max="2" width="46.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>93</v>
       </c>
@@ -3123,7 +3143,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>95</v>
       </c>
@@ -3131,7 +3151,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -3139,7 +3159,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -3147,7 +3167,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>100</v>
       </c>
@@ -3155,7 +3175,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -3163,7 +3183,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
@@ -3175,14 +3195,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
   <dimension ref="A1:B49"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="64.3515625" customWidth="1"/>
-    <col min="2" max="2" width="54.8203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.8203125" customWidth="1"/>
+    <col min="1" max="1" width="64.36328125" customWidth="1"/>
+    <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3190,7 +3210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3198,7 +3218,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3206,7 +3226,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3214,7 +3234,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -3222,7 +3242,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3230,7 +3250,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3238,7 +3258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3246,7 +3266,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -3254,7 +3274,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3262,7 +3282,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3270,7 +3290,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3278,7 +3298,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3286,7 +3306,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3294,7 +3314,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3302,7 +3322,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3310,7 +3330,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3318,7 +3338,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -3326,7 +3346,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -3334,7 +3354,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -3342,7 +3362,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -3350,7 +3370,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -3358,7 +3378,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -3366,7 +3386,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -3374,7 +3394,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -3382,7 +3402,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -3390,7 +3410,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,7 +3418,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="17.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>78</v>
       </c>
@@ -3406,7 +3426,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -3414,7 +3434,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -3422,7 +3442,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>84</v>
       </c>
@@ -3430,7 +3450,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>76</v>
       </c>
@@ -3438,7 +3458,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>86</v>
       </c>
@@ -3446,7 +3466,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>88</v>
       </c>
@@ -3454,7 +3474,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>90</v>
       </c>
@@ -3462,7 +3482,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>92</v>
       </c>
@@ -3470,7 +3490,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>104</v>
       </c>
@@ -3478,7 +3498,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -3486,7 +3506,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -3494,7 +3514,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>112</v>
       </c>
@@ -3502,7 +3522,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>116</v>
       </c>
@@ -3510,7 +3530,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>122</v>
       </c>
@@ -3518,7 +3538,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -3526,7 +3546,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>232</v>
       </c>
@@ -3534,7 +3554,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>335</v>
       </c>
@@ -3542,7 +3562,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>341</v>
       </c>
@@ -3550,7 +3570,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>343</v>
       </c>
@@ -3558,7 +3578,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>369</v>
       </c>
@@ -3566,7 +3586,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>456</v>
       </c>
@@ -3582,14 +3602,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="81.52734375" customWidth="1"/>
+    <col min="2" max="2" width="81.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>39</v>
       </c>
@@ -3597,7 +3617,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -3605,7 +3625,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>134</v>
       </c>
@@ -3613,7 +3633,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>142</v>
       </c>
@@ -3621,7 +3641,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>220</v>
       </c>
@@ -3629,7 +3649,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>222</v>
       </c>
@@ -3637,7 +3657,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>226</v>
       </c>
@@ -3645,7 +3665,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>230</v>
       </c>
@@ -3653,7 +3673,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>232</v>
       </c>
@@ -3661,7 +3681,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>284</v>
       </c>
@@ -3669,7 +3689,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>288</v>
       </c>
@@ -3677,7 +3697,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>395</v>
       </c>
@@ -3685,7 +3705,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>448</v>
       </c>
@@ -3693,7 +3713,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>450</v>
       </c>
@@ -3701,12 +3721,20 @@
         <v>451</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>464</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>465</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="18" x14ac:dyDescent="0.4">
+      <c r="A16" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -3717,13 +3745,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="53.52734375" customWidth="1"/>
-    <col min="2" max="2" width="76.87890625" customWidth="1"/>
+    <col min="1" max="1" width="53.54296875" customWidth="1"/>
+    <col min="2" max="2" width="76.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -3731,7 +3759,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>180</v>
       </c>
@@ -3739,7 +3767,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>182</v>
       </c>
@@ -3747,7 +3775,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>184</v>
       </c>
@@ -3755,7 +3783,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>186</v>
       </c>
@@ -3763,7 +3791,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>188</v>
       </c>
@@ -3771,7 +3799,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>190</v>
       </c>
@@ -3779,7 +3807,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -3787,7 +3815,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>194</v>
       </c>
@@ -3795,7 +3823,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>196</v>
       </c>
@@ -3803,7 +3831,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>198</v>
       </c>
@@ -3811,7 +3839,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>200</v>
       </c>
@@ -3819,7 +3847,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>202</v>
       </c>
@@ -3827,7 +3855,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>204</v>
       </c>
@@ -3835,7 +3863,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>206</v>
       </c>
@@ -3843,7 +3871,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>208</v>
       </c>
@@ -3851,7 +3879,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>210</v>
       </c>
@@ -3859,7 +3887,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>212</v>
       </c>
@@ -3867,7 +3895,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>214</v>
       </c>
@@ -3875,7 +3903,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>126</v>
       </c>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CB5ECD-1795-41FE-A23A-F70E5C9F0F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A55010D-5F67-496E-94C7-603A57145230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="484">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1479,6 +1479,30 @@
   </si>
   <si>
     <t>из-за особенностей временно-про-межуточных признаков</t>
+  </si>
+  <si>
+    <t>Амплитудная модуляция</t>
+  </si>
+  <si>
+    <t>Раз-маховое раз-деление</t>
+  </si>
+  <si>
+    <t>Амплитудная модуляция, вызванная</t>
+  </si>
+  <si>
+    <t>Раз-маховая раз-деление, вызванное</t>
+  </si>
+  <si>
+    <t>амплитудной модуляции</t>
+  </si>
+  <si>
+    <t>Раз-махового раз-деления</t>
+  </si>
+  <si>
+    <t>временной модуляцией</t>
+  </si>
+  <si>
+    <t>временным раз-делением</t>
   </si>
 </sst>
 </file>
@@ -1886,14 +1910,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B108"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B109"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="48.36328125" customWidth="1"/>
-    <col min="2" max="2" width="51.453125" customWidth="1"/>
+    <col min="1" max="1" width="48.3515625" customWidth="1"/>
+    <col min="2" max="2" width="51.46875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>130</v>
       </c>
@@ -1901,7 +1925,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -1909,7 +1933,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" s="3" t="s">
         <v>170</v>
       </c>
@@ -1917,7 +1941,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="3" t="s">
         <v>166</v>
       </c>
@@ -1925,7 +1949,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" s="3" t="s">
         <v>244</v>
       </c>
@@ -1933,7 +1957,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" s="3" t="s">
         <v>242</v>
       </c>
@@ -1941,7 +1965,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>302</v>
       </c>
@@ -1949,7 +1973,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -1957,7 +1981,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" s="3" t="s">
         <v>106</v>
       </c>
@@ -1965,7 +1989,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -1973,7 +1997,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" s="3" t="s">
         <v>313</v>
       </c>
@@ -1981,7 +2005,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
         <v>320</v>
       </c>
@@ -1989,7 +2013,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" s="3" t="s">
         <v>156</v>
       </c>
@@ -1997,7 +2021,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
         <v>144</v>
       </c>
@@ -2005,7 +2029,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" s="3" t="s">
         <v>294</v>
       </c>
@@ -2013,7 +2037,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" s="3" t="s">
         <v>282</v>
       </c>
@@ -2021,7 +2045,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" s="3" t="s">
         <v>240</v>
       </c>
@@ -2029,7 +2053,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" s="3" t="s">
         <v>317</v>
       </c>
@@ -2037,7 +2061,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
         <v>333</v>
       </c>
@@ -2045,7 +2069,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -2053,7 +2077,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A21" s="3" t="s">
         <v>246</v>
       </c>
@@ -2061,7 +2085,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A22" s="3" t="s">
         <v>258</v>
       </c>
@@ -2069,7 +2093,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A23" s="3" t="s">
         <v>262</v>
       </c>
@@ -2077,7 +2101,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A24" s="3" t="s">
         <v>260</v>
       </c>
@@ -2085,7 +2109,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A25" s="3" t="s">
         <v>250</v>
       </c>
@@ -2093,7 +2117,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A26" s="3" t="s">
         <v>248</v>
       </c>
@@ -2101,7 +2125,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A27" s="3" t="s">
         <v>252</v>
       </c>
@@ -2109,7 +2133,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A28" s="3" t="s">
         <v>254</v>
       </c>
@@ -2117,7 +2141,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A29" s="3" t="s">
         <v>256</v>
       </c>
@@ -2125,7 +2149,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2133,7 +2157,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A31" s="3" t="s">
         <v>322</v>
       </c>
@@ -2141,7 +2165,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
         <v>132</v>
       </c>
@@ -2149,7 +2173,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A33" s="3" t="s">
         <v>238</v>
       </c>
@@ -2157,7 +2181,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A34" s="3" t="s">
         <v>292</v>
       </c>
@@ -2165,7 +2189,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A35" s="3" t="s">
         <v>174</v>
       </c>
@@ -2173,7 +2197,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A36" s="3" t="s">
         <v>176</v>
       </c>
@@ -2181,7 +2205,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A37" s="3" t="s">
         <v>286</v>
       </c>
@@ -2189,7 +2213,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A38" s="3" t="s">
         <v>216</v>
       </c>
@@ -2197,7 +2221,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A39" s="3" t="s">
         <v>290</v>
       </c>
@@ -2205,7 +2229,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A40" s="3" t="s">
         <v>266</v>
       </c>
@@ -2213,7 +2237,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A41" s="3" t="s">
         <v>264</v>
       </c>
@@ -2221,7 +2245,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A42" s="3" t="s">
         <v>272</v>
       </c>
@@ -2229,7 +2253,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A43" s="3" t="s">
         <v>280</v>
       </c>
@@ -2237,7 +2261,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A44" s="3" t="s">
         <v>270</v>
       </c>
@@ -2245,7 +2269,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A45" s="3" t="s">
         <v>278</v>
       </c>
@@ -2253,7 +2277,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A46" s="3" t="s">
         <v>274</v>
       </c>
@@ -2261,7 +2285,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A47" s="3" t="s">
         <v>276</v>
       </c>
@@ -2269,7 +2293,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A48" s="3" t="s">
         <v>268</v>
       </c>
@@ -2277,7 +2301,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A49" s="3" t="s">
         <v>218</v>
       </c>
@@ -2285,7 +2309,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A50" s="3" t="s">
         <v>315</v>
       </c>
@@ -2293,7 +2317,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A51" s="3" t="s">
         <v>296</v>
       </c>
@@ -2301,7 +2325,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -2309,7 +2333,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
         <v>154</v>
       </c>
@@ -2317,7 +2341,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -2325,7 +2349,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
         <v>306</v>
       </c>
@@ -2333,7 +2357,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A56" s="3" t="s">
         <v>325</v>
       </c>
@@ -2341,7 +2365,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A57" s="3" t="s">
         <v>217</v>
       </c>
@@ -2349,7 +2373,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
         <v>305</v>
       </c>
@@ -2357,7 +2381,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A59" s="3" t="s">
         <v>337</v>
       </c>
@@ -2365,7 +2389,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A60" s="3" t="s">
         <v>339</v>
       </c>
@@ -2373,7 +2397,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A61" s="3" t="s">
         <v>345</v>
       </c>
@@ -2381,7 +2405,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A62" s="3" t="s">
         <v>359</v>
       </c>
@@ -2389,7 +2413,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A63" s="3" t="s">
         <v>361</v>
       </c>
@@ -2397,7 +2421,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A64" s="3" t="s">
         <v>363</v>
       </c>
@@ -2405,7 +2429,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A65" s="3" t="s">
         <v>365</v>
       </c>
@@ -2413,7 +2437,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A66" s="3" t="s">
         <v>370</v>
       </c>
@@ -2421,7 +2445,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A67" s="3" t="s">
         <v>373</v>
       </c>
@@ -2429,7 +2453,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A68" s="3" t="s">
         <v>375</v>
       </c>
@@ -2437,7 +2461,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A69" s="3" t="s">
         <v>377</v>
       </c>
@@ -2445,7 +2469,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A70" s="3" t="s">
         <v>379</v>
       </c>
@@ -2453,7 +2477,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A71" s="3" t="s">
         <v>381</v>
       </c>
@@ -2461,7 +2485,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A72" s="3" t="s">
         <v>383</v>
       </c>
@@ -2469,7 +2493,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A73" s="3" t="s">
         <v>385</v>
       </c>
@@ -2477,7 +2501,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A74" s="3" t="s">
         <v>387</v>
       </c>
@@ -2485,7 +2509,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A75" s="3" t="s">
         <v>389</v>
       </c>
@@ -2493,7 +2517,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A76" s="3" t="s">
         <v>391</v>
       </c>
@@ -2501,7 +2525,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A77" s="3" t="s">
         <v>393</v>
       </c>
@@ -2509,7 +2533,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A78" s="3" t="s">
         <v>397</v>
       </c>
@@ -2517,7 +2541,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A79" s="3" t="s">
         <v>399</v>
       </c>
@@ -2525,7 +2549,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A80" s="3" t="s">
         <v>401</v>
       </c>
@@ -2533,7 +2557,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A81" s="3" t="s">
         <v>403</v>
       </c>
@@ -2541,7 +2565,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A82" s="3" t="s">
         <v>405</v>
       </c>
@@ -2549,7 +2573,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A83" s="3" t="s">
         <v>407</v>
       </c>
@@ -2557,7 +2581,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A84" s="3" t="s">
         <v>409</v>
       </c>
@@ -2565,7 +2589,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A85" s="3" t="s">
         <v>411</v>
       </c>
@@ -2573,7 +2597,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A86" s="3" t="s">
         <v>415</v>
       </c>
@@ -2581,7 +2605,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A87" s="3" t="s">
         <v>417</v>
       </c>
@@ -2589,7 +2613,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A88" s="3" t="s">
         <v>419</v>
       </c>
@@ -2597,7 +2621,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A89" s="3" t="s">
         <v>421</v>
       </c>
@@ -2605,7 +2629,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A90" s="3" t="s">
         <v>423</v>
       </c>
@@ -2613,7 +2637,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A91" s="3" t="s">
         <v>424</v>
       </c>
@@ -2621,7 +2645,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A92" s="3" t="s">
         <v>435</v>
       </c>
@@ -2629,7 +2653,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A93" s="3" t="s">
         <v>428</v>
       </c>
@@ -2637,7 +2661,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A94" s="3" t="s">
         <v>432</v>
       </c>
@@ -2645,7 +2669,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A95" s="3" t="s">
         <v>433</v>
       </c>
@@ -2653,7 +2677,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A96" s="3" t="s">
         <v>437</v>
       </c>
@@ -2661,7 +2685,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A97" s="3" t="s">
         <v>439</v>
       </c>
@@ -2669,7 +2693,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A98" s="3" t="s">
         <v>441</v>
       </c>
@@ -2677,7 +2701,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A99" s="3" t="s">
         <v>443</v>
       </c>
@@ -2685,7 +2709,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A100" s="3" t="s">
         <v>454</v>
       </c>
@@ -2693,7 +2717,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A101" s="3" t="s">
         <v>458</v>
       </c>
@@ -2701,7 +2725,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A102" s="3" t="s">
         <v>460</v>
       </c>
@@ -2709,7 +2733,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A103" s="3" t="s">
         <v>462</v>
       </c>
@@ -2717,7 +2741,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A104" s="3" t="s">
         <v>466</v>
       </c>
@@ -2725,7 +2749,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A105" s="3" t="s">
         <v>468</v>
       </c>
@@ -2733,7 +2757,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A106" s="3" t="s">
         <v>472</v>
       </c>
@@ -2741,13 +2765,29 @@
         <v>473</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A107" s="3"/>
-      <c r="B107" s="3"/>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A108" s="3"/>
-      <c r="B108" s="3"/>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A107" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A108" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A109" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>483</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B109" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}"/>
@@ -2760,14 +2800,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B39"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="43.453125" customWidth="1"/>
-    <col min="2" max="2" width="49.81640625" customWidth="1"/>
+    <col min="1" max="1" width="43.46875" customWidth="1"/>
+    <col min="2" max="2" width="49.8203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>146</v>
       </c>
@@ -2775,7 +2815,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" s="3" t="s">
         <v>228</v>
       </c>
@@ -2783,7 +2823,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" s="3" t="s">
         <v>172</v>
       </c>
@@ -2791,7 +2831,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="3" t="s">
         <v>298</v>
       </c>
@@ -2799,7 +2839,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" s="3" t="s">
         <v>168</v>
       </c>
@@ -2807,7 +2847,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" s="13" t="s">
         <v>319</v>
       </c>
@@ -2815,7 +2855,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>307</v>
       </c>
@@ -2823,7 +2863,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -2831,7 +2871,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
         <v>140</v>
       </c>
@@ -2839,7 +2879,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
         <v>308</v>
       </c>
@@ -2847,7 +2887,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
         <v>136</v>
       </c>
@@ -2855,7 +2895,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -2863,7 +2903,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
         <v>152</v>
       </c>
@@ -2871,7 +2911,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
         <v>108</v>
       </c>
@@ -2879,7 +2919,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
         <v>224</v>
       </c>
@@ -2887,7 +2927,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" s="3" t="s">
         <v>310</v>
       </c>
@@ -2895,7 +2935,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
         <v>114</v>
       </c>
@@ -2903,7 +2943,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" s="3" t="s">
         <v>234</v>
       </c>
@@ -2911,7 +2951,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
         <v>300</v>
       </c>
@@ -2919,7 +2959,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -2927,7 +2967,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A21" s="3" t="s">
         <v>162</v>
       </c>
@@ -2935,7 +2975,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -2943,7 +2983,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A23" s="3" t="s">
         <v>164</v>
       </c>
@@ -2951,7 +2991,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
         <v>128</v>
       </c>
@@ -2959,7 +2999,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A25" s="3" t="s">
         <v>159</v>
       </c>
@@ -2967,7 +3007,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
         <v>110</v>
       </c>
@@ -2975,7 +3015,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A27" s="3" t="s">
         <v>324</v>
       </c>
@@ -2983,7 +3023,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
         <v>138</v>
       </c>
@@ -2991,7 +3031,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A29" s="3" t="s">
         <v>236</v>
       </c>
@@ -2999,7 +3039,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A30" s="3" t="s">
         <v>347</v>
       </c>
@@ -3007,7 +3047,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A31" s="3" t="s">
         <v>178</v>
       </c>
@@ -3015,7 +3055,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A32" s="3" t="s">
         <v>158</v>
       </c>
@@ -3023,7 +3063,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A33" s="3" t="s">
         <v>353</v>
       </c>
@@ -3031,7 +3071,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
       <c r="A34" s="7" t="s">
         <v>355</v>
       </c>
@@ -3039,7 +3079,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A35" s="3" t="s">
         <v>357</v>
       </c>
@@ -3047,7 +3087,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A36" s="3" t="s">
         <v>367</v>
       </c>
@@ -3055,7 +3095,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A37" s="3" t="s">
         <v>446</v>
       </c>
@@ -3063,12 +3103,20 @@
         <v>447</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A38" s="3" t="s">
         <v>470</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A39" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -3083,13 +3131,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A9ACB0-12B1-45DA-8517-08CD2F731837}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" customWidth="1"/>
-    <col min="2" max="2" width="32.6328125" customWidth="1"/>
+    <col min="1" max="1" width="25.703125" customWidth="1"/>
+    <col min="2" max="2" width="32.64453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>413</v>
       </c>
@@ -3097,7 +3145,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" s="3" t="s">
         <v>426</v>
       </c>
@@ -3105,7 +3153,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>430</v>
       </c>
@@ -3113,7 +3161,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="3" t="s">
         <v>452</v>
       </c>
@@ -3129,13 +3177,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="54.36328125" customWidth="1"/>
-    <col min="2" max="2" width="46.7265625" customWidth="1"/>
+    <col min="1" max="1" width="54.3515625" customWidth="1"/>
+    <col min="2" max="2" width="46.703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" s="6" t="s">
         <v>93</v>
       </c>
@@ -3143,7 +3191,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" s="6" t="s">
         <v>95</v>
       </c>
@@ -3151,7 +3199,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -3159,7 +3207,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -3167,7 +3215,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
       <c r="A5" s="7" t="s">
         <v>100</v>
       </c>
@@ -3175,7 +3223,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -3183,7 +3231,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
@@ -3195,14 +3243,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
   <dimension ref="A1:B49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="64.36328125" customWidth="1"/>
-    <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.81640625" customWidth="1"/>
+    <col min="1" max="1" width="64.3515625" customWidth="1"/>
+    <col min="2" max="2" width="54.8203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.8203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3210,7 +3258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3218,7 +3266,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3226,7 +3274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3234,7 +3282,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -3242,7 +3290,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3250,7 +3298,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3258,7 +3306,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3266,7 +3314,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -3274,7 +3322,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3282,7 +3330,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3290,7 +3338,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3298,7 +3346,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3306,7 +3354,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3314,7 +3362,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3322,7 +3370,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3330,7 +3378,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3338,7 +3386,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -3346,7 +3394,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -3354,7 +3402,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -3362,7 +3410,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -3370,7 +3418,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -3378,7 +3426,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -3386,7 +3434,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -3394,7 +3442,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -3402,7 +3450,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -3410,7 +3458,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -3418,7 +3466,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" ht="17.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
         <v>78</v>
       </c>
@@ -3426,7 +3474,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -3434,7 +3482,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -3442,7 +3490,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A31" s="1" t="s">
         <v>84</v>
       </c>
@@ -3450,7 +3498,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A32" s="3" t="s">
         <v>76</v>
       </c>
@@ -3458,7 +3506,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A33" s="1" t="s">
         <v>86</v>
       </c>
@@ -3466,7 +3514,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A34" s="1" t="s">
         <v>88</v>
       </c>
@@ -3474,7 +3522,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A35" s="1" t="s">
         <v>90</v>
       </c>
@@ -3482,7 +3530,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A36" s="1" t="s">
         <v>92</v>
       </c>
@@ -3490,7 +3538,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A37" s="3" t="s">
         <v>104</v>
       </c>
@@ -3498,7 +3546,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -3506,7 +3554,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -3514,7 +3562,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
         <v>112</v>
       </c>
@@ -3522,7 +3570,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
         <v>116</v>
       </c>
@@ -3530,7 +3578,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
         <v>122</v>
       </c>
@@ -3538,7 +3586,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -3546,7 +3594,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
         <v>232</v>
       </c>
@@ -3554,7 +3602,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
         <v>335</v>
       </c>
@@ -3562,7 +3610,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
         <v>341</v>
       </c>
@@ -3570,7 +3618,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
         <v>343</v>
       </c>
@@ -3578,7 +3626,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
         <v>369</v>
       </c>
@@ -3586,7 +3634,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
         <v>456</v>
       </c>
@@ -3603,13 +3651,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="81.54296875" customWidth="1"/>
+    <col min="2" max="2" width="81.52734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
         <v>39</v>
       </c>
@@ -3617,7 +3665,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -3625,7 +3673,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>134</v>
       </c>
@@ -3633,7 +3681,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>142</v>
       </c>
@@ -3641,7 +3689,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>220</v>
       </c>
@@ -3649,7 +3697,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>222</v>
       </c>
@@ -3657,7 +3705,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
         <v>226</v>
       </c>
@@ -3665,7 +3713,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>230</v>
       </c>
@@ -3673,7 +3721,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
         <v>232</v>
       </c>
@@ -3681,7 +3729,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A10" s="11" t="s">
         <v>284</v>
       </c>
@@ -3689,7 +3737,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
         <v>288</v>
       </c>
@@ -3697,7 +3745,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
         <v>395</v>
       </c>
@@ -3705,7 +3753,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
         <v>448</v>
       </c>
@@ -3713,7 +3761,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
         <v>450</v>
       </c>
@@ -3721,7 +3769,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" s="3" t="s">
         <v>464</v>
       </c>
@@ -3729,7 +3777,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="18" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" ht="17.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
         <v>474</v>
       </c>
@@ -3745,13 +3793,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="53.54296875" customWidth="1"/>
-    <col min="2" max="2" width="76.90625" customWidth="1"/>
+    <col min="1" max="1" width="53.52734375" customWidth="1"/>
+    <col min="2" max="2" width="76.87890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -3759,7 +3807,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" s="3" t="s">
         <v>180</v>
       </c>
@@ -3767,7 +3815,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" s="9" t="s">
         <v>182</v>
       </c>
@@ -3775,7 +3823,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="3" t="s">
         <v>184</v>
       </c>
@@ -3783,7 +3831,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" s="3" t="s">
         <v>186</v>
       </c>
@@ -3791,7 +3839,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" s="3" t="s">
         <v>188</v>
       </c>
@@ -3799,7 +3847,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>190</v>
       </c>
@@ -3807,7 +3855,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -3815,7 +3863,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" s="3" t="s">
         <v>194</v>
       </c>
@@ -3823,7 +3871,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
         <v>196</v>
       </c>
@@ -3831,7 +3879,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" s="3" t="s">
         <v>198</v>
       </c>
@@ -3839,7 +3887,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
         <v>200</v>
       </c>
@@ -3847,7 +3895,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" s="3" t="s">
         <v>202</v>
       </c>
@@ -3855,7 +3903,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" s="3" t="s">
         <v>204</v>
       </c>
@@ -3863,7 +3911,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" s="3" t="s">
         <v>206</v>
       </c>
@@ -3871,7 +3919,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" s="3" t="s">
         <v>208</v>
       </c>
@@ -3879,7 +3927,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" s="3" t="s">
         <v>210</v>
       </c>
@@ -3887,7 +3935,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" s="1" t="s">
         <v>212</v>
       </c>
@@ -3895,7 +3943,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
         <v>214</v>
       </c>
@@ -3903,7 +3951,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>126</v>
       </c>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A55010D-5F67-496E-94C7-603A57145230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB866D1-BCCC-4E0D-9655-D77815C80B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="492">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1503,13 +1503,37 @@
   </si>
   <si>
     <t>временным раз-делением</t>
+  </si>
+  <si>
+    <t>частотное дрожжание не будет видно</t>
+  </si>
+  <si>
+    <t>джиттер не будет виден</t>
+  </si>
+  <si>
+    <t>автоподстройкой фазы</t>
+  </si>
+  <si>
+    <t>само-под-стройкой временных про-межутков</t>
+  </si>
+  <si>
+    <t>диаграмма, построенная</t>
+  </si>
+  <si>
+    <t>чертёж-рисунок, построенный</t>
+  </si>
+  <si>
+    <t>Глазковая диаграмма, построенная</t>
+  </si>
+  <si>
+    <t>Очный чертёж-рисунок, построенный</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1592,6 +1616,13 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1613,7 +1644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1630,6 +1661,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1910,7 +1942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="48.3515625" customWidth="1"/>
@@ -2787,6 +2819,14 @@
       </c>
       <c r="B109" s="3" t="s">
         <v>483</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A110" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
@@ -3130,7 +3170,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A9ACB0-12B1-45DA-8517-08CD2F731837}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="25.703125" customWidth="1"/>
@@ -3167,6 +3207,14 @@
       </c>
       <c r="B4" s="3" t="s">
         <v>453</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A5" t="s">
+        <v>488</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -3242,7 +3290,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="64.3515625" customWidth="1"/>
@@ -3642,6 +3690,14 @@
         <v>457</v>
       </c>
     </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A50" t="s">
+        <v>485</v>
+      </c>
+      <c r="B50" t="s">
+        <v>484</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B36" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3650,7 +3706,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -3777,12 +3833,20 @@
         <v>465</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="17.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A16" s="14" t="s">
         <v>474</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>475</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A17" t="s">
+        <v>490</v>
+      </c>
+      <c r="B17" t="s">
+        <v>491</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB866D1-BCCC-4E0D-9655-D77815C80B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5248ADE0-57E8-4F73-AB54-1C35D18A3287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="503">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1436,9 +1436,6 @@
     <t>фазовой характеристики</t>
   </si>
   <si>
-    <t>временно-про-межуточныз при-знаков</t>
-  </si>
-  <si>
     <t>срыв синхронизации</t>
   </si>
   <si>
@@ -1469,12 +1466,6 @@
     <t>частотное дрожжание редко распределено</t>
   </si>
   <si>
-    <t xml:space="preserve">суммарный джиттер </t>
-  </si>
-  <si>
-    <t>сложенное частотное дрожжание</t>
-  </si>
-  <si>
     <t>из-за особенностей фазовой характеристики</t>
   </si>
   <si>
@@ -1527,6 +1518,48 @@
   </si>
   <si>
     <t>Очный чертёж-рисунок, построенный</t>
+  </si>
+  <si>
+    <t>вызванное шумом частотное дрожжание</t>
+  </si>
+  <si>
+    <t>джиттер цифрового выхода равен</t>
+  </si>
+  <si>
+    <t>частотное дрожжание числового выхода равно</t>
+  </si>
+  <si>
+    <t>межсимвольной интерференцией</t>
+  </si>
+  <si>
+    <t>межзнаковым взаимным влиянием</t>
+  </si>
+  <si>
+    <t>свойства линии передачи</t>
+  </si>
+  <si>
+    <t>свойства пути передачи</t>
+  </si>
+  <si>
+    <t>Этот дрейф</t>
+  </si>
+  <si>
+    <t>Это направленное движение заряженных частиц</t>
+  </si>
+  <si>
+    <t>временно-про-межуточных при-знаков</t>
+  </si>
+  <si>
+    <t>джиттер, образующийся</t>
+  </si>
+  <si>
+    <t>Частотное дрожжание, образующееся</t>
+  </si>
+  <si>
+    <t>суммарный джиттер</t>
+  </si>
+  <si>
+    <t>совокупное частотное дрожжание</t>
   </si>
 </sst>
 </file>
@@ -1942,7 +1975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="48.3515625" customWidth="1"/>
@@ -2762,71 +2795,87 @@
         <v>460</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>461</v>
+        <v>498</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A103" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A104" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="B104" s="3" t="s">
         <v>466</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A105" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B105" t="s">
         <v>468</v>
-      </c>
-      <c r="B105" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A106" s="3" t="s">
-        <v>472</v>
+        <v>501</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>473</v>
+        <v>502</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A107" s="3" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A108" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A109" s="3" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A110" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>487</v>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A111" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A112" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -2840,7 +2889,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="43.46875" customWidth="1"/>
@@ -3145,18 +3194,26 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A38" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A39" s="3" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>479</v>
+        <v>476</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A40" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -3170,7 +3227,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A9ACB0-12B1-45DA-8517-08CD2F731837}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="25.703125" customWidth="1"/>
@@ -3211,10 +3268,18 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A6" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -3692,10 +3757,10 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B50" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -3706,7 +3771,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -3827,25 +3892,41 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>464</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" s="14" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
+        <v>487</v>
+      </c>
+      <c r="B17" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A18" t="s">
+        <v>456</v>
+      </c>
+      <c r="B18" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A19" t="s">
         <v>490</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B19" t="s">
         <v>491</v>
       </c>
     </row>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5248ADE0-57E8-4F73-AB54-1C35D18A3287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4619538-08B5-4F14-B05B-B491CECB5357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4619538-08B5-4F14-B05B-B491CECB5357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438C6259-0FE3-4A8F-99B5-6260AADD4BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438C6259-0FE3-4A8F-99B5-6260AADD4BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EED64D-C5B9-4C27-894A-FD2FD035212F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="507">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1560,6 +1560,18 @@
   </si>
   <si>
     <t>совокупное частотное дрожжание</t>
+  </si>
+  <si>
+    <t>схема задержки была сосредоточена</t>
+  </si>
+  <si>
+    <t>Схема задержки была сосредоточена</t>
+  </si>
+  <si>
+    <t>За-мысел за-держки был со-средоточен</t>
+  </si>
+  <si>
+    <t>за-мысел за-держки был со-средоточен</t>
   </si>
 </sst>
 </file>
@@ -1976,13 +1988,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
   <dimension ref="A1:B112"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.3515625" customWidth="1"/>
-    <col min="2" max="2" width="51.46875" customWidth="1"/>
+    <col min="1" max="1" width="48.36328125" customWidth="1"/>
+    <col min="2" max="2" width="51.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>130</v>
       </c>
@@ -1990,7 +2002,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -1998,7 +2010,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>170</v>
       </c>
@@ -2006,7 +2018,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>166</v>
       </c>
@@ -2014,7 +2026,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>244</v>
       </c>
@@ -2022,7 +2034,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>242</v>
       </c>
@@ -2030,7 +2042,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>302</v>
       </c>
@@ -2038,7 +2050,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -2046,7 +2058,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>106</v>
       </c>
@@ -2054,7 +2066,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -2062,7 +2074,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>313</v>
       </c>
@@ -2070,7 +2082,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>320</v>
       </c>
@@ -2078,7 +2090,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>156</v>
       </c>
@@ -2086,7 +2098,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>144</v>
       </c>
@@ -2094,7 +2106,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>294</v>
       </c>
@@ -2102,7 +2114,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>282</v>
       </c>
@@ -2110,7 +2122,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>240</v>
       </c>
@@ -2118,7 +2130,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>317</v>
       </c>
@@ -2126,7 +2138,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>333</v>
       </c>
@@ -2134,7 +2146,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -2142,7 +2154,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>246</v>
       </c>
@@ -2150,7 +2162,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>258</v>
       </c>
@@ -2158,7 +2170,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>262</v>
       </c>
@@ -2166,7 +2178,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>260</v>
       </c>
@@ -2174,7 +2186,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>250</v>
       </c>
@@ -2182,7 +2194,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>248</v>
       </c>
@@ -2190,7 +2202,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>252</v>
       </c>
@@ -2198,7 +2210,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>254</v>
       </c>
@@ -2206,7 +2218,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>256</v>
       </c>
@@ -2214,7 +2226,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2222,7 +2234,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>322</v>
       </c>
@@ -2230,7 +2242,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>132</v>
       </c>
@@ -2238,7 +2250,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>238</v>
       </c>
@@ -2246,7 +2258,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>292</v>
       </c>
@@ -2254,7 +2266,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>174</v>
       </c>
@@ -2262,7 +2274,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>176</v>
       </c>
@@ -2270,7 +2282,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>286</v>
       </c>
@@ -2278,7 +2290,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>216</v>
       </c>
@@ -2286,7 +2298,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>290</v>
       </c>
@@ -2294,7 +2306,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>266</v>
       </c>
@@ -2302,7 +2314,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>264</v>
       </c>
@@ -2310,7 +2322,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>272</v>
       </c>
@@ -2318,7 +2330,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>280</v>
       </c>
@@ -2326,7 +2338,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>270</v>
       </c>
@@ -2334,7 +2346,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>278</v>
       </c>
@@ -2342,7 +2354,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>274</v>
       </c>
@@ -2350,7 +2362,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>276</v>
       </c>
@@ -2358,7 +2370,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>268</v>
       </c>
@@ -2366,7 +2378,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>218</v>
       </c>
@@ -2374,7 +2386,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>315</v>
       </c>
@@ -2382,7 +2394,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>296</v>
       </c>
@@ -2390,7 +2402,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -2398,7 +2410,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>154</v>
       </c>
@@ -2406,7 +2418,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -2414,7 +2426,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>306</v>
       </c>
@@ -2422,7 +2434,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>325</v>
       </c>
@@ -2430,7 +2442,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>217</v>
       </c>
@@ -2438,7 +2450,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>305</v>
       </c>
@@ -2446,7 +2458,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>337</v>
       </c>
@@ -2454,7 +2466,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>339</v>
       </c>
@@ -2462,7 +2474,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>345</v>
       </c>
@@ -2470,7 +2482,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>359</v>
       </c>
@@ -2478,7 +2490,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>361</v>
       </c>
@@ -2486,7 +2498,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>363</v>
       </c>
@@ -2494,7 +2506,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>365</v>
       </c>
@@ -2502,7 +2514,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>370</v>
       </c>
@@ -2510,7 +2522,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>373</v>
       </c>
@@ -2518,7 +2530,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>375</v>
       </c>
@@ -2526,7 +2538,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>377</v>
       </c>
@@ -2534,7 +2546,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>379</v>
       </c>
@@ -2542,7 +2554,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>381</v>
       </c>
@@ -2550,7 +2562,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>383</v>
       </c>
@@ -2558,7 +2570,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>385</v>
       </c>
@@ -2566,7 +2578,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>387</v>
       </c>
@@ -2574,7 +2586,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>389</v>
       </c>
@@ -2582,7 +2594,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>391</v>
       </c>
@@ -2590,7 +2602,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>393</v>
       </c>
@@ -2598,7 +2610,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>397</v>
       </c>
@@ -2606,7 +2618,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>399</v>
       </c>
@@ -2614,7 +2626,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>401</v>
       </c>
@@ -2622,7 +2634,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>403</v>
       </c>
@@ -2630,7 +2642,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>405</v>
       </c>
@@ -2638,7 +2650,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>407</v>
       </c>
@@ -2646,7 +2658,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>409</v>
       </c>
@@ -2654,7 +2666,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>411</v>
       </c>
@@ -2662,7 +2674,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>415</v>
       </c>
@@ -2670,7 +2682,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>417</v>
       </c>
@@ -2678,7 +2690,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>419</v>
       </c>
@@ -2686,7 +2698,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>421</v>
       </c>
@@ -2694,7 +2706,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>423</v>
       </c>
@@ -2702,7 +2714,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>424</v>
       </c>
@@ -2710,7 +2722,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>435</v>
       </c>
@@ -2718,7 +2730,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>428</v>
       </c>
@@ -2726,7 +2738,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>432</v>
       </c>
@@ -2734,7 +2746,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>433</v>
       </c>
@@ -2742,7 +2754,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>437</v>
       </c>
@@ -2750,7 +2762,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>439</v>
       </c>
@@ -2758,7 +2770,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>441</v>
       </c>
@@ -2766,7 +2778,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>443</v>
       </c>
@@ -2774,7 +2786,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
         <v>454</v>
       </c>
@@ -2782,7 +2794,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
         <v>458</v>
       </c>
@@ -2790,7 +2802,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
         <v>460</v>
       </c>
@@ -2798,7 +2810,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>461</v>
       </c>
@@ -2806,7 +2818,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
         <v>465</v>
       </c>
@@ -2814,7 +2826,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>467</v>
       </c>
@@ -2822,7 +2834,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
         <v>501</v>
       </c>
@@ -2830,7 +2842,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>473</v>
       </c>
@@ -2838,7 +2850,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
         <v>477</v>
       </c>
@@ -2846,7 +2858,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
         <v>479</v>
       </c>
@@ -2854,7 +2866,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
         <v>483</v>
       </c>
@@ -2862,7 +2874,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>492</v>
       </c>
@@ -2870,7 +2882,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
         <v>496</v>
       </c>
@@ -2890,13 +2902,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
   <dimension ref="A1:B40"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.46875" customWidth="1"/>
-    <col min="2" max="2" width="49.8203125" customWidth="1"/>
+    <col min="1" max="1" width="43.453125" customWidth="1"/>
+    <col min="2" max="2" width="49.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>146</v>
       </c>
@@ -2904,7 +2916,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>228</v>
       </c>
@@ -2912,7 +2924,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>172</v>
       </c>
@@ -2920,7 +2932,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>298</v>
       </c>
@@ -2928,7 +2940,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>168</v>
       </c>
@@ -2936,7 +2948,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>319</v>
       </c>
@@ -2944,7 +2956,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>307</v>
       </c>
@@ -2952,7 +2964,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -2960,7 +2972,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>140</v>
       </c>
@@ -2968,7 +2980,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>308</v>
       </c>
@@ -2976,7 +2988,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>136</v>
       </c>
@@ -2984,7 +2996,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -2992,7 +3004,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>152</v>
       </c>
@@ -3000,7 +3012,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>108</v>
       </c>
@@ -3008,7 +3020,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>224</v>
       </c>
@@ -3016,7 +3028,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>310</v>
       </c>
@@ -3024,7 +3036,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>114</v>
       </c>
@@ -3032,7 +3044,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>234</v>
       </c>
@@ -3040,7 +3052,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>300</v>
       </c>
@@ -3048,7 +3060,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -3056,7 +3068,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>162</v>
       </c>
@@ -3064,7 +3076,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -3072,7 +3084,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>164</v>
       </c>
@@ -3080,7 +3092,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>128</v>
       </c>
@@ -3088,7 +3100,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>159</v>
       </c>
@@ -3096,7 +3108,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>110</v>
       </c>
@@ -3104,7 +3116,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>324</v>
       </c>
@@ -3112,7 +3124,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>138</v>
       </c>
@@ -3120,7 +3132,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>236</v>
       </c>
@@ -3128,7 +3140,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>347</v>
       </c>
@@ -3136,7 +3148,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>178</v>
       </c>
@@ -3144,7 +3156,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>158</v>
       </c>
@@ -3152,7 +3164,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>353</v>
       </c>
@@ -3160,7 +3172,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>355</v>
       </c>
@@ -3168,7 +3180,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>357</v>
       </c>
@@ -3176,7 +3188,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>367</v>
       </c>
@@ -3184,7 +3196,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>446</v>
       </c>
@@ -3192,7 +3204,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>469</v>
       </c>
@@ -3200,7 +3212,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>475</v>
       </c>
@@ -3208,7 +3220,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>494</v>
       </c>
@@ -3228,13 +3240,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A9ACB0-12B1-45DA-8517-08CD2F731837}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.703125" customWidth="1"/>
-    <col min="2" max="2" width="32.64453125" customWidth="1"/>
+    <col min="1" max="1" width="25.7265625" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>413</v>
       </c>
@@ -3242,7 +3254,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>426</v>
       </c>
@@ -3250,7 +3262,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>430</v>
       </c>
@@ -3258,7 +3270,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>452</v>
       </c>
@@ -3266,7 +3278,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>485</v>
       </c>
@@ -3274,7 +3286,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>499</v>
       </c>
@@ -3290,13 +3302,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="54.3515625" customWidth="1"/>
-    <col min="2" max="2" width="46.703125" customWidth="1"/>
+    <col min="1" max="1" width="54.36328125" customWidth="1"/>
+    <col min="2" max="2" width="46.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>93</v>
       </c>
@@ -3304,7 +3316,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>95</v>
       </c>
@@ -3312,7 +3324,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -3320,7 +3332,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -3328,7 +3340,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.35" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>100</v>
       </c>
@@ -3336,7 +3348,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -3344,7 +3356,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
@@ -3356,14 +3368,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="64.3515625" customWidth="1"/>
-    <col min="2" max="2" width="54.8203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.8203125" customWidth="1"/>
+    <col min="1" max="1" width="64.36328125" customWidth="1"/>
+    <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3371,7 +3383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3379,7 +3391,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3387,7 +3399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3395,7 +3407,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -3403,7 +3415,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3411,7 +3423,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3419,7 +3431,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3427,7 +3439,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -3435,7 +3447,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3443,7 +3455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3451,7 +3463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3459,7 +3471,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3467,7 +3479,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3475,7 +3487,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3483,7 +3495,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3491,7 +3503,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3499,7 +3511,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -3507,7 +3519,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -3515,7 +3527,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -3523,7 +3535,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -3531,7 +3543,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -3539,7 +3551,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -3547,7 +3559,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -3555,7 +3567,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -3563,7 +3575,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -3571,7 +3583,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -3579,7 +3591,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="17.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>78</v>
       </c>
@@ -3587,7 +3599,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -3595,7 +3607,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -3603,7 +3615,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>84</v>
       </c>
@@ -3611,7 +3623,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>76</v>
       </c>
@@ -3619,7 +3631,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>86</v>
       </c>
@@ -3627,7 +3639,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>88</v>
       </c>
@@ -3635,7 +3647,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>90</v>
       </c>
@@ -3643,7 +3655,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>92</v>
       </c>
@@ -3651,7 +3663,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>104</v>
       </c>
@@ -3659,7 +3671,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -3667,7 +3679,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -3675,7 +3687,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>112</v>
       </c>
@@ -3683,7 +3695,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>116</v>
       </c>
@@ -3691,7 +3703,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>122</v>
       </c>
@@ -3699,7 +3711,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -3707,7 +3719,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>232</v>
       </c>
@@ -3715,7 +3727,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>335</v>
       </c>
@@ -3723,7 +3735,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>341</v>
       </c>
@@ -3731,7 +3743,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>343</v>
       </c>
@@ -3739,7 +3751,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>369</v>
       </c>
@@ -3747,7 +3759,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>456</v>
       </c>
@@ -3755,7 +3767,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>482</v>
       </c>
@@ -3771,14 +3783,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="81.52734375" customWidth="1"/>
+    <col min="2" max="2" width="81.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>39</v>
       </c>
@@ -3786,7 +3798,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -3794,7 +3806,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>134</v>
       </c>
@@ -3802,7 +3814,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>142</v>
       </c>
@@ -3810,7 +3822,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>220</v>
       </c>
@@ -3818,7 +3830,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>222</v>
       </c>
@@ -3826,7 +3838,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>226</v>
       </c>
@@ -3834,7 +3846,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>230</v>
       </c>
@@ -3842,7 +3854,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>232</v>
       </c>
@@ -3850,7 +3862,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>284</v>
       </c>
@@ -3858,7 +3870,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>288</v>
       </c>
@@ -3866,7 +3878,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>395</v>
       </c>
@@ -3874,7 +3886,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>448</v>
       </c>
@@ -3882,7 +3894,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>450</v>
       </c>
@@ -3890,7 +3902,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>463</v>
       </c>
@@ -3898,7 +3910,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
         <v>471</v>
       </c>
@@ -3906,7 +3918,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>487</v>
       </c>
@@ -3914,7 +3926,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>456</v>
       </c>
@@ -3922,12 +3934,28 @@
         <v>489</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>490</v>
       </c>
       <c r="B19" t="s">
         <v>491</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>503</v>
+      </c>
+      <c r="B20" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>504</v>
+      </c>
+      <c r="B21" t="s">
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -3938,13 +3966,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="53.52734375" customWidth="1"/>
-    <col min="2" max="2" width="76.87890625" customWidth="1"/>
+    <col min="1" max="1" width="53.54296875" customWidth="1"/>
+    <col min="2" max="2" width="76.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -3952,7 +3980,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>180</v>
       </c>
@@ -3960,7 +3988,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>182</v>
       </c>
@@ -3968,7 +3996,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>184</v>
       </c>
@@ -3976,7 +4004,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>186</v>
       </c>
@@ -3984,7 +4012,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>188</v>
       </c>
@@ -3992,7 +4020,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>190</v>
       </c>
@@ -4000,7 +4028,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -4008,7 +4036,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>194</v>
       </c>
@@ -4016,7 +4044,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>196</v>
       </c>
@@ -4024,7 +4052,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>198</v>
       </c>
@@ -4032,7 +4060,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>200</v>
       </c>
@@ -4040,7 +4068,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>202</v>
       </c>
@@ -4048,7 +4076,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>204</v>
       </c>
@@ -4056,7 +4084,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>206</v>
       </c>
@@ -4064,7 +4092,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>208</v>
       </c>
@@ -4072,7 +4100,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>210</v>
       </c>
@@ -4080,7 +4108,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>212</v>
       </c>
@@ -4088,7 +4116,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>214</v>
       </c>
@@ -4096,7 +4124,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>126</v>
       </c>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EED64D-C5B9-4C27-894A-FD2FD035212F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD89824-A3C1-453A-8F0A-EBF69099663A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="509">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1572,6 +1572,12 @@
   </si>
   <si>
     <t>за-мысел за-держки был со-средоточен</t>
+  </si>
+  <si>
+    <t>примененную терминацию</t>
+  </si>
+  <si>
+    <t>применённое подавление</t>
   </si>
 </sst>
 </file>
@@ -1987,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.36328125" customWidth="1"/>
@@ -2888,6 +2894,14 @@
       </c>
       <c r="B112" s="3" t="s">
         <v>497</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>508</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD89824-A3C1-453A-8F0A-EBF69099663A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC35E693-E847-4B8C-9566-6BA605249080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="511">
   <si>
     <t>со чертежом сумматора, приведенной</t>
   </si>
@@ -1578,6 +1578,12 @@
   </si>
   <si>
     <t>применённое подавление</t>
+  </si>
+  <si>
+    <t>емкость идеального конденсатора</t>
+  </si>
+  <si>
+    <t>вместимость совершенной ёмкости</t>
   </si>
 </sst>
 </file>
@@ -2915,7 +2921,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.453125" customWidth="1"/>
@@ -3240,6 +3246,14 @@
       </c>
       <c r="B40" s="3" t="s">
         <v>495</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>510</v>
       </c>
     </row>
   </sheetData>
